--- a/Libro1.xlsx
+++ b/Libro1.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hug.leon\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hug.leon\Desktop\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{48A860DE-C6CC-472C-A7C9-CCF2E99512D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A7393C7-5A4E-41CF-81B4-27A39B539C83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3150" yWindow="345" windowWidth="21600" windowHeight="11295" xr2:uid="{04497E22-FEAF-4EAE-A69F-4E82C41B14CF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{04497E22-FEAF-4EAE-A69F-4E82C41B14CF}"/>
   </bookViews>
   <sheets>
     <sheet name="MODEMS  2026 MAESTRO" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'MODEMS  2026 MAESTRO'!$G$1:$K$744</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'MODEMS  2026 MAESTRO'!$A$1:$D$619</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3454" uniqueCount="1435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3456" uniqueCount="1434">
   <si>
     <t>Bus</t>
   </si>
@@ -3974,9 +3974,6 @@
   </si>
   <si>
     <t>0</t>
-  </si>
-  <si>
-    <t>FASHION</t>
   </si>
   <si>
     <t>CORPORATIVO</t>
@@ -5178,7 +5175,7 @@
         <v>13</v>
       </c>
       <c r="I2" t="str">
-        <f>VLOOKUP(G2,D:D,1,0)</f>
+        <f t="shared" ref="I2:I65" si="0">VLOOKUP(G2,D:D,1,0)</f>
         <v>8956030216926247991</v>
       </c>
       <c r="J2" s="11"/>
@@ -5206,7 +5203,7 @@
         <v>17</v>
       </c>
       <c r="I3" t="str">
-        <f>VLOOKUP(G3,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>8956030242988506082</v>
       </c>
       <c r="J3" s="11"/>
@@ -5234,7 +5231,7 @@
         <v>17</v>
       </c>
       <c r="I4" t="str">
-        <f>VLOOKUP(G4,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>8956030221943028861</v>
       </c>
       <c r="J4" s="11"/>
@@ -5265,7 +5262,7 @@
         <v>17</v>
       </c>
       <c r="I5" t="e">
-        <f>VLOOKUP(G5,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
       <c r="J5" s="11"/>
@@ -5293,7 +5290,7 @@
         <v>17</v>
       </c>
       <c r="I6" t="e">
-        <f>VLOOKUP(G6,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
       <c r="J6" s="11"/>
@@ -5321,7 +5318,7 @@
         <v>17</v>
       </c>
       <c r="I7" t="str">
-        <f>VLOOKUP(G7,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>8956030185729635571</v>
       </c>
       <c r="J7" s="11"/>
@@ -5349,7 +5346,7 @@
         <v>17</v>
       </c>
       <c r="I8" t="e">
-        <f>VLOOKUP(G8,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
       <c r="J8" s="11"/>
@@ -5377,7 +5374,7 @@
         <v>17</v>
       </c>
       <c r="I9" t="e">
-        <f>VLOOKUP(G9,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
       <c r="J9" s="11"/>
@@ -5405,7 +5402,7 @@
         <v>17</v>
       </c>
       <c r="I10" t="str">
-        <f>VLOOKUP(G10,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>8956032244723774197</v>
       </c>
       <c r="J10" s="11"/>
@@ -5431,7 +5428,7 @@
         <v>17</v>
       </c>
       <c r="I11" t="e">
-        <f>VLOOKUP(G11,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
       <c r="J11" s="11"/>
@@ -5459,7 +5456,7 @@
         <v>17</v>
       </c>
       <c r="I12" t="e">
-        <f>VLOOKUP(G12,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
       <c r="J12" s="11"/>
@@ -5487,7 +5484,7 @@
         <v>17</v>
       </c>
       <c r="I13" t="e">
-        <f>VLOOKUP(G13,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
       <c r="J13" s="11"/>
@@ -5515,7 +5512,7 @@
         <v>17</v>
       </c>
       <c r="I14" t="e">
-        <f>VLOOKUP(G14,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
       <c r="J14" s="11"/>
@@ -5543,7 +5540,7 @@
         <v>17</v>
       </c>
       <c r="I15" t="e">
-        <f>VLOOKUP(G15,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
       <c r="J15" s="11"/>
@@ -5571,7 +5568,7 @@
         <v>17</v>
       </c>
       <c r="I16" t="e">
-        <f>VLOOKUP(G16,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
       <c r="J16" s="11"/>
@@ -5599,7 +5596,7 @@
         <v>17</v>
       </c>
       <c r="I17" t="e">
-        <f>VLOOKUP(G17,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
       <c r="J17" s="11"/>
@@ -5627,7 +5624,7 @@
         <v>17</v>
       </c>
       <c r="I18" t="e">
-        <f>VLOOKUP(G18,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
       <c r="J18" s="11"/>
@@ -5655,7 +5652,7 @@
         <v>17</v>
       </c>
       <c r="I19" t="e">
-        <f>VLOOKUP(G19,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
       <c r="J19" s="11"/>
@@ -5683,7 +5680,7 @@
         <v>17</v>
       </c>
       <c r="I20" t="e">
-        <f>VLOOKUP(G20,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
       <c r="J20" s="11"/>
@@ -5711,7 +5708,7 @@
         <v>17</v>
       </c>
       <c r="I21" t="e">
-        <f>VLOOKUP(G21,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
       <c r="J21" s="11"/>
@@ -5739,7 +5736,7 @@
         <v>17</v>
       </c>
       <c r="I22" t="e">
-        <f>VLOOKUP(G22,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
       <c r="J22" s="11"/>
@@ -5767,7 +5764,7 @@
         <v>17</v>
       </c>
       <c r="I23" t="str">
-        <f>VLOOKUP(G23,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>8956032244723773694</v>
       </c>
       <c r="J23" s="11"/>
@@ -5795,7 +5792,7 @@
         <v>17</v>
       </c>
       <c r="I24" t="e">
-        <f>VLOOKUP(G24,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
       <c r="J24" s="11"/>
@@ -5823,7 +5820,7 @@
         <v>17</v>
       </c>
       <c r="I25" t="e">
-        <f>VLOOKUP(G25,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
       <c r="J25" s="11"/>
@@ -5851,7 +5848,7 @@
         <v>17</v>
       </c>
       <c r="I26" t="e">
-        <f>VLOOKUP(G26,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
       <c r="J26" s="11"/>
@@ -5879,7 +5876,7 @@
         <v>17</v>
       </c>
       <c r="I27" t="e">
-        <f>VLOOKUP(G27,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
       <c r="J27" s="11"/>
@@ -5907,7 +5904,7 @@
         <v>17</v>
       </c>
       <c r="I28" t="e">
-        <f>VLOOKUP(G28,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
       <c r="J28" s="11"/>
@@ -5935,7 +5932,7 @@
         <v>17</v>
       </c>
       <c r="I29" t="e">
-        <f>VLOOKUP(G29,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
       <c r="J29" s="11"/>
@@ -5963,7 +5960,7 @@
         <v>17</v>
       </c>
       <c r="I30" t="e">
-        <f>VLOOKUP(G30,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
       <c r="J30" s="11"/>
@@ -5991,7 +5988,7 @@
         <v>17</v>
       </c>
       <c r="I31" t="str">
-        <f>VLOOKUP(G31,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>8956032244723774205</v>
       </c>
       <c r="J31" s="11"/>
@@ -6019,7 +6016,7 @@
         <v>17</v>
       </c>
       <c r="I32" t="e">
-        <f>VLOOKUP(G32,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
       <c r="J32" s="11"/>
@@ -6047,7 +6044,7 @@
         <v>17</v>
       </c>
       <c r="I33" t="e">
-        <f>VLOOKUP(G33,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
       <c r="J33" s="11"/>
@@ -6075,7 +6072,7 @@
         <v>17</v>
       </c>
       <c r="I34" t="e">
-        <f>VLOOKUP(G34,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
       <c r="J34" s="11"/>
@@ -6103,7 +6100,7 @@
         <v>17</v>
       </c>
       <c r="I35" t="e">
-        <f>VLOOKUP(G35,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
       <c r="J35" s="11"/>
@@ -6131,7 +6128,7 @@
         <v>17</v>
       </c>
       <c r="I36" t="e">
-        <f>VLOOKUP(G36,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
       <c r="J36" s="11"/>
@@ -6159,7 +6156,7 @@
         <v>17</v>
       </c>
       <c r="I37" t="e">
-        <f>VLOOKUP(G37,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
       <c r="J37" s="11"/>
@@ -6187,7 +6184,7 @@
         <v>17</v>
       </c>
       <c r="I38" t="e">
-        <f>VLOOKUP(G38,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
       <c r="J38" s="11"/>
@@ -6214,7 +6211,7 @@
         <v>17</v>
       </c>
       <c r="I39" t="e">
-        <f>VLOOKUP(G39,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
       <c r="J39" s="11"/>
@@ -6242,7 +6239,7 @@
         <v>17</v>
       </c>
       <c r="I40" t="e">
-        <f>VLOOKUP(G40,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
       <c r="J40" s="11"/>
@@ -6270,7 +6267,7 @@
         <v>17</v>
       </c>
       <c r="I41" t="e">
-        <f>VLOOKUP(G41,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
       <c r="J41" s="11"/>
@@ -6298,7 +6295,7 @@
         <v>17</v>
       </c>
       <c r="I42" t="e">
-        <f>VLOOKUP(G42,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
       <c r="J42" s="11"/>
@@ -6326,7 +6323,7 @@
         <v>17</v>
       </c>
       <c r="I43" t="e">
-        <f>VLOOKUP(G43,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
       <c r="J43" s="11"/>
@@ -6354,7 +6351,7 @@
         <v>17</v>
       </c>
       <c r="I44" t="e">
-        <f>VLOOKUP(G44,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
       <c r="J44" s="11"/>
@@ -6382,7 +6379,7 @@
         <v>17</v>
       </c>
       <c r="I45" t="e">
-        <f>VLOOKUP(G45,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
       <c r="J45" s="11"/>
@@ -6409,7 +6406,7 @@
         <v>17</v>
       </c>
       <c r="I46" t="str">
-        <f>VLOOKUP(G46,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>8956032244723774213</v>
       </c>
       <c r="J46" s="11"/>
@@ -6437,7 +6434,7 @@
         <v>17</v>
       </c>
       <c r="I47" t="e">
-        <f>VLOOKUP(G47,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
       <c r="J47" s="11"/>
@@ -6465,7 +6462,7 @@
         <v>17</v>
       </c>
       <c r="I48" t="e">
-        <f>VLOOKUP(G48,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
       <c r="J48" s="11"/>
@@ -6493,7 +6490,7 @@
         <v>17</v>
       </c>
       <c r="I49" t="e">
-        <f>VLOOKUP(G49,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
       <c r="J49" s="11"/>
@@ -6521,7 +6518,7 @@
         <v>17</v>
       </c>
       <c r="I50" t="e">
-        <f>VLOOKUP(G50,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
       <c r="J50" s="11"/>
@@ -6549,7 +6546,7 @@
         <v>17</v>
       </c>
       <c r="I51" t="e">
-        <f>VLOOKUP(G51,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
       <c r="J51" s="11"/>
@@ -6577,7 +6574,7 @@
         <v>17</v>
       </c>
       <c r="I52" t="e">
-        <f>VLOOKUP(G52,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
       <c r="J52" s="11"/>
@@ -6605,7 +6602,7 @@
         <v>17</v>
       </c>
       <c r="I53" t="e">
-        <f>VLOOKUP(G53,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
       <c r="J53" s="11"/>
@@ -6633,7 +6630,7 @@
         <v>17</v>
       </c>
       <c r="I54" t="e">
-        <f>VLOOKUP(G54,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
       <c r="J54" s="11"/>
@@ -6660,7 +6657,7 @@
         <v>17</v>
       </c>
       <c r="I55" t="e">
-        <f>VLOOKUP(G55,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
       <c r="J55" s="11"/>
@@ -6688,7 +6685,7 @@
         <v>17</v>
       </c>
       <c r="I56" t="e">
-        <f>VLOOKUP(G56,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
       <c r="J56" s="11"/>
@@ -6716,7 +6713,7 @@
         <v>173</v>
       </c>
       <c r="I57" t="str">
-        <f>VLOOKUP(G57,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>8956032254752139352</v>
       </c>
       <c r="J57" s="21" t="s">
@@ -6746,7 +6743,7 @@
         <v>173</v>
       </c>
       <c r="I58" t="e">
-        <f>VLOOKUP(G58,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
       <c r="J58" s="11"/>
@@ -6774,7 +6771,7 @@
         <v>181</v>
       </c>
       <c r="I59" t="str">
-        <f>VLOOKUP(G59,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>8956032234712739053</v>
       </c>
       <c r="J59" s="11"/>
@@ -6802,7 +6799,7 @@
         <v>185</v>
       </c>
       <c r="I60" t="str">
-        <f>VLOOKUP(G60,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>8956032254752139667</v>
       </c>
       <c r="J60" s="23" t="s">
@@ -6832,7 +6829,7 @@
         <v>185</v>
       </c>
       <c r="I61" t="str">
-        <f>VLOOKUP(G61,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>8956032201581692465</v>
       </c>
       <c r="J61" s="11"/>
@@ -6860,7 +6857,7 @@
         <v>185</v>
       </c>
       <c r="I62" t="str">
-        <f>VLOOKUP(G62,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>8956032234713494575</v>
       </c>
       <c r="J62" s="11"/>
@@ -6888,7 +6885,7 @@
         <v>185</v>
       </c>
       <c r="I63" t="str">
-        <f>VLOOKUP(G63,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>8956032254752139659</v>
       </c>
       <c r="J63" s="11"/>
@@ -6916,7 +6913,7 @@
         <v>185</v>
       </c>
       <c r="I64" t="str">
-        <f>VLOOKUP(G64,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>8956032254752139691</v>
       </c>
       <c r="J64" s="11"/>
@@ -6944,7 +6941,7 @@
         <v>185</v>
       </c>
       <c r="I65" t="str">
-        <f>VLOOKUP(G65,D:D,1,0)</f>
+        <f t="shared" si="0"/>
         <v>8956032186552547956</v>
       </c>
       <c r="J65" s="11"/>
@@ -6972,7 +6969,7 @@
         <v>185</v>
       </c>
       <c r="I66" t="str">
-        <f>VLOOKUP(G66,D:D,1,0)</f>
+        <f t="shared" ref="I66:I129" si="1">VLOOKUP(G66,D:D,1,0)</f>
         <v>8956032234712409533</v>
       </c>
       <c r="J66" s="11"/>
@@ -7000,7 +6997,7 @@
         <v>185</v>
       </c>
       <c r="I67" t="str">
-        <f>VLOOKUP(G67,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>8956030242988531296</v>
       </c>
       <c r="J67" s="11"/>
@@ -7028,7 +7025,7 @@
         <v>185</v>
       </c>
       <c r="I68" t="str">
-        <f>VLOOKUP(G68,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>8956032254752139709</v>
       </c>
       <c r="J68" s="11"/>
@@ -7056,7 +7053,7 @@
         <v>185</v>
       </c>
       <c r="I69" t="e">
-        <f>VLOOKUP(G69,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
       <c r="J69" s="11"/>
@@ -7084,7 +7081,7 @@
         <v>185</v>
       </c>
       <c r="I70" t="str">
-        <f>VLOOKUP(G70,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>8956032201581692358</v>
       </c>
       <c r="J70" s="11"/>
@@ -7112,7 +7109,7 @@
         <v>185</v>
       </c>
       <c r="I71" t="e">
-        <f>VLOOKUP(G71,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
       <c r="J71" s="11"/>
@@ -7140,7 +7137,7 @@
         <v>185</v>
       </c>
       <c r="I72" t="e">
-        <f>VLOOKUP(G72,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
       <c r="J72" s="11"/>
@@ -7168,7 +7165,7 @@
         <v>185</v>
       </c>
       <c r="I73" t="str">
-        <f>VLOOKUP(G73,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>8956030216921386232</v>
       </c>
       <c r="J73" s="11"/>
@@ -7196,7 +7193,7 @@
         <v>185</v>
       </c>
       <c r="I74" t="e">
-        <f>VLOOKUP(G74,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
       <c r="J74" s="11"/>
@@ -7224,7 +7221,7 @@
         <v>185</v>
       </c>
       <c r="I75" t="str">
-        <f>VLOOKUP(G75,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>8956032254752139675</v>
       </c>
       <c r="J75" s="23" t="s">
@@ -7253,7 +7250,7 @@
         <v>185</v>
       </c>
       <c r="I76" t="str">
-        <f>VLOOKUP(G76,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>8956032254752139642</v>
       </c>
       <c r="J76" s="23" t="s">
@@ -7283,7 +7280,7 @@
         <v>185</v>
       </c>
       <c r="I77" t="str">
-        <f>VLOOKUP(G77,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>8956032234713494674</v>
       </c>
       <c r="J77" s="11"/>
@@ -7311,7 +7308,7 @@
         <v>185</v>
       </c>
       <c r="I78" t="str">
-        <f>VLOOKUP(G78,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>8956032211667084610</v>
       </c>
       <c r="J78" s="11"/>
@@ -7339,7 +7336,7 @@
         <v>185</v>
       </c>
       <c r="I79" t="e">
-        <f>VLOOKUP(G79,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
       <c r="J79" s="11"/>
@@ -7366,7 +7363,7 @@
         <v>185</v>
       </c>
       <c r="I80" t="str">
-        <f>VLOOKUP(G80,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>8956030242988531270</v>
       </c>
       <c r="J80" s="11"/>
@@ -7394,7 +7391,7 @@
         <v>185</v>
       </c>
       <c r="I81" t="str">
-        <f>VLOOKUP(G81,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>8956032201581692317</v>
       </c>
       <c r="J81" s="11"/>
@@ -7422,7 +7419,7 @@
         <v>185</v>
       </c>
       <c r="I82" t="str">
-        <f>VLOOKUP(G82,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>8956032234712409848</v>
       </c>
       <c r="J82" s="11"/>
@@ -7450,7 +7447,7 @@
         <v>185</v>
       </c>
       <c r="I83" t="str">
-        <f>VLOOKUP(G83,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>8956032234713494583</v>
       </c>
       <c r="J83" s="11"/>
@@ -7478,7 +7475,7 @@
         <v>185</v>
       </c>
       <c r="I84" t="str">
-        <f>VLOOKUP(G84,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>8956032234713494641</v>
       </c>
       <c r="J84" s="11"/>
@@ -7506,7 +7503,7 @@
         <v>185</v>
       </c>
       <c r="I85" t="str">
-        <f>VLOOKUP(G85,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>8956032186552548103</v>
       </c>
       <c r="J85" s="11"/>
@@ -7534,7 +7531,7 @@
         <v>185</v>
       </c>
       <c r="I86" t="str">
-        <f>VLOOKUP(G86,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>8956032254752139717</v>
       </c>
       <c r="J86" s="11"/>
@@ -7562,7 +7559,7 @@
         <v>185</v>
       </c>
       <c r="I87" t="str">
-        <f>VLOOKUP(G87,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>8956030216926242836</v>
       </c>
       <c r="J87" s="11"/>
@@ -7590,7 +7587,7 @@
         <v>185</v>
       </c>
       <c r="I88" t="e">
-        <f>VLOOKUP(G88,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
       <c r="J88" s="11"/>
@@ -7618,7 +7615,7 @@
         <v>185</v>
       </c>
       <c r="I89" t="str">
-        <f>VLOOKUP(G89,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>8956030205813116468</v>
       </c>
       <c r="J89" s="11"/>
@@ -7646,7 +7643,7 @@
         <v>185</v>
       </c>
       <c r="I90" t="e">
-        <f>VLOOKUP(G90,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
       <c r="J90" s="11"/>
@@ -7674,7 +7671,7 @@
         <v>185</v>
       </c>
       <c r="I91" t="str">
-        <f>VLOOKUP(G91,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>8956032244722829851</v>
       </c>
       <c r="J91" s="11"/>
@@ -7702,7 +7699,7 @@
         <v>185</v>
       </c>
       <c r="I92" t="str">
-        <f>VLOOKUP(G92,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>8956030205813116252</v>
       </c>
       <c r="J92" s="11"/>
@@ -7730,7 +7727,7 @@
         <v>185</v>
       </c>
       <c r="I93" t="str">
-        <f>VLOOKUP(G93,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>8956030205813116419</v>
       </c>
       <c r="J93" s="11"/>
@@ -7758,7 +7755,7 @@
         <v>185</v>
       </c>
       <c r="I94" t="str">
-        <f>VLOOKUP(G94,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>8956030205813115940</v>
       </c>
       <c r="J94" s="11"/>
@@ -7786,7 +7783,7 @@
         <v>185</v>
       </c>
       <c r="I95" t="str">
-        <f>VLOOKUP(G95,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>8956030205813115890</v>
       </c>
       <c r="J95" s="11"/>
@@ -7814,7 +7811,7 @@
         <v>185</v>
       </c>
       <c r="I96" t="str">
-        <f>VLOOKUP(G96,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>8956030205813117011</v>
       </c>
       <c r="J96" s="11"/>
@@ -7842,7 +7839,7 @@
         <v>185</v>
       </c>
       <c r="I97" t="str">
-        <f>VLOOKUP(G97,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>8956030205813115296</v>
       </c>
       <c r="J97" s="11"/>
@@ -7870,7 +7867,7 @@
         <v>185</v>
       </c>
       <c r="I98" t="str">
-        <f>VLOOKUP(G98,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>8956032254752139857</v>
       </c>
       <c r="J98" s="11"/>
@@ -7898,7 +7895,7 @@
         <v>185</v>
       </c>
       <c r="I99" t="e">
-        <f>VLOOKUP(G99,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
       <c r="J99" s="11"/>
@@ -7926,7 +7923,7 @@
         <v>185</v>
       </c>
       <c r="I100" t="str">
-        <f>VLOOKUP(G100,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>8956030216926248023</v>
       </c>
       <c r="J100" s="11"/>
@@ -7954,7 +7951,7 @@
         <v>185</v>
       </c>
       <c r="I101" t="e">
-        <f>VLOOKUP(G101,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
       <c r="J101" s="11"/>
@@ -7982,7 +7979,7 @@
         <v>185</v>
       </c>
       <c r="I102" t="str">
-        <f>VLOOKUP(G102,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>8956030242988505472</v>
       </c>
       <c r="J102" s="11"/>
@@ -8010,7 +8007,7 @@
         <v>185</v>
       </c>
       <c r="I103" t="str">
-        <f>VLOOKUP(G103,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>8956032234713494450</v>
       </c>
       <c r="J103" s="11"/>
@@ -8038,7 +8035,7 @@
         <v>185</v>
       </c>
       <c r="I104" t="str">
-        <f>VLOOKUP(G104,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>8956030242988501067</v>
       </c>
       <c r="J104" s="11"/>
@@ -8066,7 +8063,7 @@
         <v>185</v>
       </c>
       <c r="I105" t="str">
-        <f>VLOOKUP(G105,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>8956030205813115932</v>
       </c>
       <c r="J105" s="11"/>
@@ -8094,7 +8091,7 @@
         <v>185</v>
       </c>
       <c r="I106" t="str">
-        <f>VLOOKUP(G106,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>8956030205813115817</v>
       </c>
       <c r="J106" s="11"/>
@@ -8122,7 +8119,7 @@
         <v>185</v>
       </c>
       <c r="I107" t="str">
-        <f>VLOOKUP(G107,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>8956030205813115387</v>
       </c>
       <c r="J107" s="11"/>
@@ -8150,7 +8147,7 @@
         <v>185</v>
       </c>
       <c r="I108" t="str">
-        <f>VLOOKUP(G108,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>8956032234712409780</v>
       </c>
       <c r="J108" s="11"/>
@@ -8178,7 +8175,7 @@
         <v>185</v>
       </c>
       <c r="I109" t="e">
-        <f>VLOOKUP(G109,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
       <c r="J109" s="11"/>
@@ -8206,7 +8203,7 @@
         <v>185</v>
       </c>
       <c r="I110" t="str">
-        <f>VLOOKUP(G110,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>8956032234712409665</v>
       </c>
       <c r="J110" s="11"/>
@@ -8234,7 +8231,7 @@
         <v>185</v>
       </c>
       <c r="I111" t="str">
-        <f>VLOOKUP(G111,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>8956030221943028234</v>
       </c>
       <c r="J111" s="11"/>
@@ -8262,7 +8259,7 @@
         <v>185</v>
       </c>
       <c r="I112" t="str">
-        <f>VLOOKUP(G112,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>8956030242988531106</v>
       </c>
       <c r="J112" s="11"/>
@@ -8290,7 +8287,7 @@
         <v>185</v>
       </c>
       <c r="I113" t="str">
-        <f>VLOOKUP(G113,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>8956030205813116948</v>
       </c>
       <c r="J113" s="11"/>
@@ -8318,7 +8315,7 @@
         <v>185</v>
       </c>
       <c r="I114" t="str">
-        <f>VLOOKUP(G114,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>8956030216921418175</v>
       </c>
       <c r="J114" s="11"/>
@@ -8346,7 +8343,7 @@
         <v>185</v>
       </c>
       <c r="I115" t="str">
-        <f>VLOOKUP(G115,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>8956032244730755833</v>
       </c>
       <c r="J115" s="11"/>
@@ -8374,7 +8371,7 @@
         <v>185</v>
       </c>
       <c r="I116" t="str">
-        <f>VLOOKUP(G116,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>8956030242988531114</v>
       </c>
       <c r="J116" s="11"/>
@@ -8402,7 +8399,7 @@
         <v>185</v>
       </c>
       <c r="I117" t="str">
-        <f>VLOOKUP(G117,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>8956030205813116336</v>
       </c>
       <c r="J117" s="11"/>
@@ -8430,7 +8427,7 @@
         <v>185</v>
       </c>
       <c r="I118" t="e">
-        <f>VLOOKUP(G118,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
       <c r="J118" s="11"/>
@@ -8458,7 +8455,7 @@
         <v>185</v>
       </c>
       <c r="I119" t="str">
-        <f>VLOOKUP(G119,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>8956030205813115247</v>
       </c>
       <c r="J119" s="11"/>
@@ -8486,7 +8483,7 @@
         <v>185</v>
       </c>
       <c r="I120" t="str">
-        <f>VLOOKUP(G120,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>8956030216926247421</v>
       </c>
       <c r="J120" s="11"/>
@@ -8514,7 +8511,7 @@
         <v>185</v>
       </c>
       <c r="I121" t="str">
-        <f>VLOOKUP(G121,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>8956030205813116989</v>
       </c>
       <c r="J121" s="11"/>
@@ -8542,7 +8539,7 @@
         <v>185</v>
       </c>
       <c r="I122" t="str">
-        <f>VLOOKUP(G122,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>8956030216926247454</v>
       </c>
       <c r="J122" s="11"/>
@@ -8570,7 +8567,7 @@
         <v>185</v>
       </c>
       <c r="I123" t="str">
-        <f>VLOOKUP(G123,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>8956030242988501075</v>
       </c>
       <c r="J123" s="11"/>
@@ -8598,7 +8595,7 @@
         <v>185</v>
       </c>
       <c r="I124" t="str">
-        <f>VLOOKUP(G124,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>8956030205813116351</v>
       </c>
       <c r="J124" s="11"/>
@@ -8626,7 +8623,7 @@
         <v>185</v>
       </c>
       <c r="I125" t="e">
-        <f>VLOOKUP(G125,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
       <c r="J125" s="11"/>
@@ -8654,7 +8651,7 @@
         <v>185</v>
       </c>
       <c r="I126" t="str">
-        <f>VLOOKUP(G126,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>8956030205813116385</v>
       </c>
       <c r="J126" s="11"/>
@@ -8682,7 +8679,7 @@
         <v>185</v>
       </c>
       <c r="I127" t="str">
-        <f>VLOOKUP(G127,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>8956030205813115882</v>
       </c>
       <c r="J127" s="11"/>
@@ -8710,7 +8707,7 @@
         <v>185</v>
       </c>
       <c r="I128" t="str">
-        <f>VLOOKUP(G128,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>8956032254752139865</v>
       </c>
       <c r="J128" s="23" t="s">
@@ -8740,7 +8737,7 @@
         <v>185</v>
       </c>
       <c r="I129" t="str">
-        <f>VLOOKUP(G129,D:D,1,0)</f>
+        <f t="shared" si="1"/>
         <v>8956030205813117003</v>
       </c>
       <c r="J129" s="11"/>
@@ -8768,7 +8765,7 @@
         <v>185</v>
       </c>
       <c r="I130" t="str">
-        <f>VLOOKUP(G130,D:D,1,0)</f>
+        <f t="shared" ref="I130:I193" si="2">VLOOKUP(G130,D:D,1,0)</f>
         <v>8956030205813115999</v>
       </c>
       <c r="J130" s="11"/>
@@ -8796,7 +8793,7 @@
         <v>185</v>
       </c>
       <c r="I131" t="str">
-        <f>VLOOKUP(G131,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>8956032254752139758</v>
       </c>
       <c r="J131" s="11"/>
@@ -8824,7 +8821,7 @@
         <v>185</v>
       </c>
       <c r="I132" t="str">
-        <f>VLOOKUP(G132,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>8956030205813115130</v>
       </c>
       <c r="J132" s="11"/>
@@ -8852,7 +8849,7 @@
         <v>185</v>
       </c>
       <c r="I133" t="str">
-        <f>VLOOKUP(G133,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>8956030242988532336</v>
       </c>
       <c r="J133" s="11"/>
@@ -8880,7 +8877,7 @@
         <v>185</v>
       </c>
       <c r="I134" t="str">
-        <f>VLOOKUP(G134,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>8956030205813116476</v>
       </c>
       <c r="J134" s="11"/>
@@ -8908,7 +8905,7 @@
         <v>185</v>
       </c>
       <c r="I135" t="str">
-        <f>VLOOKUP(G135,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>8956030205813115692</v>
       </c>
       <c r="J135" s="11"/>
@@ -8936,7 +8933,7 @@
         <v>185</v>
       </c>
       <c r="I136" t="str">
-        <f>VLOOKUP(G136,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>8956030205813115213</v>
       </c>
       <c r="J136" s="11"/>
@@ -8964,7 +8961,7 @@
         <v>185</v>
       </c>
       <c r="I137" t="e">
-        <f>VLOOKUP(G137,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
       <c r="J137" s="11"/>
@@ -8992,7 +8989,7 @@
         <v>185</v>
       </c>
       <c r="I138" t="str">
-        <f>VLOOKUP(G138,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>8956030205813115783</v>
       </c>
       <c r="J138" s="11"/>
@@ -9020,7 +9017,7 @@
         <v>185</v>
       </c>
       <c r="I139" t="e">
-        <f>VLOOKUP(G139,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
       <c r="J139" s="11"/>
@@ -9048,7 +9045,7 @@
         <v>185</v>
       </c>
       <c r="I140" t="str">
-        <f>VLOOKUP(G140,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>8956030205813116245</v>
       </c>
       <c r="J140" s="11"/>
@@ -9076,7 +9073,7 @@
         <v>185</v>
       </c>
       <c r="I141" t="str">
-        <f>VLOOKUP(G141,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>8956030221943028044</v>
       </c>
       <c r="J141" s="11"/>
@@ -9104,7 +9101,7 @@
         <v>185</v>
       </c>
       <c r="I142" t="str">
-        <f>VLOOKUP(G142,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>8956030205813115593</v>
       </c>
       <c r="J142" s="11"/>
@@ -9132,7 +9129,7 @@
         <v>185</v>
       </c>
       <c r="I143" t="e">
-        <f>VLOOKUP(G143,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
       <c r="J143" s="11"/>
@@ -9160,7 +9157,7 @@
         <v>185</v>
       </c>
       <c r="I144" t="e">
-        <f>VLOOKUP(G144,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
       <c r="J144" s="11"/>
@@ -9188,7 +9185,7 @@
         <v>185</v>
       </c>
       <c r="I145" t="e">
-        <f>VLOOKUP(G145,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
       <c r="J145" s="11"/>
@@ -9216,7 +9213,7 @@
         <v>185</v>
       </c>
       <c r="I146" t="str">
-        <f>VLOOKUP(G146,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>8956030242988501125</v>
       </c>
       <c r="J146" s="11"/>
@@ -9244,7 +9241,7 @@
         <v>185</v>
       </c>
       <c r="I147" t="str">
-        <f>VLOOKUP(G147,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>8956030205813115205</v>
       </c>
       <c r="J147" s="11"/>
@@ -9272,7 +9269,7 @@
         <v>185</v>
       </c>
       <c r="I148" t="e">
-        <f>VLOOKUP(G148,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
       <c r="J148" s="11"/>
@@ -9300,7 +9297,7 @@
         <v>185</v>
       </c>
       <c r="I149" t="str">
-        <f>VLOOKUP(G149,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>8956030205813116302</v>
       </c>
       <c r="J149" s="11"/>
@@ -9328,7 +9325,7 @@
         <v>185</v>
       </c>
       <c r="I150" t="str">
-        <f>VLOOKUP(G150,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>8956032254752139766</v>
       </c>
       <c r="J150" s="11"/>
@@ -9356,7 +9353,7 @@
         <v>185</v>
       </c>
       <c r="I151" t="str">
-        <f>VLOOKUP(G151,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>8956032234712409699</v>
       </c>
       <c r="J151" s="11"/>
@@ -9384,7 +9381,7 @@
         <v>185</v>
       </c>
       <c r="I152" t="e">
-        <f>VLOOKUP(G152,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
       <c r="J152" s="11"/>
@@ -9412,7 +9409,7 @@
         <v>185</v>
       </c>
       <c r="I153" t="str">
-        <f>VLOOKUP(G153,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>8956030205813116484</v>
       </c>
       <c r="J153" s="11"/>
@@ -9440,7 +9437,7 @@
         <v>185</v>
       </c>
       <c r="I154" t="e">
-        <f>VLOOKUP(G154,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
       <c r="J154" s="11"/>
@@ -9468,7 +9465,7 @@
         <v>185</v>
       </c>
       <c r="I155" t="str">
-        <f>VLOOKUP(G155,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>8956032254752139782</v>
       </c>
       <c r="J155" s="11"/>
@@ -9496,7 +9493,7 @@
         <v>185</v>
       </c>
       <c r="I156" t="str">
-        <f>VLOOKUP(G156,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>8956030216926248130</v>
       </c>
       <c r="J156" s="11"/>
@@ -9524,7 +9521,7 @@
         <v>185</v>
       </c>
       <c r="I157" t="str">
-        <f>VLOOKUP(G157,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>8956030205813115775</v>
       </c>
       <c r="J157" s="11"/>
@@ -9552,7 +9549,7 @@
         <v>185</v>
       </c>
       <c r="I158" t="str">
-        <f>VLOOKUP(G158,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>8956030205813115627</v>
       </c>
       <c r="J158" s="11"/>
@@ -9580,7 +9577,7 @@
         <v>185</v>
       </c>
       <c r="I159" t="str">
-        <f>VLOOKUP(G159,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>8956030205813115502</v>
       </c>
       <c r="J159" s="11"/>
@@ -9608,7 +9605,7 @@
         <v>185</v>
       </c>
       <c r="I160" t="e">
-        <f>VLOOKUP(G160,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
       <c r="J160" s="11"/>
@@ -9636,7 +9633,7 @@
         <v>185</v>
       </c>
       <c r="I161" t="str">
-        <f>VLOOKUP(G161,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>8956030205813115528</v>
       </c>
       <c r="J161" s="11"/>
@@ -9664,7 +9661,7 @@
         <v>185</v>
       </c>
       <c r="I162" t="str">
-        <f>VLOOKUP(G162,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>8956030205813115312</v>
       </c>
       <c r="J162" s="11"/>
@@ -9692,7 +9689,7 @@
         <v>185</v>
       </c>
       <c r="I163" t="str">
-        <f>VLOOKUP(G163,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>8956030216921417722</v>
       </c>
       <c r="J163" s="11"/>
@@ -9720,7 +9717,7 @@
         <v>185</v>
       </c>
       <c r="I164" t="str">
-        <f>VLOOKUP(G164,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>8956032254752139774</v>
       </c>
       <c r="J164" s="21" t="s">
@@ -9750,7 +9747,7 @@
         <v>185</v>
       </c>
       <c r="I165" t="str">
-        <f>VLOOKUP(G165,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>8956030205813115270</v>
       </c>
       <c r="J165" s="11"/>
@@ -9778,7 +9775,7 @@
         <v>185</v>
       </c>
       <c r="I166" t="str">
-        <f>VLOOKUP(G166,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>8956032234713494708</v>
       </c>
       <c r="J166" s="11"/>
@@ -9806,7 +9803,7 @@
         <v>185</v>
       </c>
       <c r="I167" t="str">
-        <f>VLOOKUP(G167,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>8956030205813115486</v>
       </c>
       <c r="J167" s="11"/>
@@ -9834,7 +9831,7 @@
         <v>185</v>
       </c>
       <c r="I168" t="str">
-        <f>VLOOKUP(G168,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>8956030205813115825</v>
       </c>
       <c r="J168" s="11"/>
@@ -9862,7 +9859,7 @@
         <v>185</v>
       </c>
       <c r="I169" t="str">
-        <f>VLOOKUP(G169,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>8956032254752139733</v>
       </c>
       <c r="J169" s="23" t="s">
@@ -9892,7 +9889,7 @@
         <v>185</v>
       </c>
       <c r="I170" t="str">
-        <f>VLOOKUP(G170,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>8956032254752139741</v>
       </c>
       <c r="J170" s="11"/>
@@ -9920,7 +9917,7 @@
         <v>185</v>
       </c>
       <c r="I171" t="str">
-        <f>VLOOKUP(G171,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>8956030205813115569</v>
       </c>
       <c r="J171" s="11"/>
@@ -9948,7 +9945,7 @@
         <v>185</v>
       </c>
       <c r="I172" t="str">
-        <f>VLOOKUP(G172,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>8956030242988531122</v>
       </c>
       <c r="J172" s="11"/>
@@ -9976,7 +9973,7 @@
         <v>185</v>
       </c>
       <c r="I173" t="e">
-        <f>VLOOKUP(G173,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
       <c r="J173" s="11"/>
@@ -10004,7 +10001,7 @@
         <v>185</v>
       </c>
       <c r="I174" t="str">
-        <f>VLOOKUP(G174,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>8956030216926247413</v>
       </c>
       <c r="J174" s="11"/>
@@ -10032,7 +10029,7 @@
         <v>185</v>
       </c>
       <c r="I175" t="str">
-        <f>VLOOKUP(G175,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>8956030221943028911</v>
       </c>
       <c r="J175" s="11"/>
@@ -10060,7 +10057,7 @@
         <v>185</v>
       </c>
       <c r="I176" t="str">
-        <f>VLOOKUP(G176,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>8956030216926241564</v>
       </c>
       <c r="J176" s="11"/>
@@ -10088,7 +10085,7 @@
         <v>185</v>
       </c>
       <c r="I177" t="str">
-        <f>VLOOKUP(G177,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>8956032234713494682</v>
       </c>
       <c r="J177" s="11"/>
@@ -10116,7 +10113,7 @@
         <v>185</v>
       </c>
       <c r="I178" t="str">
-        <f>VLOOKUP(G178,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>8956030205813115411</v>
       </c>
       <c r="J178" s="11"/>
@@ -10144,7 +10141,7 @@
         <v>185</v>
       </c>
       <c r="I179" t="str">
-        <f>VLOOKUP(G179,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>8956030216921418191</v>
       </c>
       <c r="J179" s="11"/>
@@ -10172,7 +10169,7 @@
         <v>185</v>
       </c>
       <c r="I180" t="str">
-        <f>VLOOKUP(G180,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>8956030205813116997</v>
       </c>
       <c r="J180" s="11"/>
@@ -10200,7 +10197,7 @@
         <v>185</v>
       </c>
       <c r="I181" t="e">
-        <f>VLOOKUP(G181,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
       <c r="J181" s="11"/>
@@ -10228,7 +10225,7 @@
         <v>185</v>
       </c>
       <c r="I182" t="str">
-        <f>VLOOKUP(G182,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>8956030205813115536</v>
       </c>
       <c r="J182" s="11"/>
@@ -10256,7 +10253,7 @@
         <v>185</v>
       </c>
       <c r="I183" t="e">
-        <f>VLOOKUP(G183,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
       <c r="J183" s="11"/>
@@ -10284,7 +10281,7 @@
         <v>185</v>
       </c>
       <c r="I184" t="e">
-        <f>VLOOKUP(G184,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
       <c r="J184" s="11"/>
@@ -10312,7 +10309,7 @@
         <v>185</v>
       </c>
       <c r="I185" t="e">
-        <f>VLOOKUP(G185,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
       <c r="J185" s="11"/>
@@ -10340,7 +10337,7 @@
         <v>185</v>
       </c>
       <c r="I186" t="str">
-        <f>VLOOKUP(G186,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>8956030242988531098</v>
       </c>
       <c r="J186" s="11"/>
@@ -10367,7 +10364,7 @@
         <v>185</v>
       </c>
       <c r="I187" t="str">
-        <f>VLOOKUP(G187,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>8956030205813115510</v>
       </c>
       <c r="J187" s="11"/>
@@ -10395,7 +10392,7 @@
         <v>185</v>
       </c>
       <c r="I188" t="str">
-        <f>VLOOKUP(G188,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>8956032254752139808</v>
       </c>
       <c r="J188" s="11"/>
@@ -10423,7 +10420,7 @@
         <v>185</v>
       </c>
       <c r="I189" t="e">
-        <f>VLOOKUP(G189,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
       <c r="J189" s="11"/>
@@ -10451,7 +10448,7 @@
         <v>185</v>
       </c>
       <c r="I190" t="str">
-        <f>VLOOKUP(G190,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>8956030205813115122</v>
       </c>
       <c r="J190" s="11"/>
@@ -10479,7 +10476,7 @@
         <v>185</v>
       </c>
       <c r="I191" t="str">
-        <f>VLOOKUP(G191,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>8956030205813116328</v>
       </c>
       <c r="J191" s="11"/>
@@ -10507,7 +10504,7 @@
         <v>185</v>
       </c>
       <c r="I192" t="str">
-        <f>VLOOKUP(G192,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>8956030205813115650</v>
       </c>
       <c r="J192" s="11"/>
@@ -10535,7 +10532,7 @@
         <v>185</v>
       </c>
       <c r="I193" t="str">
-        <f>VLOOKUP(G193,D:D,1,0)</f>
+        <f t="shared" si="2"/>
         <v>8956032234713494831</v>
       </c>
       <c r="J193" s="11"/>
@@ -10563,7 +10560,7 @@
         <v>185</v>
       </c>
       <c r="I194" t="str">
-        <f>VLOOKUP(G194,D:D,1,0)</f>
+        <f t="shared" ref="I194:I257" si="3">VLOOKUP(G194,D:D,1,0)</f>
         <v>8956030216921386307</v>
       </c>
       <c r="J194" s="11"/>
@@ -10591,7 +10588,7 @@
         <v>185</v>
       </c>
       <c r="I195" t="str">
-        <f>VLOOKUP(G195,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>8956030216921418183</v>
       </c>
       <c r="J195" s="11"/>
@@ -10619,7 +10616,7 @@
         <v>185</v>
       </c>
       <c r="I196" t="str">
-        <f>VLOOKUP(G196,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>8956030221943029026</v>
       </c>
       <c r="J196" s="11"/>
@@ -10647,7 +10644,7 @@
         <v>185</v>
       </c>
       <c r="I197" t="str">
-        <f>VLOOKUP(G197,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>8956030205813116898</v>
       </c>
       <c r="J197" s="11"/>
@@ -10675,7 +10672,7 @@
         <v>185</v>
       </c>
       <c r="I198" t="str">
-        <f>VLOOKUP(G198,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>8956030205813116369</v>
       </c>
       <c r="J198" s="11"/>
@@ -10703,7 +10700,7 @@
         <v>185</v>
       </c>
       <c r="I199" t="str">
-        <f>VLOOKUP(G199,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>8956030205813115395</v>
       </c>
       <c r="J199" s="11"/>
@@ -10731,7 +10728,7 @@
         <v>185</v>
       </c>
       <c r="I200" t="str">
-        <f>VLOOKUP(G200,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>8956032254752139816</v>
       </c>
       <c r="J200" s="11"/>
@@ -10759,7 +10756,7 @@
         <v>185</v>
       </c>
       <c r="I201" t="str">
-        <f>VLOOKUP(G201,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>8956030205813115221</v>
       </c>
       <c r="J201" s="11"/>
@@ -10787,7 +10784,7 @@
         <v>185</v>
       </c>
       <c r="I202" t="str">
-        <f>VLOOKUP(G202,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>8956030205813116435</v>
       </c>
       <c r="J202" s="11"/>
@@ -10815,7 +10812,7 @@
         <v>185</v>
       </c>
       <c r="I203" t="e">
-        <f>VLOOKUP(G203,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>#N/A</v>
       </c>
       <c r="J203" s="11"/>
@@ -10843,7 +10840,7 @@
         <v>185</v>
       </c>
       <c r="I204" t="str">
-        <f>VLOOKUP(G204,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>8956030216921418720</v>
       </c>
       <c r="J204" s="11"/>
@@ -10871,7 +10868,7 @@
         <v>185</v>
       </c>
       <c r="I205" t="str">
-        <f>VLOOKUP(G205,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>8956032234712409855</v>
       </c>
       <c r="J205" s="11"/>
@@ -10899,7 +10896,7 @@
         <v>185</v>
       </c>
       <c r="I206" t="str">
-        <f>VLOOKUP(G206,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>8956030216926247439</v>
       </c>
       <c r="J206" s="11"/>
@@ -10927,7 +10924,7 @@
         <v>185</v>
       </c>
       <c r="I207" t="str">
-        <f>VLOOKUP(G207,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>8956030205813115288</v>
       </c>
       <c r="J207" s="11"/>
@@ -10955,7 +10952,7 @@
         <v>185</v>
       </c>
       <c r="I208" t="e">
-        <f>VLOOKUP(G208,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>#N/A</v>
       </c>
       <c r="J208" s="11"/>
@@ -10983,7 +10980,7 @@
         <v>185</v>
       </c>
       <c r="I209" t="str">
-        <f>VLOOKUP(G209,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>8956032254752139832</v>
       </c>
       <c r="J209" s="21" t="s">
@@ -11013,7 +11010,7 @@
         <v>185</v>
       </c>
       <c r="I210" t="str">
-        <f>VLOOKUP(G210,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>8956030205813115668</v>
       </c>
       <c r="J210" s="11"/>
@@ -11041,7 +11038,7 @@
         <v>185</v>
       </c>
       <c r="I211" t="str">
-        <f>VLOOKUP(G211,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>8956030216921386463</v>
       </c>
       <c r="J211" s="11"/>
@@ -11069,7 +11066,7 @@
         <v>185</v>
       </c>
       <c r="I212" t="str">
-        <f>VLOOKUP(G212,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>8956030205813116906</v>
       </c>
       <c r="J212" s="11"/>
@@ -11097,7 +11094,7 @@
         <v>185</v>
       </c>
       <c r="I213" t="str">
-        <f>VLOOKUP(G213,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>8956030205813115866</v>
       </c>
       <c r="J213" s="11"/>
@@ -11125,7 +11122,7 @@
         <v>185</v>
       </c>
       <c r="I214" t="str">
-        <f>VLOOKUP(G214,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>8956030205813117078</v>
       </c>
       <c r="J214" s="11"/>
@@ -11153,7 +11150,7 @@
         <v>185</v>
       </c>
       <c r="I215" t="str">
-        <f>VLOOKUP(G215,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>8956032254752139840</v>
       </c>
       <c r="J215" s="23" t="s">
@@ -11183,7 +11180,7 @@
         <v>185</v>
       </c>
       <c r="I216" t="e">
-        <f>VLOOKUP(G216,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>#N/A</v>
       </c>
       <c r="J216" s="23" t="s">
@@ -11213,7 +11210,7 @@
         <v>185</v>
       </c>
       <c r="I217" t="str">
-        <f>VLOOKUP(G217,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>8956032254752139873</v>
       </c>
       <c r="J217" s="23" t="s">
@@ -11243,7 +11240,7 @@
         <v>185</v>
       </c>
       <c r="I218" t="str">
-        <f>VLOOKUP(G218,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>8956032204612146386</v>
       </c>
       <c r="J218" s="11"/>
@@ -11271,7 +11268,7 @@
         <v>185</v>
       </c>
       <c r="I219" t="str">
-        <f>VLOOKUP(G219,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>8956032234712409723</v>
       </c>
       <c r="J219" s="11"/>
@@ -11299,7 +11296,7 @@
         <v>185</v>
       </c>
       <c r="I220" t="e">
-        <f>VLOOKUP(G220,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>#N/A</v>
       </c>
       <c r="J220" s="11"/>
@@ -11327,7 +11324,7 @@
         <v>185</v>
       </c>
       <c r="I221" t="e">
-        <f>VLOOKUP(G221,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>#N/A</v>
       </c>
       <c r="J221" s="23" t="s">
@@ -11357,7 +11354,7 @@
         <v>185</v>
       </c>
       <c r="I222" t="str">
-        <f>VLOOKUP(G222,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>8956032254752139287</v>
       </c>
       <c r="J222" s="23" t="s">
@@ -11387,7 +11384,7 @@
         <v>185</v>
       </c>
       <c r="I223" t="str">
-        <f>VLOOKUP(G223,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>8956030221943028903</v>
       </c>
       <c r="J223" s="11"/>
@@ -11415,7 +11412,7 @@
         <v>185</v>
       </c>
       <c r="I224" t="str">
-        <f>VLOOKUP(G224,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>8956032234712409772</v>
       </c>
       <c r="J224" s="11"/>
@@ -11443,7 +11440,7 @@
         <v>185</v>
       </c>
       <c r="I225" t="str">
-        <f>VLOOKUP(G225,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>8956032201581696193</v>
       </c>
       <c r="J225" s="11"/>
@@ -11471,7 +11468,7 @@
         <v>185</v>
       </c>
       <c r="I226" t="e">
-        <f>VLOOKUP(G226,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>#N/A</v>
       </c>
       <c r="J226" s="11"/>
@@ -11499,7 +11496,7 @@
         <v>185</v>
       </c>
       <c r="I227" t="str">
-        <f>VLOOKUP(G227,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>8956034203014350669</v>
       </c>
       <c r="J227" s="11"/>
@@ -11527,7 +11524,7 @@
         <v>185</v>
       </c>
       <c r="I228" t="str">
-        <f>VLOOKUP(G228,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>8956030185729589786</v>
       </c>
       <c r="J228" s="11"/>
@@ -11555,7 +11552,7 @@
         <v>185</v>
       </c>
       <c r="I229" t="str">
-        <f>VLOOKUP(G229,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>8956034203014348119</v>
       </c>
       <c r="J229" s="11"/>
@@ -11583,7 +11580,7 @@
         <v>185</v>
       </c>
       <c r="I230" t="str">
-        <f>VLOOKUP(G230,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>8956032254752139386</v>
       </c>
       <c r="J230" s="11"/>
@@ -11611,7 +11608,7 @@
         <v>185</v>
       </c>
       <c r="I231" t="str">
-        <f>VLOOKUP(G231,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>8956034203014361393</v>
       </c>
       <c r="J231" s="11"/>
@@ -11639,7 +11636,7 @@
         <v>185</v>
       </c>
       <c r="I232" t="str">
-        <f>VLOOKUP(G232,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>8956032254752139360</v>
       </c>
       <c r="J232" s="11"/>
@@ -11667,7 +11664,7 @@
         <v>185</v>
       </c>
       <c r="I233" t="str">
-        <f>VLOOKUP(G233,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>8956032201581696771</v>
       </c>
       <c r="J233" s="11"/>
@@ -11695,7 +11692,7 @@
         <v>185</v>
       </c>
       <c r="I234" t="str">
-        <f>VLOOKUP(G234,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>8956032201581696763</v>
       </c>
       <c r="J234" s="11"/>
@@ -11723,7 +11720,7 @@
         <v>185</v>
       </c>
       <c r="I235" t="str">
-        <f>VLOOKUP(G235,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>8956032204612146527</v>
       </c>
       <c r="J235" s="11"/>
@@ -11751,7 +11748,7 @@
         <v>185</v>
       </c>
       <c r="I236" t="str">
-        <f>VLOOKUP(G236,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>8956034203014351048</v>
       </c>
       <c r="J236" s="11"/>
@@ -11779,7 +11776,7 @@
         <v>185</v>
       </c>
       <c r="I237" t="str">
-        <f>VLOOKUP(G237,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>8956030242988505480</v>
       </c>
       <c r="J237" s="11"/>
@@ -11807,7 +11804,7 @@
         <v>185</v>
       </c>
       <c r="I238" t="str">
-        <f>VLOOKUP(G238,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>8956032254752139329</v>
       </c>
       <c r="J238" s="11"/>
@@ -11835,7 +11832,7 @@
         <v>185</v>
       </c>
       <c r="I239" t="str">
-        <f>VLOOKUP(G239,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>8956034203014361112</v>
       </c>
       <c r="J239" s="11"/>
@@ -11863,7 +11860,7 @@
         <v>185</v>
       </c>
       <c r="I240" t="str">
-        <f>VLOOKUP(G240,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>8956034203014361351</v>
       </c>
       <c r="J240" s="11"/>
@@ -11891,7 +11888,7 @@
         <v>185</v>
       </c>
       <c r="I241" t="str">
-        <f>VLOOKUP(G241,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>8956030185729635522</v>
       </c>
       <c r="J241" s="11"/>
@@ -11919,7 +11916,7 @@
         <v>185</v>
       </c>
       <c r="I242" t="str">
-        <f>VLOOKUP(G242,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>8956034203014348416</v>
       </c>
       <c r="J242" s="11"/>
@@ -11945,7 +11942,7 @@
         <v>185</v>
       </c>
       <c r="I243" t="str">
-        <f>VLOOKUP(G243,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>8956030185729586923</v>
       </c>
       <c r="J243" s="11"/>
@@ -11973,7 +11970,7 @@
         <v>185</v>
       </c>
       <c r="I244" t="str">
-        <f>VLOOKUP(G244,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>8956032254752139311</v>
       </c>
       <c r="J244" s="23" t="s">
@@ -12003,7 +12000,7 @@
         <v>185</v>
       </c>
       <c r="I245" t="str">
-        <f>VLOOKUP(G245,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>8956034203014361252</v>
       </c>
       <c r="J245" s="11"/>
@@ -12031,7 +12028,7 @@
         <v>185</v>
       </c>
       <c r="I246" t="str">
-        <f>VLOOKUP(G246,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>8956032254752139378</v>
       </c>
       <c r="J246" s="23" t="s">
@@ -12061,7 +12058,7 @@
         <v>185</v>
       </c>
       <c r="I247" t="str">
-        <f>VLOOKUP(G247,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>8956034203014361450</v>
       </c>
       <c r="J247" s="11"/>
@@ -12089,7 +12086,7 @@
         <v>185</v>
       </c>
       <c r="I248" t="e">
-        <f>VLOOKUP(G248,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>#N/A</v>
       </c>
       <c r="J248" s="11"/>
@@ -12117,7 +12114,7 @@
         <v>185</v>
       </c>
       <c r="I249" t="str">
-        <f>VLOOKUP(G249,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>8956032254752139337</v>
       </c>
       <c r="J249" s="23" t="s">
@@ -12147,7 +12144,7 @@
         <v>185</v>
       </c>
       <c r="I250" t="str">
-        <f>VLOOKUP(G250,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>8956032254752139345</v>
       </c>
       <c r="J250" s="11"/>
@@ -12175,7 +12172,7 @@
         <v>185</v>
       </c>
       <c r="I251" t="str">
-        <f>VLOOKUP(G251,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>8956034203014351030</v>
       </c>
       <c r="J251" s="11"/>
@@ -12203,7 +12200,7 @@
         <v>185</v>
       </c>
       <c r="I252" t="str">
-        <f>VLOOKUP(G252,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>8956032186552547550</v>
       </c>
       <c r="J252" s="11"/>
@@ -12231,7 +12228,7 @@
         <v>185</v>
       </c>
       <c r="I253" t="str">
-        <f>VLOOKUP(G253,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>8956032254752139402</v>
       </c>
       <c r="J253" s="11"/>
@@ -12259,7 +12256,7 @@
         <v>185</v>
       </c>
       <c r="I254" t="str">
-        <f>VLOOKUP(G254,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>8956032204612146394</v>
       </c>
       <c r="J254" s="11"/>
@@ -12287,7 +12284,7 @@
         <v>185</v>
       </c>
       <c r="I255" t="e">
-        <f>VLOOKUP(G255,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>#N/A</v>
       </c>
       <c r="J255" s="11"/>
@@ -12315,7 +12312,7 @@
         <v>185</v>
       </c>
       <c r="I256" t="e">
-        <f>VLOOKUP(G256,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>#N/A</v>
       </c>
       <c r="J256" s="11"/>
@@ -12343,7 +12340,7 @@
         <v>185</v>
       </c>
       <c r="I257" t="str">
-        <f>VLOOKUP(G257,D:D,1,0)</f>
+        <f t="shared" si="3"/>
         <v>8956034203014350792</v>
       </c>
       <c r="J257" s="11"/>
@@ -12371,7 +12368,7 @@
         <v>185</v>
       </c>
       <c r="I258" t="str">
-        <f>VLOOKUP(G258,D:D,1,0)</f>
+        <f t="shared" ref="I258:I321" si="4">VLOOKUP(G258,D:D,1,0)</f>
         <v>8956030185729635837</v>
       </c>
       <c r="J258" s="11"/>
@@ -12382,7 +12379,9 @@
       <c r="A259" s="9">
         <v>2942</v>
       </c>
-      <c r="B259" s="3"/>
+      <c r="B259" s="3" t="s">
+        <v>18</v>
+      </c>
       <c r="C259" s="3"/>
       <c r="D259" s="3" t="s">
         <v>709</v>
@@ -12395,7 +12394,7 @@
         <v>185</v>
       </c>
       <c r="I259" t="str">
-        <f>VLOOKUP(G259,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>8956032201581696821</v>
       </c>
       <c r="J259" s="11"/>
@@ -12423,7 +12422,7 @@
         <v>185</v>
       </c>
       <c r="I260" t="str">
-        <f>VLOOKUP(G260,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>8956032201581692374</v>
       </c>
       <c r="J260" s="11"/>
@@ -12451,7 +12450,7 @@
         <v>185</v>
       </c>
       <c r="I261" t="str">
-        <f>VLOOKUP(G261,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>8956034203014361484</v>
       </c>
       <c r="J261" s="11"/>
@@ -12479,7 +12478,7 @@
         <v>185</v>
       </c>
       <c r="I262" t="e">
-        <f>VLOOKUP(G262,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
       <c r="J262" s="11"/>
@@ -12507,7 +12506,7 @@
         <v>185</v>
       </c>
       <c r="I263" t="str">
-        <f>VLOOKUP(G263,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>8956030185729589497</v>
       </c>
       <c r="J263" s="11"/>
@@ -12535,7 +12534,7 @@
         <v>185</v>
       </c>
       <c r="I264" t="str">
-        <f>VLOOKUP(G264,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>8956030216921386265</v>
       </c>
       <c r="J264" s="11"/>
@@ -12563,7 +12562,7 @@
         <v>185</v>
       </c>
       <c r="I265" t="str">
-        <f>VLOOKUP(G265,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>8956034203014348333</v>
       </c>
       <c r="J265" s="11"/>
@@ -12591,7 +12590,7 @@
         <v>185</v>
       </c>
       <c r="I266" t="e">
-        <f>VLOOKUP(G266,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
       <c r="J266" s="11"/>
@@ -12619,7 +12618,7 @@
         <v>185</v>
       </c>
       <c r="I267" t="e">
-        <f>VLOOKUP(G267,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
       <c r="J267" s="11"/>
@@ -12647,7 +12646,7 @@
         <v>185</v>
       </c>
       <c r="I268" t="e">
-        <f>VLOOKUP(G268,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
       <c r="J268" s="11"/>
@@ -12675,7 +12674,7 @@
         <v>185</v>
       </c>
       <c r="I269" t="str">
-        <f>VLOOKUP(G269,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>8956032186552548152</v>
       </c>
       <c r="J269" s="11"/>
@@ -12703,7 +12702,7 @@
         <v>185</v>
       </c>
       <c r="I270" t="str">
-        <f>VLOOKUP(G270,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>8956030216926247983</v>
       </c>
       <c r="J270" s="11"/>
@@ -12731,7 +12730,7 @@
         <v>185</v>
       </c>
       <c r="I271" t="str">
-        <f>VLOOKUP(G271,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>8956032234713494567</v>
       </c>
       <c r="J271" s="11"/>
@@ -12759,7 +12758,7 @@
         <v>185</v>
       </c>
       <c r="I272" t="str">
-        <f>VLOOKUP(G272,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>8956032254752139543</v>
       </c>
       <c r="J272" s="11"/>
@@ -12787,7 +12786,7 @@
         <v>185</v>
       </c>
       <c r="I273" t="str">
-        <f>VLOOKUP(G273,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>8956030216926248189</v>
       </c>
       <c r="J273" s="11"/>
@@ -12815,7 +12814,7 @@
         <v>185</v>
       </c>
       <c r="I274" t="str">
-        <f>VLOOKUP(G274,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>8956032234713494518</v>
       </c>
       <c r="J274" s="11"/>
@@ -12843,7 +12842,7 @@
         <v>185</v>
       </c>
       <c r="I275" t="str">
-        <f>VLOOKUP(G275,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>8956032201581692457</v>
       </c>
       <c r="J275" s="11"/>
@@ -12871,7 +12870,7 @@
         <v>185</v>
       </c>
       <c r="I276" t="str">
-        <f>VLOOKUP(G276,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>8956032234713494666</v>
       </c>
       <c r="J276" s="11"/>
@@ -12899,7 +12898,7 @@
         <v>185</v>
       </c>
       <c r="I277" t="str">
-        <f>VLOOKUP(G277,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>8956030221943028226</v>
       </c>
       <c r="J277" s="11"/>
@@ -12927,7 +12926,7 @@
         <v>185</v>
       </c>
       <c r="I278" t="str">
-        <f>VLOOKUP(G278,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>8956030185729636124</v>
       </c>
       <c r="J278" s="11"/>
@@ -12955,7 +12954,7 @@
         <v>185</v>
       </c>
       <c r="I279" t="str">
-        <f>VLOOKUP(G279,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>8956030216921418449</v>
       </c>
       <c r="J279" s="11"/>
@@ -12966,7 +12965,9 @@
       <c r="A280" s="9">
         <v>2964</v>
       </c>
-      <c r="B280" s="3"/>
+      <c r="B280" s="3" t="s">
+        <v>18</v>
+      </c>
       <c r="C280" s="3"/>
       <c r="D280" s="3" t="s">
         <v>749</v>
@@ -12979,7 +12980,7 @@
         <v>185</v>
       </c>
       <c r="I280" t="str">
-        <f>VLOOKUP(G280,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>8956034203014361500</v>
       </c>
       <c r="J280" s="11"/>
@@ -13007,7 +13008,7 @@
         <v>185</v>
       </c>
       <c r="I281" t="str">
-        <f>VLOOKUP(G281,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>8956034203014348408</v>
       </c>
       <c r="J281" s="11"/>
@@ -13035,7 +13036,7 @@
         <v>185</v>
       </c>
       <c r="I282" t="str">
-        <f>VLOOKUP(G282,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>8956032254752139444</v>
       </c>
       <c r="J282" s="11"/>
@@ -13063,7 +13064,7 @@
         <v>185</v>
       </c>
       <c r="I283" t="str">
-        <f>VLOOKUP(G283,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>8956034203014351071</v>
       </c>
       <c r="J283" s="11"/>
@@ -13091,7 +13092,7 @@
         <v>185</v>
       </c>
       <c r="I284" t="str">
-        <f>VLOOKUP(G284,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>8956032201581696680</v>
       </c>
       <c r="J284" s="11"/>
@@ -13119,7 +13120,7 @@
         <v>185</v>
       </c>
       <c r="I285" t="str">
-        <f>VLOOKUP(G285,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>8956032201581692283</v>
       </c>
       <c r="J285" s="11"/>
@@ -13147,7 +13148,7 @@
         <v>185</v>
       </c>
       <c r="I286" t="str">
-        <f>VLOOKUP(G286,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>8956032254752139477</v>
       </c>
       <c r="J286" s="11"/>
@@ -13175,7 +13176,7 @@
         <v>185</v>
       </c>
       <c r="I287" t="str">
-        <f>VLOOKUP(G287,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>8956032201581696979</v>
       </c>
       <c r="J287" s="11"/>
@@ -13203,7 +13204,7 @@
         <v>185</v>
       </c>
       <c r="I288" t="str">
-        <f>VLOOKUP(G288,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>8956030216921386166</v>
       </c>
       <c r="J288" s="11"/>
@@ -13231,7 +13232,7 @@
         <v>185</v>
       </c>
       <c r="I289" t="e">
-        <f>VLOOKUP(G289,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
       <c r="J289" s="11"/>
@@ -13259,7 +13260,7 @@
         <v>185</v>
       </c>
       <c r="I290" t="str">
-        <f>VLOOKUP(G290,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>8956034203014348572</v>
       </c>
       <c r="J290" s="11"/>
@@ -13287,7 +13288,7 @@
         <v>185</v>
       </c>
       <c r="I291" t="e">
-        <f>VLOOKUP(G291,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
       <c r="J291" s="11"/>
@@ -13315,7 +13316,7 @@
         <v>185</v>
       </c>
       <c r="I292" t="str">
-        <f>VLOOKUP(G292,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>8956030185729585545</v>
       </c>
       <c r="J292" s="11"/>
@@ -13343,7 +13344,7 @@
         <v>185</v>
       </c>
       <c r="I293" t="e">
-        <f>VLOOKUP(G293,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
       <c r="J293" s="11"/>
@@ -13371,7 +13372,7 @@
         <v>185</v>
       </c>
       <c r="I294" t="str">
-        <f>VLOOKUP(G294,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>8956032201581696862</v>
       </c>
       <c r="J294" s="11"/>
@@ -13399,7 +13400,7 @@
         <v>185</v>
       </c>
       <c r="I295" t="str">
-        <f>VLOOKUP(G295,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>8956030242988531072</v>
       </c>
       <c r="J295" s="11"/>
@@ -13427,7 +13428,7 @@
         <v>185</v>
       </c>
       <c r="I296" t="str">
-        <f>VLOOKUP(G296,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>8956032244722829976</v>
       </c>
       <c r="J296" s="11"/>
@@ -13455,7 +13456,7 @@
         <v>185</v>
       </c>
       <c r="I297" t="str">
-        <f>VLOOKUP(G297,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>8956030185729585941</v>
       </c>
       <c r="J297" s="11"/>
@@ -13483,7 +13484,7 @@
         <v>185</v>
       </c>
       <c r="I298" t="str">
-        <f>VLOOKUP(G298,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>8956032201581696243</v>
       </c>
       <c r="J298" s="11"/>
@@ -13511,7 +13512,7 @@
         <v>185</v>
       </c>
       <c r="I299" t="e">
-        <f>VLOOKUP(G299,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
       <c r="J299" s="11"/>
@@ -13539,7 +13540,7 @@
         <v>185</v>
       </c>
       <c r="I300" t="str">
-        <f>VLOOKUP(G300,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>8956030215874997474</v>
       </c>
       <c r="J300" s="11"/>
@@ -13567,7 +13568,7 @@
         <v>185</v>
       </c>
       <c r="I301" t="str">
-        <f>VLOOKUP(G301,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>8956032254752139410</v>
       </c>
       <c r="J301" s="11"/>
@@ -13595,7 +13596,7 @@
         <v>185</v>
       </c>
       <c r="I302" t="str">
-        <f>VLOOKUP(G302,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>8956032186552547535</v>
       </c>
       <c r="J302" s="11"/>
@@ -13623,7 +13624,7 @@
         <v>185</v>
       </c>
       <c r="I303" t="str">
-        <f>VLOOKUP(G303,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>8956030185729587749</v>
       </c>
       <c r="J303" s="11"/>
@@ -13651,7 +13652,7 @@
         <v>185</v>
       </c>
       <c r="I304" t="str">
-        <f>VLOOKUP(G304,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>8956032254752139436</v>
       </c>
       <c r="J304" s="23" t="s">
@@ -13681,7 +13682,7 @@
         <v>185</v>
       </c>
       <c r="I305" t="e">
-        <f>VLOOKUP(G305,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
       <c r="J305" s="11"/>
@@ -13709,7 +13710,7 @@
         <v>185</v>
       </c>
       <c r="I306" t="str">
-        <f>VLOOKUP(G306,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>8956030216926248015</v>
       </c>
       <c r="J306" s="11"/>
@@ -13737,7 +13738,7 @@
         <v>185</v>
       </c>
       <c r="I307" t="str">
-        <f>VLOOKUP(G307,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>8956032234713494492</v>
       </c>
       <c r="J307" s="11"/>
@@ -13765,7 +13766,7 @@
         <v>185</v>
       </c>
       <c r="I308" t="str">
-        <f>VLOOKUP(G308,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>8956034203014348317</v>
       </c>
       <c r="J308" s="11"/>
@@ -13793,7 +13794,7 @@
         <v>185</v>
       </c>
       <c r="I309" t="str">
-        <f>VLOOKUP(G309,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>8956030185729586147</v>
       </c>
       <c r="J309" s="11"/>
@@ -13821,7 +13822,7 @@
         <v>185</v>
       </c>
       <c r="I310" t="e">
-        <f>VLOOKUP(G310,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
       <c r="J310" s="11"/>
@@ -13849,7 +13850,7 @@
         <v>185</v>
       </c>
       <c r="I311" t="str">
-        <f>VLOOKUP(G311,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>8956034203014361401</v>
       </c>
       <c r="J311" s="11"/>
@@ -13877,7 +13878,7 @@
         <v>185</v>
       </c>
       <c r="I312" t="str">
-        <f>VLOOKUP(G312,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>8956032201581696706</v>
       </c>
       <c r="J312" s="11"/>
@@ -13905,7 +13906,7 @@
         <v>185</v>
       </c>
       <c r="I313" t="str">
-        <f>VLOOKUP(G313,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>8956032244730755650</v>
       </c>
       <c r="J313" s="11"/>
@@ -13933,7 +13934,7 @@
         <v>185</v>
       </c>
       <c r="I314" t="str">
-        <f>VLOOKUP(G314,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>8956032254752139469</v>
       </c>
       <c r="J314" s="23" t="s">
@@ -13963,7 +13964,7 @@
         <v>185</v>
       </c>
       <c r="I315" t="str">
-        <f>VLOOKUP(G315,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>8956032204612146402</v>
       </c>
       <c r="J315" s="11"/>
@@ -13991,7 +13992,7 @@
         <v>185</v>
       </c>
       <c r="I316" t="str">
-        <f>VLOOKUP(G316,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>8956032234713494724</v>
       </c>
       <c r="J316" s="11"/>
@@ -14019,7 +14020,7 @@
         <v>185</v>
       </c>
       <c r="I317" t="str">
-        <f>VLOOKUP(G317,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>8956030242988501059</v>
       </c>
       <c r="J317" s="11"/>
@@ -14047,7 +14048,7 @@
         <v>185</v>
       </c>
       <c r="I318" t="str">
-        <f>VLOOKUP(G318,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>8956032254752139493</v>
       </c>
       <c r="J318" s="11"/>
@@ -14075,7 +14076,7 @@
         <v>185</v>
       </c>
       <c r="I319" t="str">
-        <f>VLOOKUP(G319,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>8956034203014350958</v>
       </c>
       <c r="J319" s="11"/>
@@ -14103,7 +14104,7 @@
         <v>185</v>
       </c>
       <c r="I320" t="str">
-        <f>VLOOKUP(G320,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>8956032204612146428</v>
       </c>
       <c r="J320" s="11"/>
@@ -14131,7 +14132,7 @@
         <v>185</v>
       </c>
       <c r="I321" t="e">
-        <f>VLOOKUP(G321,D:D,1,0)</f>
+        <f t="shared" si="4"/>
         <v>#N/A</v>
       </c>
       <c r="J321" s="11"/>
@@ -14159,7 +14160,7 @@
         <v>185</v>
       </c>
       <c r="I322" t="str">
-        <f>VLOOKUP(G322,D:D,1,0)</f>
+        <f t="shared" ref="I322:I385" si="5">VLOOKUP(G322,D:D,1,0)</f>
         <v>8956032244722830016</v>
       </c>
       <c r="J322" s="21" t="s">
@@ -14189,7 +14190,7 @@
         <v>185</v>
       </c>
       <c r="I323" t="str">
-        <f>VLOOKUP(G323,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>8956030242988531668</v>
       </c>
       <c r="J323" s="11"/>
@@ -14217,7 +14218,7 @@
         <v>185</v>
       </c>
       <c r="I324" t="str">
-        <f>VLOOKUP(G324,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>8956030185729635365</v>
       </c>
       <c r="J324" s="11"/>
@@ -14245,7 +14246,7 @@
         <v>185</v>
       </c>
       <c r="I325" t="str">
-        <f>VLOOKUP(G325,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>8956034203014350867</v>
       </c>
       <c r="J325" s="11"/>
@@ -14273,7 +14274,7 @@
         <v>185</v>
       </c>
       <c r="I326" t="str">
-        <f>VLOOKUP(G326,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>8956032186552548384</v>
       </c>
       <c r="J326" s="11"/>
@@ -14301,7 +14302,7 @@
         <v>185</v>
       </c>
       <c r="I327" t="str">
-        <f>VLOOKUP(G327,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>8956032234713494625</v>
       </c>
       <c r="J327" s="11"/>
@@ -14329,7 +14330,7 @@
         <v>185</v>
       </c>
       <c r="I328" t="str">
-        <f>VLOOKUP(G328,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>8956032186552548210</v>
       </c>
       <c r="J328" s="21" t="s">
@@ -14359,7 +14360,7 @@
         <v>185</v>
       </c>
       <c r="I329" t="str">
-        <f>VLOOKUP(G329,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>8956032201581692325</v>
       </c>
       <c r="J329" s="11"/>
@@ -14387,7 +14388,7 @@
         <v>185</v>
       </c>
       <c r="I330" t="str">
-        <f>VLOOKUP(G330,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>8956032234712409632</v>
       </c>
       <c r="J330" s="21" t="s">
@@ -14417,7 +14418,7 @@
         <v>185</v>
       </c>
       <c r="I331" t="str">
-        <f>VLOOKUP(G331,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>8956032254752139238</v>
       </c>
       <c r="J331" s="21" t="s">
@@ -14447,7 +14448,7 @@
         <v>185</v>
       </c>
       <c r="I332" t="str">
-        <f>VLOOKUP(G332,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>8956032204612146196</v>
       </c>
       <c r="J332" s="21" t="s">
@@ -14477,7 +14478,7 @@
         <v>185</v>
       </c>
       <c r="I333" t="str">
-        <f>VLOOKUP(G333,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>8956032254752134536</v>
       </c>
       <c r="J333" s="23" t="s">
@@ -14507,7 +14508,7 @@
         <v>185</v>
       </c>
       <c r="I334" t="e">
-        <f>VLOOKUP(G334,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="J334" s="21" t="s">
@@ -14537,7 +14538,7 @@
         <v>185</v>
       </c>
       <c r="I335" t="str">
-        <f>VLOOKUP(G335,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>8956032201581696557</v>
       </c>
       <c r="J335" s="11"/>
@@ -14565,7 +14566,7 @@
         <v>185</v>
       </c>
       <c r="I336" t="str">
-        <f>VLOOKUP(G336,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>8956032201581696599</v>
       </c>
       <c r="J336" s="11"/>
@@ -14593,7 +14594,7 @@
         <v>185</v>
       </c>
       <c r="I337" t="str">
-        <f>VLOOKUP(G337,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>8956032186552548434</v>
       </c>
       <c r="J337" s="21" t="s">
@@ -14623,7 +14624,7 @@
         <v>185</v>
       </c>
       <c r="I338" t="str">
-        <f>VLOOKUP(G338,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>8956032201581696615</v>
       </c>
       <c r="J338" s="11"/>
@@ -14651,7 +14652,7 @@
         <v>185</v>
       </c>
       <c r="I339" t="str">
-        <f>VLOOKUP(G339,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>8956030185729589927</v>
       </c>
       <c r="J339" s="11"/>
@@ -14679,7 +14680,7 @@
         <v>185</v>
       </c>
       <c r="I340" t="str">
-        <f>VLOOKUP(G340,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>8956032234713494773</v>
       </c>
       <c r="J340" s="11"/>
@@ -14707,7 +14708,7 @@
         <v>185</v>
       </c>
       <c r="I341" t="str">
-        <f>VLOOKUP(G341,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>8956032201581696664</v>
       </c>
       <c r="J341" s="11"/>
@@ -14735,7 +14736,7 @@
         <v>185</v>
       </c>
       <c r="I342" t="str">
-        <f>VLOOKUP(G342,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>8956032204612146212</v>
       </c>
       <c r="J342" s="11"/>
@@ -14763,7 +14764,7 @@
         <v>185</v>
       </c>
       <c r="I343" t="str">
-        <f>VLOOKUP(G343,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>8956032201581696276</v>
       </c>
       <c r="J343" s="11"/>
@@ -14791,7 +14792,7 @@
         <v>185</v>
       </c>
       <c r="I344" t="str">
-        <f>VLOOKUP(G344,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>8956030185729589679</v>
       </c>
       <c r="J344" s="11"/>
@@ -14819,7 +14820,7 @@
         <v>185</v>
       </c>
       <c r="I345" t="str">
-        <f>VLOOKUP(G345,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>8956032201581696532</v>
       </c>
       <c r="J345" s="11"/>
@@ -14847,7 +14848,7 @@
         <v>185</v>
       </c>
       <c r="I346" t="str">
-        <f>VLOOKUP(G346,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>8956030216926248007</v>
       </c>
       <c r="J346" s="11"/>
@@ -14875,7 +14876,7 @@
         <v>185</v>
       </c>
       <c r="I347" t="str">
-        <f>VLOOKUP(G347,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>8956030185729586485</v>
       </c>
       <c r="J347" s="11"/>
@@ -14903,7 +14904,7 @@
         <v>185</v>
       </c>
       <c r="I348" t="str">
-        <f>VLOOKUP(G348,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>8956030216921386216</v>
       </c>
       <c r="J348" s="11"/>
@@ -14931,7 +14932,7 @@
         <v>185</v>
       </c>
       <c r="I349" t="str">
-        <f>VLOOKUP(G349,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>8956034203014348176</v>
       </c>
       <c r="J349" s="11"/>
@@ -14959,7 +14960,7 @@
         <v>185</v>
       </c>
       <c r="I350" t="str">
-        <f>VLOOKUP(G350,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>8956032254752139246</v>
       </c>
       <c r="J350" s="23" t="s">
@@ -14989,7 +14990,7 @@
         <v>185</v>
       </c>
       <c r="I351" t="e">
-        <f>VLOOKUP(G351,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="J351" s="11"/>
@@ -15017,7 +15018,7 @@
         <v>185</v>
       </c>
       <c r="I352" t="e">
-        <f>VLOOKUP(G352,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="J352" s="11"/>
@@ -15045,7 +15046,7 @@
         <v>185</v>
       </c>
       <c r="I353" t="str">
-        <f>VLOOKUP(G353,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>8956030242988531353</v>
       </c>
       <c r="J353" s="11"/>
@@ -15073,7 +15074,7 @@
         <v>185</v>
       </c>
       <c r="I354" t="str">
-        <f>VLOOKUP(G354,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>8956032204612146220</v>
       </c>
       <c r="J354" s="11"/>
@@ -15101,7 +15102,7 @@
         <v>185</v>
       </c>
       <c r="I355" t="str">
-        <f>VLOOKUP(G355,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>8956032204612146337</v>
       </c>
       <c r="J355" s="11"/>
@@ -15129,7 +15130,7 @@
         <v>185</v>
       </c>
       <c r="I356" t="str">
-        <f>VLOOKUP(G356,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>8956034203014350909</v>
       </c>
       <c r="J356" s="11"/>
@@ -15157,7 +15158,7 @@
         <v>185</v>
       </c>
       <c r="I357" t="e">
-        <f>VLOOKUP(G357,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="J357" s="11"/>
@@ -15185,7 +15186,7 @@
         <v>185</v>
       </c>
       <c r="I358" t="str">
-        <f>VLOOKUP(G358,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>8956032201581696508</v>
       </c>
       <c r="J358" s="11"/>
@@ -15213,7 +15214,7 @@
         <v>185</v>
       </c>
       <c r="I359" t="str">
-        <f>VLOOKUP(G359,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>8956030216921386158</v>
       </c>
       <c r="J359" s="11"/>
@@ -15241,7 +15242,7 @@
         <v>185</v>
       </c>
       <c r="I360" t="str">
-        <f>VLOOKUP(G360,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>8956032234713494849</v>
       </c>
       <c r="J360" s="11"/>
@@ -15269,7 +15270,7 @@
         <v>185</v>
       </c>
       <c r="I361" t="str">
-        <f>VLOOKUP(G361,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>8956030216921386257</v>
       </c>
       <c r="J361" s="11"/>
@@ -15297,7 +15298,7 @@
         <v>185</v>
       </c>
       <c r="I362" t="str">
-        <f>VLOOKUP(G362,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>8956030185729635894</v>
       </c>
       <c r="J362" s="11"/>
@@ -15325,7 +15326,7 @@
         <v>185</v>
       </c>
       <c r="I363" t="str">
-        <f>VLOOKUP(G363,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>8956034203014361336</v>
       </c>
       <c r="J363" s="11"/>
@@ -15353,7 +15354,7 @@
         <v>185</v>
       </c>
       <c r="I364" t="str">
-        <f>VLOOKUP(G364,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>8956032254752139253</v>
       </c>
       <c r="J364" s="23" t="s">
@@ -15383,7 +15384,7 @@
         <v>185</v>
       </c>
       <c r="I365" t="str">
-        <f>VLOOKUP(G365,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>8956034203014350701</v>
       </c>
       <c r="J365" s="11"/>
@@ -15411,7 +15412,7 @@
         <v>185</v>
       </c>
       <c r="I366" t="str">
-        <f>VLOOKUP(G366,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>8956032244730755676</v>
       </c>
       <c r="J366" s="11"/>
@@ -15439,7 +15440,7 @@
         <v>185</v>
       </c>
       <c r="I367" t="e">
-        <f>VLOOKUP(G367,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="J367" s="11"/>
@@ -15467,7 +15468,7 @@
         <v>185</v>
       </c>
       <c r="I368" t="str">
-        <f>VLOOKUP(G368,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>8956034203014361104</v>
       </c>
       <c r="J368" s="11"/>
@@ -15495,7 +15496,7 @@
         <v>185</v>
       </c>
       <c r="I369" t="str">
-        <f>VLOOKUP(G369,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>8956032234712409491</v>
       </c>
       <c r="J369" s="11"/>
@@ -15523,7 +15524,7 @@
         <v>185</v>
       </c>
       <c r="I370" t="e">
-        <f>VLOOKUP(G370,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="J370" s="11"/>
@@ -15551,7 +15552,7 @@
         <v>185</v>
       </c>
       <c r="I371" t="str">
-        <f>VLOOKUP(G371,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>8956032244730755932</v>
       </c>
       <c r="J371" s="21" t="s">
@@ -15581,7 +15582,7 @@
         <v>185</v>
       </c>
       <c r="I372" t="str">
-        <f>VLOOKUP(G372,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>8956032234713494732</v>
       </c>
       <c r="J372" s="11"/>
@@ -15609,7 +15610,7 @@
         <v>185</v>
       </c>
       <c r="I373" t="str">
-        <f>VLOOKUP(G373,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>8956034203014350982</v>
       </c>
       <c r="J373" s="11"/>
@@ -15637,7 +15638,7 @@
         <v>185</v>
       </c>
       <c r="I374" t="str">
-        <f>VLOOKUP(G374,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>8956030185729585784</v>
       </c>
       <c r="J374" s="11"/>
@@ -15665,7 +15666,7 @@
         <v>185</v>
       </c>
       <c r="I375" t="str">
-        <f>VLOOKUP(G375,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>8956030185729585560</v>
       </c>
       <c r="J375" s="11"/>
@@ -15693,7 +15694,7 @@
         <v>185</v>
       </c>
       <c r="I376" t="e">
-        <f>VLOOKUP(G376,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>#N/A</v>
       </c>
       <c r="J376" s="11"/>
@@ -15721,7 +15722,7 @@
         <v>185</v>
       </c>
       <c r="I377" t="str">
-        <f>VLOOKUP(G377,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>8956032204612146246</v>
       </c>
       <c r="J377" s="11"/>
@@ -15749,7 +15750,7 @@
         <v>185</v>
       </c>
       <c r="I378" t="str">
-        <f>VLOOKUP(G378,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>8956030242988532526</v>
       </c>
       <c r="J378" s="11"/>
@@ -15777,7 +15778,7 @@
         <v>185</v>
       </c>
       <c r="I379" t="str">
-        <f>VLOOKUP(G379,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>8956032244730755684</v>
       </c>
       <c r="J379" s="11"/>
@@ -15805,7 +15806,7 @@
         <v>185</v>
       </c>
       <c r="I380" t="str">
-        <f>VLOOKUP(G380,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>8956030242988531585</v>
       </c>
       <c r="J380" s="11"/>
@@ -15833,7 +15834,7 @@
         <v>185</v>
       </c>
       <c r="I381" t="str">
-        <f>VLOOKUP(G381,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>8956030242988531445</v>
       </c>
       <c r="J381" s="11"/>
@@ -15861,7 +15862,7 @@
         <v>185</v>
       </c>
       <c r="I382" t="str">
-        <f>VLOOKUP(G382,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>8956032254752139261</v>
       </c>
       <c r="J382" s="11"/>
@@ -15889,7 +15890,7 @@
         <v>185</v>
       </c>
       <c r="I383" t="str">
-        <f>VLOOKUP(G383,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>8956030185729586667</v>
       </c>
       <c r="J383" s="11"/>
@@ -15917,7 +15918,7 @@
         <v>185</v>
       </c>
       <c r="I384" t="str">
-        <f>VLOOKUP(G384,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>8956032234712409970</v>
       </c>
       <c r="J384" s="11"/>
@@ -15945,7 +15946,7 @@
         <v>185</v>
       </c>
       <c r="I385" t="str">
-        <f>VLOOKUP(G385,D:D,1,0)</f>
+        <f t="shared" si="5"/>
         <v>8956032234712409749</v>
       </c>
       <c r="J385" s="11"/>
@@ -15973,7 +15974,7 @@
         <v>185</v>
       </c>
       <c r="I386" t="str">
-        <f>VLOOKUP(G386,D:D,1,0)</f>
+        <f t="shared" ref="I386:I449" si="6">VLOOKUP(G386,D:D,1,0)</f>
         <v>8956030185729587285</v>
       </c>
       <c r="J386" s="11"/>
@@ -16001,7 +16002,7 @@
         <v>185</v>
       </c>
       <c r="I387" t="str">
-        <f>VLOOKUP(G387,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>8956032201581696649</v>
       </c>
       <c r="J387" s="11"/>
@@ -16029,7 +16030,7 @@
         <v>185</v>
       </c>
       <c r="I388" t="str">
-        <f>VLOOKUP(G388,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>8956030185729587004</v>
       </c>
       <c r="J388" s="11"/>
@@ -16057,7 +16058,7 @@
         <v>185</v>
       </c>
       <c r="I389" t="e">
-        <f>VLOOKUP(G389,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
       <c r="J389" s="11"/>
@@ -16085,7 +16086,7 @@
         <v>185</v>
       </c>
       <c r="I390" t="str">
-        <f>VLOOKUP(G390,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>8956032201581696714</v>
       </c>
       <c r="J390" s="11"/>
@@ -16113,7 +16114,7 @@
         <v>185</v>
       </c>
       <c r="I391" t="str">
-        <f>VLOOKUP(G391,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>8956030216921386083</v>
       </c>
       <c r="J391" s="11"/>
@@ -16141,7 +16142,7 @@
         <v>185</v>
       </c>
       <c r="I392" t="str">
-        <f>VLOOKUP(G392,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>8956034203014350610</v>
       </c>
       <c r="J392" s="11"/>
@@ -16169,7 +16170,7 @@
         <v>185</v>
       </c>
       <c r="I393" t="str">
-        <f>VLOOKUP(G393,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>8956034203014348309</v>
       </c>
       <c r="J393" s="11"/>
@@ -16197,7 +16198,7 @@
         <v>185</v>
       </c>
       <c r="I394" t="str">
-        <f>VLOOKUP(G394,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>8956032254752139279</v>
       </c>
       <c r="J394" s="11"/>
@@ -16225,7 +16226,7 @@
         <v>185</v>
       </c>
       <c r="I395" t="str">
-        <f>VLOOKUP(G395,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>8956034203014361096</v>
       </c>
       <c r="J395" s="11"/>
@@ -16253,7 +16254,7 @@
         <v>185</v>
       </c>
       <c r="I396" t="str">
-        <f>VLOOKUP(G396,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>8956034203014350727</v>
       </c>
       <c r="J396" s="11"/>
@@ -16281,7 +16282,7 @@
         <v>185</v>
       </c>
       <c r="I397" t="str">
-        <f>VLOOKUP(G397,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>8956032204612146360</v>
       </c>
       <c r="J397" s="11"/>
@@ -16309,7 +16310,7 @@
         <v>185</v>
       </c>
       <c r="I398" t="str">
-        <f>VLOOKUP(G398,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>8956030185729635332</v>
       </c>
       <c r="J398" s="11"/>
@@ -16337,7 +16338,7 @@
         <v>185</v>
       </c>
       <c r="I399" t="str">
-        <f>VLOOKUP(G399,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>8956030185729589646</v>
       </c>
       <c r="J399" s="11"/>
@@ -16365,7 +16366,7 @@
         <v>185</v>
       </c>
       <c r="I400" t="e">
-        <f>VLOOKUP(G400,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
       <c r="J400" s="11"/>
@@ -16393,7 +16394,7 @@
         <v>185</v>
       </c>
       <c r="I401" t="str">
-        <f>VLOOKUP(G401,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>8956030242988532534</v>
       </c>
       <c r="J401" s="11"/>
@@ -16421,7 +16422,7 @@
         <v>185</v>
       </c>
       <c r="I402" t="str">
-        <f>VLOOKUP(G402,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>8956030221943028853</v>
       </c>
       <c r="J402" s="11"/>
@@ -16449,7 +16450,7 @@
         <v>185</v>
       </c>
       <c r="I403" t="str">
-        <f>VLOOKUP(G403,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>8956032204612146378</v>
       </c>
       <c r="J403" s="11"/>
@@ -16477,7 +16478,7 @@
         <v>185</v>
       </c>
       <c r="I404" t="e">
-        <f>VLOOKUP(G404,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
       <c r="J404" s="11"/>
@@ -16505,7 +16506,7 @@
         <v>185</v>
       </c>
       <c r="I405" t="str">
-        <f>VLOOKUP(G405,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>8956030185729635076</v>
       </c>
       <c r="J405" s="11"/>
@@ -16533,7 +16534,7 @@
         <v>185</v>
       </c>
       <c r="I406" t="str">
-        <f>VLOOKUP(G406,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>8956034203014348523</v>
       </c>
       <c r="J406" s="11"/>
@@ -16561,7 +16562,7 @@
         <v>185</v>
       </c>
       <c r="I407" t="str">
-        <f>VLOOKUP(G407,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>8956030221943028218</v>
       </c>
       <c r="J407" s="11"/>
@@ -16589,7 +16590,7 @@
         <v>185</v>
       </c>
       <c r="I408" t="e">
-        <f>VLOOKUP(G408,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
       <c r="J408" s="11"/>
@@ -16617,7 +16618,7 @@
         <v>185</v>
       </c>
       <c r="I409" t="str">
-        <f>VLOOKUP(G409,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>8956030215873273638</v>
       </c>
       <c r="J409" s="11"/>
@@ -16645,7 +16646,7 @@
         <v>185</v>
       </c>
       <c r="I410" t="str">
-        <f>VLOOKUP(G410,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>8956032254752134601</v>
       </c>
       <c r="J410" s="11"/>
@@ -16673,7 +16674,7 @@
         <v>185</v>
       </c>
       <c r="I411" t="str">
-        <f>VLOOKUP(G411,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>8956030215873272796</v>
       </c>
       <c r="J411" s="11"/>
@@ -16701,7 +16702,7 @@
         <v>185</v>
       </c>
       <c r="I412" t="e">
-        <f>VLOOKUP(G412,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
       <c r="J412" s="11"/>
@@ -16729,7 +16730,7 @@
         <v>185</v>
       </c>
       <c r="I413" t="str">
-        <f>VLOOKUP(G413,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>8956032234712409764</v>
       </c>
       <c r="J413" s="11"/>
@@ -16757,7 +16758,7 @@
         <v>185</v>
       </c>
       <c r="I414" t="str">
-        <f>VLOOKUP(G414,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>8956030215873272846</v>
       </c>
       <c r="J414" s="11"/>
@@ -16785,7 +16786,7 @@
         <v>185</v>
       </c>
       <c r="I415" t="str">
-        <f>VLOOKUP(G415,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>8956032254752134510</v>
       </c>
       <c r="J415" s="11"/>
@@ -16813,7 +16814,7 @@
         <v>185</v>
       </c>
       <c r="I416" t="str">
-        <f>VLOOKUP(G416,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>8956030242988501133</v>
       </c>
       <c r="J416" s="11"/>
@@ -16841,7 +16842,7 @@
         <v>185</v>
       </c>
       <c r="I417" t="str">
-        <f>VLOOKUP(G417,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>8956030216926247538</v>
       </c>
       <c r="J417" s="11"/>
@@ -16869,7 +16870,7 @@
         <v>185</v>
       </c>
       <c r="I418" t="str">
-        <f>VLOOKUP(G418,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>8956030215873273620</v>
       </c>
       <c r="J418" s="11"/>
@@ -16897,7 +16898,7 @@
         <v>185</v>
       </c>
       <c r="I419" t="str">
-        <f>VLOOKUP(G419,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>8956030216926247520</v>
       </c>
       <c r="J419" s="11"/>
@@ -16925,7 +16926,7 @@
         <v>185</v>
       </c>
       <c r="I420" t="str">
-        <f>VLOOKUP(G420,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>8956030215873273521</v>
       </c>
       <c r="J420" s="11"/>
@@ -16953,7 +16954,7 @@
         <v>185</v>
       </c>
       <c r="I421" t="str">
-        <f>VLOOKUP(G421,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>8956032254752134635</v>
       </c>
       <c r="J421" s="11"/>
@@ -16981,7 +16982,7 @@
         <v>185</v>
       </c>
       <c r="I422" t="str">
-        <f>VLOOKUP(G422,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>8956030215873272754</v>
       </c>
       <c r="J422" s="11"/>
@@ -17009,7 +17010,7 @@
         <v>185</v>
       </c>
       <c r="I423" t="str">
-        <f>VLOOKUP(G423,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>8956032254752134593</v>
       </c>
       <c r="J423" s="23" t="s">
@@ -17039,7 +17040,7 @@
         <v>185</v>
       </c>
       <c r="I424" t="e">
-        <f>VLOOKUP(G424,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
       <c r="J424" s="11"/>
@@ -17067,7 +17068,7 @@
         <v>185</v>
       </c>
       <c r="I425" t="str">
-        <f>VLOOKUP(G425,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>8956030185729586006</v>
       </c>
       <c r="J425" s="11"/>
@@ -17095,7 +17096,7 @@
         <v>185</v>
       </c>
       <c r="I426" t="str">
-        <f>VLOOKUP(G426,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>8956030215873272887</v>
       </c>
       <c r="J426" s="11"/>
@@ -17123,7 +17124,7 @@
         <v>185</v>
       </c>
       <c r="I427" t="e">
-        <f>VLOOKUP(G427,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
       <c r="J427" s="11"/>
@@ -17151,7 +17152,7 @@
         <v>185</v>
       </c>
       <c r="I428" t="e">
-        <f>VLOOKUP(G428,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
       <c r="J428" s="11"/>
@@ -17179,7 +17180,7 @@
         <v>185</v>
       </c>
       <c r="I429" t="e">
-        <f>VLOOKUP(G429,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
       <c r="J429" s="11"/>
@@ -17207,7 +17208,7 @@
         <v>185</v>
       </c>
       <c r="I430" t="str">
-        <f>VLOOKUP(G430,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>8956030215873272788</v>
       </c>
       <c r="J430" s="11"/>
@@ -17235,7 +17236,7 @@
         <v>185</v>
       </c>
       <c r="I431" t="str">
-        <f>VLOOKUP(G431,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>8956030215873273562</v>
       </c>
       <c r="J431" s="11"/>
@@ -17263,7 +17264,7 @@
         <v>185</v>
       </c>
       <c r="I432" t="str">
-        <f>VLOOKUP(G432,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>8956030215873272820</v>
       </c>
       <c r="J432" s="11"/>
@@ -17291,7 +17292,7 @@
         <v>185</v>
       </c>
       <c r="I433" t="str">
-        <f>VLOOKUP(G433,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>8956030216926247504</v>
       </c>
       <c r="J433" s="11"/>
@@ -17319,7 +17320,7 @@
         <v>185</v>
       </c>
       <c r="I434" t="str">
-        <f>VLOOKUP(G434,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>8956032254752134650</v>
       </c>
       <c r="J434" s="11"/>
@@ -17347,7 +17348,7 @@
         <v>185</v>
       </c>
       <c r="I435" t="e">
-        <f>VLOOKUP(G435,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
       <c r="J435" s="11"/>
@@ -17375,7 +17376,7 @@
         <v>185</v>
       </c>
       <c r="I436" t="str">
-        <f>VLOOKUP(G436,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>8956030215873273596</v>
       </c>
       <c r="J436" s="11"/>
@@ -17403,7 +17404,7 @@
         <v>185</v>
       </c>
       <c r="I437" t="str">
-        <f>VLOOKUP(G437,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>8956030216926247579</v>
       </c>
       <c r="J437" s="11"/>
@@ -17431,7 +17432,7 @@
         <v>185</v>
       </c>
       <c r="I438" t="str">
-        <f>VLOOKUP(G438,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>8956032254752134767</v>
       </c>
       <c r="J438" s="23" t="s">
@@ -17461,7 +17462,7 @@
         <v>185</v>
       </c>
       <c r="I439" t="str">
-        <f>VLOOKUP(G439,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>8956032254752134619</v>
       </c>
       <c r="J439" s="11"/>
@@ -17489,7 +17490,7 @@
         <v>185</v>
       </c>
       <c r="I440" t="str">
-        <f>VLOOKUP(G440,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>8956030215873273588</v>
       </c>
       <c r="J440" s="11"/>
@@ -17517,7 +17518,7 @@
         <v>185</v>
       </c>
       <c r="I441" t="str">
-        <f>VLOOKUP(G441,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>8956030215873272705</v>
       </c>
       <c r="J441" s="11"/>
@@ -17545,7 +17546,7 @@
         <v>185</v>
       </c>
       <c r="I442" t="str">
-        <f>VLOOKUP(G442,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>8956032254752139212</v>
       </c>
       <c r="J442" s="11"/>
@@ -17573,7 +17574,7 @@
         <v>185</v>
       </c>
       <c r="I443" t="e">
-        <f>VLOOKUP(G443,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
       <c r="J443" s="11"/>
@@ -17601,7 +17602,7 @@
         <v>185</v>
       </c>
       <c r="I444" t="str">
-        <f>VLOOKUP(G444,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>8956030216926248197</v>
       </c>
       <c r="J444" s="11"/>
@@ -17629,7 +17630,7 @@
         <v>185</v>
       </c>
       <c r="I445" t="e">
-        <f>VLOOKUP(G445,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>#N/A</v>
       </c>
       <c r="J445" s="11"/>
@@ -17657,7 +17658,7 @@
         <v>185</v>
       </c>
       <c r="I446" t="str">
-        <f>VLOOKUP(G446,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>8956032234713494823</v>
       </c>
       <c r="J446" s="11"/>
@@ -17685,7 +17686,7 @@
         <v>185</v>
       </c>
       <c r="I447" t="str">
-        <f>VLOOKUP(G447,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>8956032211667084446</v>
       </c>
       <c r="J447" s="11"/>
@@ -17713,7 +17714,7 @@
         <v>185</v>
       </c>
       <c r="I448" t="str">
-        <f>VLOOKUP(G448,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>8956032211667084503</v>
       </c>
       <c r="J448" s="11"/>
@@ -17741,7 +17742,7 @@
         <v>185</v>
       </c>
       <c r="I449" t="str">
-        <f>VLOOKUP(G449,D:D,1,0)</f>
+        <f t="shared" si="6"/>
         <v>8956032211667084727</v>
       </c>
       <c r="J449" s="11"/>
@@ -17769,7 +17770,7 @@
         <v>185</v>
       </c>
       <c r="I450" t="str">
-        <f>VLOOKUP(G450,D:D,1,0)</f>
+        <f t="shared" ref="I450:I513" si="7">VLOOKUP(G450,D:D,1,0)</f>
         <v>8956030242988532880</v>
       </c>
       <c r="J450" s="11"/>
@@ -17797,7 +17798,7 @@
         <v>185</v>
       </c>
       <c r="I451" t="str">
-        <f>VLOOKUP(G451,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>8956030216926241630</v>
       </c>
       <c r="J451" s="11"/>
@@ -17825,7 +17826,7 @@
         <v>185</v>
       </c>
       <c r="I452" t="str">
-        <f>VLOOKUP(G452,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>8956030205811195191</v>
       </c>
       <c r="J452" s="11"/>
@@ -17853,7 +17854,7 @@
         <v>185</v>
       </c>
       <c r="I453" t="str">
-        <f>VLOOKUP(G453,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>8956032254752139899</v>
       </c>
       <c r="J453" s="23" t="s">
@@ -17883,7 +17884,7 @@
         <v>185</v>
       </c>
       <c r="I454" t="str">
-        <f>VLOOKUP(G454,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>8956030242988531049</v>
       </c>
       <c r="J454" s="11"/>
@@ -17911,7 +17912,7 @@
         <v>185</v>
       </c>
       <c r="I455" t="str">
-        <f>VLOOKUP(G455,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>8956032244730755999</v>
       </c>
       <c r="J455" s="11"/>
@@ -17939,7 +17940,7 @@
         <v>185</v>
       </c>
       <c r="I456" t="str">
-        <f>VLOOKUP(G456,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>8956034203014361161</v>
       </c>
       <c r="J456" s="11"/>
@@ -17967,7 +17968,7 @@
         <v>185</v>
       </c>
       <c r="I457" t="str">
-        <f>VLOOKUP(G457,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>8956030242988531429</v>
       </c>
       <c r="J457" s="11"/>
@@ -17995,7 +17996,7 @@
         <v>185</v>
       </c>
       <c r="I458" t="str">
-        <f>VLOOKUP(G458,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>8956034203014348127</v>
       </c>
       <c r="J458" s="11"/>
@@ -18023,7 +18024,7 @@
         <v>185</v>
       </c>
       <c r="I459" t="e">
-        <f>VLOOKUP(G459,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>#N/A</v>
       </c>
       <c r="J459" s="11"/>
@@ -18049,7 +18050,7 @@
         <v>185</v>
       </c>
       <c r="I460" t="str">
-        <f>VLOOKUP(G460,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>8956034203014348564</v>
       </c>
       <c r="J460" s="11"/>
@@ -18077,7 +18078,7 @@
         <v>185</v>
       </c>
       <c r="I461" t="str">
-        <f>VLOOKUP(G461,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>8956034203014350628</v>
       </c>
       <c r="J461" s="11"/>
@@ -18105,7 +18106,7 @@
         <v>185</v>
       </c>
       <c r="I462" t="str">
-        <f>VLOOKUP(G462,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>8956032254752139501</v>
       </c>
       <c r="J462" s="11"/>
@@ -18133,7 +18134,7 @@
         <v>185</v>
       </c>
       <c r="I463" t="str">
-        <f>VLOOKUP(G463,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>8956030185729589067</v>
       </c>
       <c r="J463" s="11"/>
@@ -18161,7 +18162,7 @@
         <v>185</v>
       </c>
       <c r="I464" t="str">
-        <f>VLOOKUP(G464,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>8956032204612146436</v>
       </c>
       <c r="J464" s="11"/>
@@ -18189,7 +18190,7 @@
         <v>185</v>
       </c>
       <c r="I465" t="e">
-        <f>VLOOKUP(G465,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>#N/A</v>
       </c>
       <c r="J465" s="11"/>
@@ -18217,7 +18218,7 @@
         <v>185</v>
       </c>
       <c r="I466" t="str">
-        <f>VLOOKUP(G466,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>8956034203014361435</v>
       </c>
       <c r="J466" s="11"/>
@@ -18245,7 +18246,7 @@
         <v>185</v>
       </c>
       <c r="I467" t="str">
-        <f>VLOOKUP(G467,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>8956032254752139535</v>
       </c>
       <c r="J467" s="11"/>
@@ -18273,7 +18274,7 @@
         <v>185</v>
       </c>
       <c r="I468" t="str">
-        <f>VLOOKUP(G468,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>8956032234712409962</v>
       </c>
       <c r="J468" s="11"/>
@@ -18299,7 +18300,7 @@
         <v>185</v>
       </c>
       <c r="I469" t="str">
-        <f>VLOOKUP(G469,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>8956034203014361294</v>
       </c>
       <c r="J469" s="11"/>
@@ -18325,7 +18326,7 @@
         <v>185</v>
       </c>
       <c r="I470" t="e">
-        <f>VLOOKUP(G470,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>#N/A</v>
       </c>
       <c r="J470" s="11"/>
@@ -18353,7 +18354,7 @@
         <v>185</v>
       </c>
       <c r="I471" t="str">
-        <f>VLOOKUP(G471,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>8956030185729585792</v>
       </c>
       <c r="J471" s="11"/>
@@ -18379,7 +18380,7 @@
         <v>185</v>
       </c>
       <c r="I472" t="str">
-        <f>VLOOKUP(G472,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>8956034203014351063</v>
       </c>
       <c r="J472" s="11"/>
@@ -18405,7 +18406,7 @@
         <v>185</v>
       </c>
       <c r="I473" t="str">
-        <f>VLOOKUP(G473,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>8956030185729589091</v>
       </c>
       <c r="J473" s="11"/>
@@ -18431,7 +18432,7 @@
         <v>185</v>
       </c>
       <c r="I474" t="e">
-        <f>VLOOKUP(G474,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>#N/A</v>
       </c>
       <c r="J474" s="11"/>
@@ -18457,7 +18458,7 @@
         <v>185</v>
       </c>
       <c r="I475" t="str">
-        <f>VLOOKUP(G475,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>8956030185729588614</v>
       </c>
       <c r="J475" s="11"/>
@@ -18483,7 +18484,7 @@
         <v>185</v>
       </c>
       <c r="I476" t="str">
-        <f>VLOOKUP(G476,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>8956030216926248031</v>
       </c>
       <c r="J476" s="11"/>
@@ -18509,7 +18510,7 @@
         <v>185</v>
       </c>
       <c r="I477" t="e">
-        <f>VLOOKUP(G477,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>#N/A</v>
       </c>
       <c r="J477" s="11"/>
@@ -18537,7 +18538,7 @@
         <v>185</v>
       </c>
       <c r="I478" t="str">
-        <f>VLOOKUP(G478,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>8956032254752139527</v>
       </c>
       <c r="J478" s="11"/>
@@ -18565,7 +18566,7 @@
         <v>185</v>
       </c>
       <c r="I479" t="str">
-        <f>VLOOKUP(G479,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>8956034203014350800</v>
       </c>
       <c r="J479" s="11"/>
@@ -18593,7 +18594,7 @@
         <v>185</v>
       </c>
       <c r="I480" t="str">
-        <f>VLOOKUP(G480,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>8956032204612146444</v>
       </c>
       <c r="J480" s="11"/>
@@ -18621,7 +18622,7 @@
         <v>185</v>
       </c>
       <c r="I481" t="str">
-        <f>VLOOKUP(G481,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>8956034203014361237</v>
       </c>
       <c r="J481" s="11"/>
@@ -18649,7 +18650,7 @@
         <v>185</v>
       </c>
       <c r="I482" t="str">
-        <f>VLOOKUP(G482,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>8956032254752139550</v>
       </c>
       <c r="J482" s="11"/>
@@ -18677,7 +18678,7 @@
         <v>185</v>
       </c>
       <c r="I483" t="str">
-        <f>VLOOKUP(G483,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>8956032254752139568</v>
       </c>
       <c r="J483" s="11"/>
@@ -18705,7 +18706,7 @@
         <v>185</v>
       </c>
       <c r="I484" t="str">
-        <f>VLOOKUP(G484,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>8956032254752139576</v>
       </c>
       <c r="J484" s="11"/>
@@ -18733,7 +18734,7 @@
         <v>185</v>
       </c>
       <c r="I485" t="str">
-        <f>VLOOKUP(G485,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>8956030242988531056</v>
       </c>
       <c r="J485" s="11"/>
@@ -18761,7 +18762,7 @@
         <v>185</v>
       </c>
       <c r="I486" t="str">
-        <f>VLOOKUP(G486,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>8956032254752139592</v>
       </c>
       <c r="J486" s="11"/>
@@ -18789,7 +18790,7 @@
         <v>185</v>
       </c>
       <c r="I487" t="str">
-        <f>VLOOKUP(G487,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>8956032254752139584</v>
       </c>
       <c r="J487" s="11"/>
@@ -18817,7 +18818,7 @@
         <v>185</v>
       </c>
       <c r="I488" t="str">
-        <f>VLOOKUP(G488,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>8956030216926242646</v>
       </c>
       <c r="J488" s="11"/>
@@ -18845,7 +18846,7 @@
         <v>185</v>
       </c>
       <c r="I489" t="str">
-        <f>VLOOKUP(G489,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>8956030242988505522</v>
       </c>
       <c r="J489" s="11"/>
@@ -18873,7 +18874,7 @@
         <v>185</v>
       </c>
       <c r="I490" t="str">
-        <f>VLOOKUP(G490,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>8956030216926242729</v>
       </c>
       <c r="J490" s="11"/>
@@ -18901,7 +18902,7 @@
         <v>185</v>
       </c>
       <c r="I491" t="str">
-        <f>VLOOKUP(G491,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>8956030242988531205</v>
       </c>
       <c r="J491" s="11"/>
@@ -18929,7 +18930,7 @@
         <v>185</v>
       </c>
       <c r="I492" t="str">
-        <f>VLOOKUP(G492,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>8956030242988505431</v>
       </c>
       <c r="J492" s="11"/>
@@ -18957,7 +18958,7 @@
         <v>185</v>
       </c>
       <c r="I493" t="e">
-        <f>VLOOKUP(G493,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>#N/A</v>
       </c>
       <c r="J493" s="11"/>
@@ -18985,7 +18986,7 @@
         <v>185</v>
       </c>
       <c r="I494" t="str">
-        <f>VLOOKUP(G494,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>8956032234712409863</v>
       </c>
       <c r="J494" s="11"/>
@@ -19013,7 +19014,7 @@
         <v>185</v>
       </c>
       <c r="I495" t="str">
-        <f>VLOOKUP(G495,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>8956032186552548160</v>
       </c>
       <c r="J495" s="11"/>
@@ -19041,7 +19042,7 @@
         <v>185</v>
       </c>
       <c r="I496" t="str">
-        <f>VLOOKUP(G496,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>8956032201581696250</v>
       </c>
       <c r="J496" s="11"/>
@@ -19069,7 +19070,7 @@
         <v>185</v>
       </c>
       <c r="I497" t="str">
-        <f>VLOOKUP(G497,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>8956030242988531312</v>
       </c>
       <c r="J497" s="11"/>
@@ -19097,7 +19098,7 @@
         <v>185</v>
       </c>
       <c r="I498" t="str">
-        <f>VLOOKUP(G498,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>8956032254752139626</v>
       </c>
       <c r="J498" s="11"/>
@@ -19125,7 +19126,7 @@
         <v>185</v>
       </c>
       <c r="I499" t="str">
-        <f>VLOOKUP(G499,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>8956032201581696268</v>
       </c>
       <c r="J499" s="11"/>
@@ -19153,7 +19154,7 @@
         <v>185</v>
       </c>
       <c r="I500" t="str">
-        <f>VLOOKUP(G500,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>8956032254752139634</v>
       </c>
       <c r="J500" s="11"/>
@@ -19181,7 +19182,7 @@
         <v>185</v>
       </c>
       <c r="I501" t="str">
-        <f>VLOOKUP(G501,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>8956030242988531627</v>
       </c>
       <c r="J501" s="11"/>
@@ -19209,7 +19210,7 @@
         <v>185</v>
       </c>
       <c r="I502" t="str">
-        <f>VLOOKUP(G502,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>8956032186552547741</v>
       </c>
       <c r="J502" s="11"/>
@@ -19237,7 +19238,7 @@
         <v>185</v>
       </c>
       <c r="I503" t="str">
-        <f>VLOOKUP(G503,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>8956032201581692341</v>
       </c>
       <c r="J503" s="11"/>
@@ -19265,7 +19266,7 @@
         <v>185</v>
       </c>
       <c r="I504" t="str">
-        <f>VLOOKUP(G504,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>8956030242988531304</v>
       </c>
       <c r="J504" s="11"/>
@@ -19293,7 +19294,7 @@
         <v>185</v>
       </c>
       <c r="I505" t="str">
-        <f>VLOOKUP(G505,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>8956032186552548186</v>
       </c>
       <c r="J505" s="11"/>
@@ -19321,7 +19322,7 @@
         <v>185</v>
       </c>
       <c r="I506" t="str">
-        <f>VLOOKUP(G506,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>8956032254752139600</v>
       </c>
       <c r="J506" s="11"/>
@@ -19349,7 +19350,7 @@
         <v>185</v>
       </c>
       <c r="I507" t="str">
-        <f>VLOOKUP(G507,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>8956032254752139618</v>
       </c>
       <c r="J507" s="11"/>
@@ -19377,7 +19378,7 @@
         <v>185</v>
       </c>
       <c r="I508" t="str">
-        <f>VLOOKUP(G508,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>8956032201581692366</v>
       </c>
       <c r="J508" s="11"/>
@@ -19405,7 +19406,7 @@
         <v>185</v>
       </c>
       <c r="I509" t="str">
-        <f>VLOOKUP(G509,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>8956032244730755718</v>
       </c>
       <c r="J509" s="11"/>
@@ -19433,7 +19434,7 @@
         <v>185</v>
       </c>
       <c r="I510" t="str">
-        <f>VLOOKUP(G510,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>8956032186552548178</v>
       </c>
       <c r="J510" s="11"/>
@@ -19461,7 +19462,7 @@
         <v>185</v>
       </c>
       <c r="I511" t="e">
-        <f>VLOOKUP(G511,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>#N/A</v>
       </c>
       <c r="J511" s="11"/>
@@ -19489,7 +19490,7 @@
         <v>185</v>
       </c>
       <c r="I512" t="str">
-        <f>VLOOKUP(G512,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>8956032234713494807</v>
       </c>
       <c r="J512" s="11"/>
@@ -19517,7 +19518,7 @@
         <v>185</v>
       </c>
       <c r="I513" t="str">
-        <f>VLOOKUP(G513,D:D,1,0)</f>
+        <f t="shared" si="7"/>
         <v>8956032186552547600</v>
       </c>
       <c r="J513" s="11"/>
@@ -19545,7 +19546,7 @@
         <v>185</v>
       </c>
       <c r="I514" t="str">
-        <f>VLOOKUP(G514,D:D,1,0)</f>
+        <f t="shared" ref="I514:I577" si="8">VLOOKUP(G514,D:D,1,0)</f>
         <v>8956032234712409681</v>
       </c>
       <c r="J514" s="11"/>
@@ -19573,7 +19574,7 @@
         <v>185</v>
       </c>
       <c r="I515" t="e">
-        <f>VLOOKUP(G515,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>#N/A</v>
       </c>
       <c r="J515" s="11"/>
@@ -19604,7 +19605,7 @@
         <v>185</v>
       </c>
       <c r="I516" t="str">
-        <f>VLOOKUP(G516,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>8956032186552548079</v>
       </c>
       <c r="J516" s="11"/>
@@ -19632,7 +19633,7 @@
         <v>185</v>
       </c>
       <c r="I517" t="e">
-        <f>VLOOKUP(G517,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>#N/A</v>
       </c>
       <c r="J517" s="23" t="s">
@@ -19662,7 +19663,7 @@
         <v>185</v>
       </c>
       <c r="I518" t="e">
-        <f>VLOOKUP(G518,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>#N/A</v>
       </c>
       <c r="J518" s="11"/>
@@ -19690,19 +19691,19 @@
         <v>185</v>
       </c>
       <c r="I519" t="str">
-        <f>VLOOKUP(G519,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>8956030205811195431</v>
       </c>
       <c r="J519" s="11"/>
       <c r="N519" s="13"/>
       <c r="P519" s="14"/>
     </row>
-    <row r="520" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A520" s="9" t="s">
+    <row r="520" spans="1:16" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A520" s="3" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B520" s="9" t="s">
         <v>1146</v>
-      </c>
-      <c r="B520" s="3" t="s">
-        <v>1147</v>
       </c>
       <c r="C520" s="3" t="s">
         <v>1148</v>
@@ -19718,7 +19719,7 @@
         <v>185</v>
       </c>
       <c r="I520" t="str">
-        <f>VLOOKUP(G520,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>8956032254752133975</v>
       </c>
       <c r="J520" s="11"/>
@@ -19726,11 +19727,11 @@
       <c r="P520" s="14"/>
     </row>
     <row r="521" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A521" s="16" t="s">
+      <c r="A521" s="17" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B521" s="16" t="s">
         <v>1146</v>
-      </c>
-      <c r="B521" s="17" t="s">
-        <v>1149</v>
       </c>
       <c r="C521" s="17" t="s">
         <v>1150</v>
@@ -19746,19 +19747,19 @@
         <v>185</v>
       </c>
       <c r="I521" t="str">
-        <f>VLOOKUP(G521,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>8956030216926242711</v>
       </c>
       <c r="J521" s="11"/>
       <c r="N521" s="13"/>
       <c r="P521" s="14"/>
     </row>
-    <row r="522" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A522" s="9" t="s">
+    <row r="522" spans="1:16" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A522" s="3" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B522" s="9" t="s">
         <v>1152</v>
-      </c>
-      <c r="B522" s="3" t="s">
-        <v>1153</v>
       </c>
       <c r="C522" s="3" t="s">
         <v>1154</v>
@@ -19774,7 +19775,7 @@
         <v>185</v>
       </c>
       <c r="I522" t="str">
-        <f>VLOOKUP(G522,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>8956032211667084834</v>
       </c>
       <c r="J522" s="11"/>
@@ -19782,11 +19783,11 @@
       <c r="P522" s="14"/>
     </row>
     <row r="523" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A523" s="9" t="s">
+      <c r="A523" s="3" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B523" s="9" t="s">
         <v>1155</v>
-      </c>
-      <c r="B523" s="3" t="s">
-        <v>1156</v>
       </c>
       <c r="C523" s="3" t="s">
         <v>1157</v>
@@ -19802,7 +19803,7 @@
         <v>185</v>
       </c>
       <c r="I523" t="str">
-        <f>VLOOKUP(G523,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>8956032254752133819</v>
       </c>
       <c r="J523" s="23" t="s">
@@ -19812,11 +19813,11 @@
       <c r="P523" s="14"/>
     </row>
     <row r="524" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A524" s="9" t="s">
+      <c r="A524" s="3" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B524" s="9" t="s">
         <v>1155</v>
-      </c>
-      <c r="B524" s="3" t="s">
-        <v>1159</v>
       </c>
       <c r="C524" s="3" t="s">
         <v>1160</v>
@@ -19832,7 +19833,7 @@
         <v>185</v>
       </c>
       <c r="I524" t="str">
-        <f>VLOOKUP(G524,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>8956032211667101497</v>
       </c>
       <c r="J524" s="11"/>
@@ -19840,11 +19841,11 @@
       <c r="P524" s="14"/>
     </row>
     <row r="525" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A525" s="9" t="s">
+      <c r="A525" s="3" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B525" s="9" t="s">
         <v>1155</v>
-      </c>
-      <c r="B525" s="3" t="s">
-        <v>1162</v>
       </c>
       <c r="C525" s="3" t="s">
         <v>1163</v>
@@ -19860,19 +19861,19 @@
         <v>185</v>
       </c>
       <c r="I525" t="str">
-        <f>VLOOKUP(G525,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>8956032254752133967</v>
       </c>
       <c r="J525" s="11"/>
       <c r="N525" s="13"/>
       <c r="P525" s="14"/>
     </row>
-    <row r="526" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A526" s="16" t="s">
+    <row r="526" spans="1:16" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A526" s="17" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B526" s="16" t="s">
         <v>1155</v>
-      </c>
-      <c r="B526" s="17" t="s">
-        <v>1164</v>
       </c>
       <c r="C526" s="17" t="s">
         <v>1165</v>
@@ -19888,19 +19889,19 @@
         <v>185</v>
       </c>
       <c r="I526" t="str">
-        <f>VLOOKUP(G526,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>8956030216926247587</v>
       </c>
       <c r="J526" s="11"/>
       <c r="N526" s="13"/>
       <c r="P526" s="14"/>
     </row>
-    <row r="527" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A527" s="16" t="s">
+    <row r="527" spans="1:16" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A527" s="17" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B527" s="16" t="s">
         <v>1155</v>
-      </c>
-      <c r="B527" s="17" t="s">
-        <v>1167</v>
       </c>
       <c r="C527" s="17" t="s">
         <v>1168</v>
@@ -19916,19 +19917,19 @@
         <v>185</v>
       </c>
       <c r="I527" t="str">
-        <f>VLOOKUP(G527,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>8956030216926242695</v>
       </c>
       <c r="J527" s="11"/>
       <c r="N527" s="13"/>
       <c r="P527" s="14"/>
     </row>
-    <row r="528" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A528" s="16" t="s">
+    <row r="528" spans="1:16" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A528" s="17" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B528" s="16" t="s">
         <v>1155</v>
-      </c>
-      <c r="B528" s="17" t="s">
-        <v>1170</v>
       </c>
       <c r="C528" s="17" t="s">
         <v>1171</v>
@@ -19944,7 +19945,7 @@
         <v>185</v>
       </c>
       <c r="I528" t="str">
-        <f>VLOOKUP(G528,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>8956032254752139907</v>
       </c>
       <c r="J528" s="23" t="s">
@@ -19954,11 +19955,11 @@
       <c r="P528" s="14"/>
     </row>
     <row r="529" spans="1:16" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A529" s="9" t="s">
+      <c r="A529" s="3" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B529" s="9" t="s">
         <v>1155</v>
-      </c>
-      <c r="B529" s="3" t="s">
-        <v>1174</v>
       </c>
       <c r="C529" s="3" t="s">
         <v>1175</v>
@@ -19974,19 +19975,19 @@
         <v>185</v>
       </c>
       <c r="I529" t="str">
-        <f>VLOOKUP(G529,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>8956030216926242828</v>
       </c>
       <c r="J529" s="11"/>
       <c r="N529" s="13"/>
       <c r="P529" s="14"/>
     </row>
-    <row r="530" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A530" s="9" t="s">
+    <row r="530" spans="1:16" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A530" s="3" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B530" s="9" t="s">
         <v>1155</v>
-      </c>
-      <c r="B530" s="3" t="s">
-        <v>1176</v>
       </c>
       <c r="C530" s="3" t="s">
         <v>1177</v>
@@ -20002,7 +20003,7 @@
         <v>185</v>
       </c>
       <c r="I530" t="str">
-        <f>VLOOKUP(G530,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>8956032254752139915</v>
       </c>
       <c r="J530" s="11"/>
@@ -20010,11 +20011,11 @@
       <c r="P530" s="14"/>
     </row>
     <row r="531" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A531" s="16" t="s">
+      <c r="A531" s="17" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B531" s="16" t="s">
         <v>1155</v>
-      </c>
-      <c r="B531" s="17" t="s">
-        <v>1179</v>
       </c>
       <c r="C531" s="17" t="s">
         <v>1180</v>
@@ -20030,7 +20031,7 @@
         <v>185</v>
       </c>
       <c r="I531" t="e">
-        <f>VLOOKUP(G531,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>#N/A</v>
       </c>
       <c r="J531" s="11"/>
@@ -20038,11 +20039,11 @@
       <c r="P531" s="14"/>
     </row>
     <row r="532" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A532" s="9" t="s">
+      <c r="A532" s="3" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B532" s="9" t="s">
         <v>1155</v>
-      </c>
-      <c r="B532" s="3" t="s">
-        <v>1183</v>
       </c>
       <c r="C532" s="3" t="s">
         <v>1184</v>
@@ -20055,7 +20056,7 @@
         <v>185</v>
       </c>
       <c r="I532" t="e">
-        <f>VLOOKUP(G532,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>#N/A</v>
       </c>
       <c r="J532" s="11"/>
@@ -20063,11 +20064,11 @@
       <c r="P532" s="14"/>
     </row>
     <row r="533" spans="1:16" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A533" s="9" t="s">
+      <c r="A533" s="3" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B533" s="9" t="s">
         <v>1155</v>
-      </c>
-      <c r="B533" s="3" t="s">
-        <v>1186</v>
       </c>
       <c r="C533" s="3" t="s">
         <v>1187</v>
@@ -20083,7 +20084,7 @@
         <v>185</v>
       </c>
       <c r="I533" t="str">
-        <f>VLOOKUP(G533,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>8956032254752139923</v>
       </c>
       <c r="J533" s="11"/>
@@ -20091,11 +20092,11 @@
       <c r="P533" s="14"/>
     </row>
     <row r="534" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A534" s="9" t="s">
+      <c r="A534" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B534" s="9" t="s">
         <v>1155</v>
-      </c>
-      <c r="B534" s="3" t="s">
-        <v>1189</v>
       </c>
       <c r="C534" s="3" t="s">
         <v>1190</v>
@@ -20111,7 +20112,7 @@
         <v>185</v>
       </c>
       <c r="I534" t="str">
-        <f>VLOOKUP(G534,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>8956032211667101588</v>
       </c>
       <c r="J534" s="21" t="s">
@@ -20121,11 +20122,11 @@
       <c r="P534" s="14"/>
     </row>
     <row r="535" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A535" s="9" t="s">
+      <c r="A535" s="3" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B535" s="9" t="s">
         <v>1155</v>
-      </c>
-      <c r="B535" s="3" t="s">
-        <v>1193</v>
       </c>
       <c r="C535" s="3" t="s">
         <v>1194</v>
@@ -20141,7 +20142,7 @@
         <v>185</v>
       </c>
       <c r="I535" t="e">
-        <f>VLOOKUP(G535,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>#N/A</v>
       </c>
       <c r="J535" s="11"/>
@@ -20149,11 +20150,11 @@
       <c r="P535" s="14"/>
     </row>
     <row r="536" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A536" s="9" t="s">
+      <c r="A536" s="3" t="s">
+        <v>1196</v>
+      </c>
+      <c r="B536" s="9" t="s">
         <v>1155</v>
-      </c>
-      <c r="B536" s="3" t="s">
-        <v>1196</v>
       </c>
       <c r="C536" s="3" t="s">
         <v>1197</v>
@@ -20169,7 +20170,7 @@
         <v>185</v>
       </c>
       <c r="I536" t="str">
-        <f>VLOOKUP(G536,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>8956032211667084792</v>
       </c>
       <c r="J536" s="11"/>
@@ -20177,11 +20178,11 @@
       <c r="P536" s="14"/>
     </row>
     <row r="537" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A537" s="9" t="s">
+      <c r="A537" s="3" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B537" s="9" t="s">
         <v>1152</v>
-      </c>
-      <c r="B537" s="3" t="s">
-        <v>1198</v>
       </c>
       <c r="C537" s="3"/>
       <c r="D537" s="3" t="s">
@@ -20195,7 +20196,7 @@
         <v>185</v>
       </c>
       <c r="I537" t="str">
-        <f>VLOOKUP(G537,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>8956030216926248163</v>
       </c>
       <c r="J537" s="21" t="s">
@@ -20205,11 +20206,11 @@
       <c r="P537" s="14"/>
     </row>
     <row r="538" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A538" s="9" t="s">
+      <c r="A538" s="3" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B538" s="9" t="s">
         <v>1152</v>
-      </c>
-      <c r="B538" s="3" t="s">
-        <v>1200</v>
       </c>
       <c r="C538" s="3" t="s">
         <v>1201</v>
@@ -20225,7 +20226,7 @@
         <v>185</v>
       </c>
       <c r="I538" t="str">
-        <f>VLOOKUP(G538,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>8956030216921414240</v>
       </c>
       <c r="J538" s="11"/>
@@ -20233,11 +20234,11 @@
       <c r="P538" s="14"/>
     </row>
     <row r="539" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A539" s="9" t="s">
+      <c r="A539" s="3" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B539" s="9" t="s">
         <v>1152</v>
-      </c>
-      <c r="B539" s="3" t="s">
-        <v>1203</v>
       </c>
       <c r="C539" s="3"/>
       <c r="D539" s="3" t="s">
@@ -20251,7 +20252,7 @@
         <v>185</v>
       </c>
       <c r="I539" t="str">
-        <f>VLOOKUP(G539,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>8956034212030553974</v>
       </c>
       <c r="J539" s="21" t="s">
@@ -20261,11 +20262,11 @@
       <c r="P539" s="14"/>
     </row>
     <row r="540" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A540" s="9" t="s">
+      <c r="A540" s="3" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B540" s="9" t="s">
         <v>1152</v>
-      </c>
-      <c r="B540" s="3" t="s">
-        <v>1205</v>
       </c>
       <c r="C540" s="3"/>
       <c r="D540" s="3" t="s">
@@ -20279,7 +20280,7 @@
         <v>185</v>
       </c>
       <c r="I540" t="str">
-        <f>VLOOKUP(G540,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>8956030216926248098</v>
       </c>
       <c r="J540" s="21" t="s">
@@ -20289,11 +20290,11 @@
       <c r="P540" s="14"/>
     </row>
     <row r="541" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A541" s="9" t="s">
+      <c r="A541" s="3" t="s">
+        <v>1206</v>
+      </c>
+      <c r="B541" s="9" t="s">
         <v>1152</v>
-      </c>
-      <c r="B541" s="3" t="s">
-        <v>1206</v>
       </c>
       <c r="C541" s="3" t="s">
         <v>1207</v>
@@ -20309,7 +20310,7 @@
         <v>185</v>
       </c>
       <c r="I541" t="e">
-        <f>VLOOKUP(G541,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>#N/A</v>
       </c>
       <c r="J541" s="11"/>
@@ -20317,11 +20318,11 @@
       <c r="P541" s="14"/>
     </row>
     <row r="542" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A542" s="9" t="s">
+      <c r="A542" s="3" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B542" s="9" t="s">
         <v>1152</v>
-      </c>
-      <c r="B542" s="3" t="s">
-        <v>1209</v>
       </c>
       <c r="C542" s="3" t="s">
         <v>1210</v>
@@ -20337,7 +20338,7 @@
         <v>185</v>
       </c>
       <c r="I542" t="str">
-        <f>VLOOKUP(G542,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>8956032211667084750</v>
       </c>
       <c r="J542" s="11"/>
@@ -20345,11 +20346,11 @@
       <c r="P542" s="14"/>
     </row>
     <row r="543" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A543" s="9" t="s">
+      <c r="A543" s="3" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B543" s="9" t="s">
         <v>1152</v>
-      </c>
-      <c r="B543" s="3" t="s">
-        <v>1211</v>
       </c>
       <c r="C543" s="3" t="s">
         <v>1212</v>
@@ -20365,7 +20366,7 @@
         <v>185</v>
       </c>
       <c r="I543" t="str">
-        <f>VLOOKUP(G543,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>8956032211667100937</v>
       </c>
       <c r="J543" s="21" t="s">
@@ -20375,11 +20376,11 @@
       <c r="P543" s="14"/>
     </row>
     <row r="544" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A544" s="9" t="s">
+      <c r="A544" s="3" t="s">
+        <v>1215</v>
+      </c>
+      <c r="B544" s="9" t="s">
         <v>1152</v>
-      </c>
-      <c r="B544" s="3" t="s">
-        <v>1215</v>
       </c>
       <c r="C544" s="3" t="s">
         <v>1216</v>
@@ -20395,7 +20396,7 @@
         <v>185</v>
       </c>
       <c r="I544" t="str">
-        <f>VLOOKUP(G544,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>8956032211667084776</v>
       </c>
       <c r="J544" s="11"/>
@@ -20403,11 +20404,11 @@
       <c r="P544" s="14"/>
     </row>
     <row r="545" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A545" s="9" t="s">
+      <c r="A545" s="3" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B545" s="9" t="s">
         <v>1152</v>
-      </c>
-      <c r="B545" s="3" t="s">
-        <v>1217</v>
       </c>
       <c r="C545" s="3" t="s">
         <v>1218</v>
@@ -20423,7 +20424,7 @@
         <v>185</v>
       </c>
       <c r="I545" t="str">
-        <f>VLOOKUP(G545,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>8956032244730755981</v>
       </c>
       <c r="J545" s="21" t="s">
@@ -20433,11 +20434,11 @@
       <c r="P545" s="14"/>
     </row>
     <row r="546" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A546" s="9" t="s">
+      <c r="A546" s="3" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B546" s="9" t="s">
         <v>1152</v>
-      </c>
-      <c r="B546" s="3" t="s">
-        <v>1220</v>
       </c>
       <c r="C546" s="3" t="s">
         <v>1221</v>
@@ -20453,7 +20454,7 @@
         <v>185</v>
       </c>
       <c r="I546" t="str">
-        <f>VLOOKUP(G546,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>8956032211667084859</v>
       </c>
       <c r="J546" s="21" t="s">
@@ -20463,11 +20464,11 @@
       <c r="P546" s="14"/>
     </row>
     <row r="547" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A547" s="9" t="s">
+      <c r="A547" s="3" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B547" s="9" t="s">
         <v>1152</v>
-      </c>
-      <c r="B547" s="3" t="s">
-        <v>1223</v>
       </c>
       <c r="C547" s="3" t="s">
         <v>1224</v>
@@ -20483,19 +20484,19 @@
         <v>185</v>
       </c>
       <c r="I547" t="str">
-        <f>VLOOKUP(G547,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>8956032211667084842</v>
       </c>
       <c r="J547" s="11"/>
       <c r="N547" s="13"/>
       <c r="P547" s="14"/>
     </row>
-    <row r="548" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A548" s="9" t="s">
+    <row r="548" spans="1:16" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A548" s="3" t="s">
+        <v>1226</v>
+      </c>
+      <c r="B548" s="9" t="s">
         <v>1152</v>
-      </c>
-      <c r="B548" s="3" t="s">
-        <v>1226</v>
       </c>
       <c r="C548" s="3" t="s">
         <v>1227</v>
@@ -20511,7 +20512,7 @@
         <v>185</v>
       </c>
       <c r="I548" t="e">
-        <f>VLOOKUP(G548,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>#N/A</v>
       </c>
       <c r="J548" s="11"/>
@@ -20519,11 +20520,11 @@
       <c r="P548" s="14"/>
     </row>
     <row r="549" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A549" s="16" t="s">
+      <c r="A549" s="17" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B549" s="16" t="s">
         <v>1152</v>
-      </c>
-      <c r="B549" s="17" t="s">
-        <v>1229</v>
       </c>
       <c r="C549" s="17" t="s">
         <v>1230</v>
@@ -20539,7 +20540,7 @@
         <v>185</v>
       </c>
       <c r="I549" t="str">
-        <f>VLOOKUP(G549,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>8956032211667084461</v>
       </c>
       <c r="J549" s="23" t="s">
@@ -20549,11 +20550,11 @@
       <c r="P549" s="14"/>
     </row>
     <row r="550" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A550" s="16" t="s">
+      <c r="A550" s="17" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B550" s="16" t="s">
         <v>1152</v>
-      </c>
-      <c r="B550" s="17" t="s">
-        <v>1232</v>
       </c>
       <c r="C550" s="17" t="s">
         <v>1233</v>
@@ -20569,7 +20570,7 @@
         <v>185</v>
       </c>
       <c r="I550" t="str">
-        <f>VLOOKUP(G550,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>8956030216926380487</v>
       </c>
       <c r="J550" s="11"/>
@@ -20577,11 +20578,11 @@
       <c r="P550" s="14"/>
     </row>
     <row r="551" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A551" s="9" t="s">
+      <c r="A551" s="3" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B551" s="9" t="s">
         <v>1152</v>
-      </c>
-      <c r="B551" s="3" t="s">
-        <v>1234</v>
       </c>
       <c r="C551" s="3" t="s">
         <v>1235</v>
@@ -20597,7 +20598,7 @@
         <v>185</v>
       </c>
       <c r="I551" t="str">
-        <f>VLOOKUP(G551,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>8956030216926242687</v>
       </c>
       <c r="J551" s="21" t="s">
@@ -20607,11 +20608,11 @@
       <c r="P551" s="14"/>
     </row>
     <row r="552" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A552" s="9" t="s">
+      <c r="A552" s="3" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B552" s="9" t="s">
         <v>1152</v>
-      </c>
-      <c r="B552" s="3" t="s">
-        <v>1237</v>
       </c>
       <c r="C552" s="3"/>
       <c r="D552" s="3" t="s">
@@ -20625,7 +20626,7 @@
         <v>185</v>
       </c>
       <c r="I552" t="str">
-        <f>VLOOKUP(G552,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>8956030221943028200</v>
       </c>
       <c r="J552" s="21" t="s">
@@ -20635,11 +20636,11 @@
       <c r="P552" s="14"/>
     </row>
     <row r="553" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A553" s="9" t="s">
+      <c r="A553" s="3" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B553" s="9" t="s">
         <v>1239</v>
-      </c>
-      <c r="B553" s="3" t="s">
-        <v>1240</v>
       </c>
       <c r="C553" s="3" t="s">
         <v>1241</v>
@@ -20655,19 +20656,19 @@
         <v>185</v>
       </c>
       <c r="I553" t="str">
-        <f>VLOOKUP(G553,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>8956032254752139931</v>
       </c>
       <c r="J553" s="11"/>
       <c r="N553" s="13"/>
       <c r="P553" s="14"/>
     </row>
-    <row r="554" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A554" s="9" t="s">
+    <row r="554" spans="1:16" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A554" s="3" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B554" s="9" t="s">
         <v>1239</v>
-      </c>
-      <c r="B554" s="3" t="s">
-        <v>1242</v>
       </c>
       <c r="C554" s="3" t="s">
         <v>1243</v>
@@ -20683,7 +20684,7 @@
         <v>185</v>
       </c>
       <c r="I554" t="str">
-        <f>VLOOKUP(G554,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>8956032211667084560</v>
       </c>
       <c r="J554" s="21" t="s">
@@ -20693,11 +20694,11 @@
       <c r="P554" s="14"/>
     </row>
     <row r="555" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A555" s="9" t="s">
+      <c r="A555" s="3" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B555" s="9" t="s">
         <v>1152</v>
-      </c>
-      <c r="B555" s="3" t="s">
-        <v>1245</v>
       </c>
       <c r="C555" s="3"/>
       <c r="D555" s="3" t="s">
@@ -20711,7 +20712,7 @@
         <v>185</v>
       </c>
       <c r="I555" t="str">
-        <f>VLOOKUP(G555,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>8956032211667084594</v>
       </c>
       <c r="J555" s="21" t="s">
@@ -20721,11 +20722,11 @@
       <c r="P555" s="14"/>
     </row>
     <row r="556" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A556" s="9" t="s">
+      <c r="A556" s="3" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B556" s="9" t="s">
         <v>1152</v>
-      </c>
-      <c r="B556" s="3" t="s">
-        <v>1247</v>
       </c>
       <c r="C556" s="3"/>
       <c r="D556" s="3" t="s">
@@ -20739,7 +20740,7 @@
         <v>185</v>
       </c>
       <c r="I556" t="str">
-        <f>VLOOKUP(G556,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>8956030215874997466</v>
       </c>
       <c r="J556" s="11"/>
@@ -20747,11 +20748,11 @@
       <c r="P556" s="14"/>
     </row>
     <row r="557" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A557" s="9" t="s">
+      <c r="A557" s="3" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B557" s="9" t="s">
         <v>1152</v>
-      </c>
-      <c r="B557" s="3" t="s">
-        <v>1205</v>
       </c>
       <c r="C557" s="3"/>
       <c r="D557" s="3" t="s">
@@ -20765,7 +20766,7 @@
         <v>185</v>
       </c>
       <c r="I557" t="str">
-        <f>VLOOKUP(G557,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>8956032211667084586</v>
       </c>
       <c r="J557" s="11"/>
@@ -20773,11 +20774,11 @@
       <c r="P557" s="14"/>
     </row>
     <row r="558" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A558" s="9" t="s">
+      <c r="A558" s="3" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B558" s="9" t="s">
         <v>1152</v>
-      </c>
-      <c r="B558" s="3" t="s">
-        <v>1250</v>
       </c>
       <c r="C558" s="3"/>
       <c r="D558" s="3" t="s">
@@ -20791,7 +20792,7 @@
         <v>185</v>
       </c>
       <c r="I558" t="str">
-        <f>VLOOKUP(G558,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>8956030216926241515</v>
       </c>
       <c r="J558" s="21" t="s">
@@ -20801,11 +20802,11 @@
       <c r="P558" s="14"/>
     </row>
     <row r="559" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A559" s="9" t="s">
+      <c r="A559" s="3" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B559" s="9" t="s">
         <v>1152</v>
-      </c>
-      <c r="B559" s="3" t="s">
-        <v>1252</v>
       </c>
       <c r="C559" s="3"/>
       <c r="D559" s="3" t="s">
@@ -20819,7 +20820,7 @@
         <v>185</v>
       </c>
       <c r="I559" t="str">
-        <f>VLOOKUP(G559,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>8956030242988531387</v>
       </c>
       <c r="J559" s="11"/>
@@ -20827,11 +20828,11 @@
       <c r="P559" s="14"/>
     </row>
     <row r="560" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A560" s="9" t="s">
+      <c r="A560" s="3" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B560" s="9" t="s">
         <v>1155</v>
-      </c>
-      <c r="B560" s="3" t="s">
-        <v>1253</v>
       </c>
       <c r="C560" s="3"/>
       <c r="D560" s="3" t="s">
@@ -20845,7 +20846,7 @@
         <v>185</v>
       </c>
       <c r="I560" t="str">
-        <f>VLOOKUP(G560,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>8956030242988505456</v>
       </c>
       <c r="J560" s="11"/>
@@ -20853,11 +20854,11 @@
       <c r="P560" s="14"/>
     </row>
     <row r="561" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A561" s="16" t="s">
+      <c r="A561" s="17" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B561" s="16" t="s">
         <v>1155</v>
-      </c>
-      <c r="B561" s="17" t="s">
-        <v>1255</v>
       </c>
       <c r="C561" s="17" t="s">
         <v>1256</v>
@@ -20873,7 +20874,7 @@
         <v>185</v>
       </c>
       <c r="I561" t="str">
-        <f>VLOOKUP(G561,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>8956034212030554105</v>
       </c>
       <c r="J561" s="11"/>
@@ -20881,11 +20882,11 @@
       <c r="P561" s="14"/>
     </row>
     <row r="562" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A562" s="9" t="s">
+      <c r="A562" s="3" t="s">
+        <v>1258</v>
+      </c>
+      <c r="B562" s="9" t="s">
         <v>1155</v>
-      </c>
-      <c r="B562" s="3" t="s">
-        <v>1258</v>
       </c>
       <c r="C562" s="3" t="s">
         <v>1259</v>
@@ -20901,7 +20902,7 @@
         <v>185</v>
       </c>
       <c r="I562" t="str">
-        <f>VLOOKUP(G562,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>8956032211667101448</v>
       </c>
       <c r="J562" s="11"/>
@@ -20909,11 +20910,11 @@
       <c r="P562" s="14"/>
     </row>
     <row r="563" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A563" s="9" t="s">
+      <c r="A563" s="3" t="s">
+        <v>1260</v>
+      </c>
+      <c r="B563" s="9" t="s">
         <v>1152</v>
-      </c>
-      <c r="B563" s="3" t="s">
-        <v>1260</v>
       </c>
       <c r="C563" s="3" t="s">
         <v>1261</v>
@@ -20929,7 +20930,7 @@
         <v>185</v>
       </c>
       <c r="I563" t="str">
-        <f>VLOOKUP(G563,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>8956030242988531403</v>
       </c>
       <c r="J563" s="11"/>
@@ -20937,11 +20938,11 @@
       <c r="P563" s="14"/>
     </row>
     <row r="564" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A564" s="9" t="s">
+      <c r="A564" s="3" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B564" s="9" t="s">
         <v>1152</v>
-      </c>
-      <c r="B564" s="3" t="s">
-        <v>1262</v>
       </c>
       <c r="C564" s="3"/>
       <c r="D564" s="3" t="s">
@@ -20955,7 +20956,7 @@
         <v>185</v>
       </c>
       <c r="I564" t="str">
-        <f>VLOOKUP(G564,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>8956030216926248148</v>
       </c>
       <c r="J564" s="21" t="s">
@@ -20965,11 +20966,11 @@
       <c r="P564" s="14"/>
     </row>
     <row r="565" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A565" s="9" t="s">
+      <c r="A565" s="3" t="s">
+        <v>1264</v>
+      </c>
+      <c r="B565" s="9" t="s">
         <v>1146</v>
-      </c>
-      <c r="B565" s="3" t="s">
-        <v>1264</v>
       </c>
       <c r="C565" s="3"/>
       <c r="D565" s="3" t="s">
@@ -20983,19 +20984,19 @@
         <v>185</v>
       </c>
       <c r="I565" t="e">
-        <f>VLOOKUP(G565,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>#N/A</v>
       </c>
       <c r="J565" s="11"/>
       <c r="N565" s="13"/>
       <c r="P565" s="14"/>
     </row>
-    <row r="566" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A566" s="16" t="s">
+    <row r="566" spans="1:16" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A566" s="17" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B566" s="16" t="s">
         <v>1239</v>
-      </c>
-      <c r="B566" s="17" t="s">
-        <v>1267</v>
       </c>
       <c r="C566" s="17" t="s">
         <v>1268</v>
@@ -21011,7 +21012,7 @@
         <v>185</v>
       </c>
       <c r="I566" t="str">
-        <f>VLOOKUP(G566,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>8956032211667084628</v>
       </c>
       <c r="J566" s="11"/>
@@ -21019,11 +21020,11 @@
       <c r="P566" s="14"/>
     </row>
     <row r="567" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A567" s="25" t="s">
+      <c r="A567" s="26" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B567" s="25" t="s">
         <v>1239</v>
-      </c>
-      <c r="B567" s="26" t="s">
-        <v>1269</v>
       </c>
       <c r="C567" s="27" t="s">
         <v>1270</v>
@@ -21039,7 +21040,7 @@
         <v>185</v>
       </c>
       <c r="I567" t="str">
-        <f>VLOOKUP(G567,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>8956032211667084651</v>
       </c>
       <c r="J567" s="11"/>
@@ -21047,11 +21048,11 @@
       <c r="P567" s="14"/>
     </row>
     <row r="568" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A568" s="18" t="s">
+      <c r="A568" s="28" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B568" s="18" t="s">
         <v>1155</v>
-      </c>
-      <c r="B568" s="28" t="s">
-        <v>1271</v>
       </c>
       <c r="C568" s="19"/>
       <c r="D568" s="3" t="s">
@@ -21065,7 +21066,7 @@
         <v>185</v>
       </c>
       <c r="I568" t="e">
-        <f>VLOOKUP(G568,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>#N/A</v>
       </c>
       <c r="J568" s="21" t="s">
@@ -21075,11 +21076,11 @@
       <c r="P568" s="14"/>
     </row>
     <row r="569" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A569" s="9" t="s">
+      <c r="A569" s="26" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B569" s="9" t="s">
         <v>1155</v>
-      </c>
-      <c r="B569" s="26" t="s">
-        <v>1275</v>
       </c>
       <c r="C569" s="27" t="s">
         <v>1276</v>
@@ -21095,7 +21096,7 @@
         <v>185</v>
       </c>
       <c r="I569" t="str">
-        <f>VLOOKUP(G569,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>8956030216926241622</v>
       </c>
       <c r="J569" s="21" t="s">
@@ -21105,11 +21106,11 @@
       <c r="P569" s="14"/>
     </row>
     <row r="570" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A570" s="18" t="s">
+      <c r="A570" s="28" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B570" s="18" t="s">
         <v>1155</v>
-      </c>
-      <c r="B570" s="28" t="s">
-        <v>1275</v>
       </c>
       <c r="C570" s="19"/>
       <c r="D570" s="3" t="s">
@@ -21123,7 +21124,7 @@
         <v>185</v>
       </c>
       <c r="I570" t="str">
-        <f>VLOOKUP(G570,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>8956032254752139956</v>
       </c>
       <c r="J570" s="21" t="s">
@@ -21133,11 +21134,11 @@
       <c r="P570" s="14"/>
     </row>
     <row r="571" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A571" s="18" t="s">
+      <c r="A571" s="28" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B571" s="18" t="s">
         <v>1155</v>
-      </c>
-      <c r="B571" s="28" t="s">
-        <v>1275</v>
       </c>
       <c r="C571" s="19"/>
       <c r="D571" s="3" t="s">
@@ -21151,7 +21152,7 @@
         <v>185</v>
       </c>
       <c r="I571" t="str">
-        <f>VLOOKUP(G571,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>8956034212030554287</v>
       </c>
       <c r="J571" s="21" t="s">
@@ -21161,11 +21162,11 @@
       <c r="P571" s="14"/>
     </row>
     <row r="572" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A572" s="18" t="s">
+      <c r="A572" s="19" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B572" s="18" t="s">
         <v>1283</v>
-      </c>
-      <c r="B572" s="19" t="s">
-        <v>1284</v>
       </c>
       <c r="C572" s="19" t="s">
         <v>1285</v>
@@ -21181,7 +21182,7 @@
         <v>185</v>
       </c>
       <c r="I572" t="str">
-        <f>VLOOKUP(G572,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>8956032254752140004</v>
       </c>
       <c r="J572" s="11"/>
@@ -21189,11 +21190,11 @@
       <c r="P572" s="14"/>
     </row>
     <row r="573" spans="1:16" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A573" s="9" t="s">
+      <c r="A573" s="3" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B573" s="9" t="s">
         <v>1283</v>
-      </c>
-      <c r="B573" s="3" t="s">
-        <v>1287</v>
       </c>
       <c r="C573" s="3" t="s">
         <v>1288</v>
@@ -21209,7 +21210,7 @@
         <v>185</v>
       </c>
       <c r="I573" t="str">
-        <f>VLOOKUP(G573,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>8956032254752139998</v>
       </c>
       <c r="J573" s="21" t="s">
@@ -21219,11 +21220,11 @@
       <c r="P573" s="14"/>
     </row>
     <row r="574" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A574" s="9" t="s">
+      <c r="A574" s="3" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B574" s="9" t="s">
         <v>1283</v>
-      </c>
-      <c r="B574" s="3" t="s">
-        <v>1291</v>
       </c>
       <c r="C574" s="3" t="s">
         <v>1292</v>
@@ -21239,19 +21240,19 @@
         <v>185</v>
       </c>
       <c r="I574" t="e">
-        <f>VLOOKUP(G574,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>#N/A</v>
       </c>
       <c r="J574" s="11"/>
       <c r="N574" s="13"/>
       <c r="P574" s="14"/>
     </row>
-    <row r="575" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A575" s="9" t="s">
+    <row r="575" spans="1:16" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A575" s="3" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B575" s="9" t="s">
         <v>1283</v>
-      </c>
-      <c r="B575" s="3" t="s">
-        <v>1294</v>
       </c>
       <c r="C575" s="3" t="s">
         <v>1292</v>
@@ -21267,7 +21268,7 @@
         <v>185</v>
       </c>
       <c r="I575" t="str">
-        <f>VLOOKUP(G575,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>8956032254752140020</v>
       </c>
       <c r="J575" s="23" t="s">
@@ -21277,11 +21278,11 @@
       <c r="P575" s="14"/>
     </row>
     <row r="576" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A576" s="9" t="s">
+      <c r="A576" s="3" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B576" s="9" t="s">
         <v>1239</v>
-      </c>
-      <c r="B576" s="3" t="s">
-        <v>1297</v>
       </c>
       <c r="C576" s="3" t="s">
         <v>1298</v>
@@ -21297,7 +21298,7 @@
         <v>185</v>
       </c>
       <c r="I576" t="str">
-        <f>VLOOKUP(G576,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>8956032244730755874</v>
       </c>
       <c r="J576" s="11"/>
@@ -21308,12 +21309,12 @@
       <c r="A577" s="19" t="s">
         <v>1299</v>
       </c>
-      <c r="B577" s="19" t="s">
-        <v>1300</v>
+      <c r="B577" s="18" t="s">
+        <v>1155</v>
       </c>
       <c r="C577" s="19"/>
       <c r="D577" s="3" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="F577" s="10"/>
       <c r="G577" s="11" t="s">
@@ -21323,7 +21324,7 @@
         <v>185</v>
       </c>
       <c r="I577" t="str">
-        <f>VLOOKUP(G577,D:D,1,0)</f>
+        <f t="shared" si="8"/>
         <v>8956032254752140038</v>
       </c>
       <c r="J577" s="11"/>
@@ -21335,13 +21336,13 @@
         <v>1302</v>
       </c>
       <c r="B578" s="3" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C578" s="3" t="s">
         <v>1303</v>
       </c>
-      <c r="C578" s="3" t="s">
+      <c r="D578" s="3" t="s">
         <v>1304</v>
-      </c>
-      <c r="D578" s="3" t="s">
-        <v>1305</v>
       </c>
       <c r="F578" s="10"/>
       <c r="G578" s="11" t="s">
@@ -21351,7 +21352,7 @@
         <v>185</v>
       </c>
       <c r="I578" t="str">
-        <f>VLOOKUP(G578,D:D,1,0)</f>
+        <f t="shared" ref="I578:I641" si="9">VLOOKUP(G578,D:D,1,0)</f>
         <v>8956032211667084529</v>
       </c>
       <c r="J578" s="11"/>
@@ -21360,16 +21361,16 @@
     </row>
     <row r="579" spans="1:16" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A579" s="3" t="s">
+        <v>1305</v>
+      </c>
+      <c r="B579" s="3" t="s">
         <v>1283</v>
       </c>
-      <c r="B579" s="3" t="s">
+      <c r="C579" s="3" t="s">
         <v>1306</v>
       </c>
-      <c r="C579" s="3" t="s">
+      <c r="D579" s="3" t="s">
         <v>1307</v>
-      </c>
-      <c r="D579" s="3" t="s">
-        <v>1308</v>
       </c>
       <c r="F579" s="10"/>
       <c r="G579" s="11" t="s">
@@ -21379,7 +21380,7 @@
         <v>185</v>
       </c>
       <c r="I579" t="str">
-        <f>VLOOKUP(G579,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>8956030216926242604</v>
       </c>
       <c r="J579" s="11"/>
@@ -21387,11 +21388,11 @@
       <c r="P579" s="14"/>
     </row>
     <row r="580" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A580" s="9" t="s">
+      <c r="A580" s="3" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B580" s="9" t="s">
         <v>1239</v>
-      </c>
-      <c r="B580" s="3" t="s">
-        <v>1297</v>
       </c>
       <c r="C580" s="3" t="s">
         <v>1298</v>
@@ -21407,25 +21408,25 @@
         <v>185</v>
       </c>
       <c r="I580" t="str">
-        <f>VLOOKUP(G580,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>8956032211667101596</v>
       </c>
       <c r="J580" s="11"/>
       <c r="N580" s="13"/>
       <c r="P580" s="14"/>
     </row>
-    <row r="581" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A581" s="9" t="s">
-        <v>1302</v>
-      </c>
-      <c r="B581" s="3" t="s">
-        <v>1309</v>
+    <row r="581" spans="1:16" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A581" s="3" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B581" s="9" t="s">
+        <v>1301</v>
       </c>
       <c r="C581" s="3" t="s">
         <v>883</v>
       </c>
       <c r="D581" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="F581" s="10"/>
       <c r="G581" s="11" t="s">
@@ -21435,7 +21436,7 @@
         <v>185</v>
       </c>
       <c r="I581" t="str">
-        <f>VLOOKUP(G581,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>8956032211667101513</v>
       </c>
       <c r="J581" s="11"/>
@@ -21444,10 +21445,10 @@
     </row>
     <row r="582" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A582" s="17" t="s">
-        <v>1302</v>
+        <v>1310</v>
       </c>
       <c r="B582" s="17" t="s">
-        <v>1311</v>
+        <v>1301</v>
       </c>
       <c r="C582" s="17"/>
       <c r="D582" s="3" t="s">
@@ -21455,13 +21456,13 @@
       </c>
       <c r="F582" s="10"/>
       <c r="G582" s="11" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="H582" s="15" t="s">
         <v>185</v>
       </c>
       <c r="I582" t="e">
-        <f>VLOOKUP(G582,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>#N/A</v>
       </c>
       <c r="J582" s="11"/>
@@ -21469,11 +21470,11 @@
       <c r="P582" s="14"/>
     </row>
     <row r="583" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A583" s="9" t="s">
+      <c r="A583" s="3" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B583" s="9" t="s">
         <v>1155</v>
-      </c>
-      <c r="B583" s="3" t="s">
-        <v>1313</v>
       </c>
       <c r="C583" s="3" t="s">
         <v>883</v>
@@ -21489,7 +21490,7 @@
         <v>185</v>
       </c>
       <c r="I583" t="str">
-        <f>VLOOKUP(G583,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>8956032244730755965</v>
       </c>
       <c r="J583" s="11"/>
@@ -21497,11 +21498,11 @@
       <c r="P583" s="14"/>
     </row>
     <row r="584" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A584" s="9" t="s">
+      <c r="A584" s="3" t="s">
+        <v>1313</v>
+      </c>
+      <c r="B584" s="9" t="s">
         <v>1155</v>
-      </c>
-      <c r="B584" s="3" t="s">
-        <v>1314</v>
       </c>
       <c r="C584" s="3" t="s">
         <v>894</v>
@@ -21517,7 +21518,7 @@
         <v>185</v>
       </c>
       <c r="I584" t="str">
-        <f>VLOOKUP(G584,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>8956030216921418399</v>
       </c>
       <c r="J584" s="11"/>
@@ -21525,11 +21526,11 @@
       <c r="P584" s="14"/>
     </row>
     <row r="585" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A585" s="9" t="s">
+      <c r="A585" s="3" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B585" s="9" t="s">
         <v>1239</v>
-      </c>
-      <c r="B585" s="3" t="s">
-        <v>1315</v>
       </c>
       <c r="C585" s="3"/>
       <c r="D585" s="3" t="s">
@@ -21543,7 +21544,7 @@
         <v>185</v>
       </c>
       <c r="I585" t="str">
-        <f>VLOOKUP(G585,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>8956032211667101620</v>
       </c>
       <c r="J585" s="11"/>
@@ -21551,11 +21552,11 @@
       <c r="P585" s="14"/>
     </row>
     <row r="586" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A586" s="9" t="s">
+      <c r="A586" s="3" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B586" s="9" t="s">
         <v>1239</v>
-      </c>
-      <c r="B586" s="3" t="s">
-        <v>1315</v>
       </c>
       <c r="C586" s="3"/>
       <c r="D586" s="3" t="s">
@@ -21569,7 +21570,7 @@
         <v>185</v>
       </c>
       <c r="I586" t="str">
-        <f>VLOOKUP(G586,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>8956030242988532898</v>
       </c>
       <c r="J586" s="11"/>
@@ -21577,11 +21578,11 @@
       <c r="P586" s="14"/>
     </row>
     <row r="587" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A587" s="9" t="s">
+      <c r="A587" s="3" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B587" s="9" t="s">
         <v>1239</v>
-      </c>
-      <c r="B587" s="3" t="s">
-        <v>1315</v>
       </c>
       <c r="C587" s="3"/>
       <c r="D587" s="3" t="s">
@@ -21589,27 +21590,27 @@
       </c>
       <c r="F587" s="10"/>
       <c r="G587" s="20" t="s">
+        <v>1315</v>
+      </c>
+      <c r="H587" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="I587" t="str">
+        <f t="shared" si="9"/>
+        <v>8956032254752139964</v>
+      </c>
+      <c r="J587" s="23" t="s">
         <v>1316</v>
-      </c>
-      <c r="H587" s="22" t="s">
-        <v>185</v>
-      </c>
-      <c r="I587" t="str">
-        <f>VLOOKUP(G587,D:D,1,0)</f>
-        <v>8956032254752139964</v>
-      </c>
-      <c r="J587" s="23" t="s">
-        <v>1317</v>
       </c>
       <c r="N587" s="13"/>
       <c r="P587" s="14"/>
     </row>
     <row r="588" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A588" s="9" t="s">
+      <c r="A588" s="3" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B588" s="9" t="s">
         <v>1239</v>
-      </c>
-      <c r="B588" s="3" t="s">
-        <v>1318</v>
       </c>
       <c r="C588" s="3"/>
       <c r="D588" s="3" t="s">
@@ -21623,7 +21624,7 @@
         <v>185</v>
       </c>
       <c r="I588" t="str">
-        <f>VLOOKUP(G588,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>8956030242988505464</v>
       </c>
       <c r="J588" s="11"/>
@@ -21631,11 +21632,11 @@
       <c r="P588" s="14"/>
     </row>
     <row r="589" spans="1:16" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A589" s="9" t="s">
+      <c r="A589" s="3" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B589" s="9" t="s">
         <v>1239</v>
-      </c>
-      <c r="B589" s="3" t="s">
-        <v>1319</v>
       </c>
       <c r="C589" s="3"/>
       <c r="D589" s="3" t="s">
@@ -21649,7 +21650,7 @@
         <v>185</v>
       </c>
       <c r="I589" t="str">
-        <f>VLOOKUP(G589,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>8956030216926242810</v>
       </c>
       <c r="J589" s="11"/>
@@ -21657,11 +21658,11 @@
       <c r="P589" s="14"/>
     </row>
     <row r="590" spans="1:16" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A590" s="9" t="s">
+      <c r="A590" s="3" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B590" s="9" t="s">
         <v>1239</v>
-      </c>
-      <c r="B590" s="3" t="s">
-        <v>1319</v>
       </c>
       <c r="C590" s="3"/>
       <c r="D590" s="3" t="s">
@@ -21669,13 +21670,13 @@
       </c>
       <c r="F590" s="10"/>
       <c r="G590" s="11" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="H590" s="15" t="s">
         <v>185</v>
       </c>
       <c r="I590" t="str">
-        <f>VLOOKUP(G590,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>8956032254752140053</v>
       </c>
       <c r="J590" s="11"/>
@@ -21683,11 +21684,11 @@
       <c r="P590" s="14"/>
     </row>
     <row r="591" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A591" s="9" t="s">
+      <c r="A591" s="3" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B591" s="9" t="s">
         <v>1283</v>
-      </c>
-      <c r="B591" s="3" t="s">
-        <v>1321</v>
       </c>
       <c r="C591" s="3"/>
       <c r="D591" s="3" t="s">
@@ -21695,13 +21696,13 @@
       </c>
       <c r="F591" s="10"/>
       <c r="G591" s="11" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="H591" s="15" t="s">
         <v>185</v>
       </c>
       <c r="I591" t="e">
-        <f>VLOOKUP(G591,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>#N/A</v>
       </c>
       <c r="J591" s="11"/>
@@ -21709,25 +21710,25 @@
       <c r="P591" s="14"/>
     </row>
     <row r="592" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A592" s="9" t="s">
+      <c r="A592" s="3" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B592" s="9" t="s">
         <v>1283</v>
-      </c>
-      <c r="B592" s="3" t="s">
-        <v>1323</v>
       </c>
       <c r="C592" s="3"/>
       <c r="D592" s="3" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="F592" s="10"/>
       <c r="G592" s="11" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="H592" s="15" t="s">
         <v>185</v>
       </c>
       <c r="I592" t="e">
-        <f>VLOOKUP(G592,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>#N/A</v>
       </c>
       <c r="J592" s="11"/>
@@ -21735,11 +21736,11 @@
       <c r="P592" s="14"/>
     </row>
     <row r="593" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A593" s="16" t="s">
+      <c r="A593" s="17" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B593" s="16" t="s">
         <v>1283</v>
-      </c>
-      <c r="B593" s="17" t="s">
-        <v>1326</v>
       </c>
       <c r="C593" s="17"/>
       <c r="D593" s="3" t="s">
@@ -21753,7 +21754,7 @@
         <v>185</v>
       </c>
       <c r="I593" t="str">
-        <f>VLOOKUP(G593,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>8956030205811195183</v>
       </c>
       <c r="J593" s="11"/>
@@ -21761,15 +21762,15 @@
       <c r="P593" s="14"/>
     </row>
     <row r="594" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A594" s="16" t="s">
+      <c r="A594" s="17" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B594" s="16" t="s">
         <v>1283</v>
-      </c>
-      <c r="B594" s="17" t="s">
-        <v>1327</v>
       </c>
       <c r="C594" s="17"/>
       <c r="D594" s="3" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="F594" s="10"/>
       <c r="G594" s="11" t="s">
@@ -21779,7 +21780,7 @@
         <v>185</v>
       </c>
       <c r="I594" t="str">
-        <f>VLOOKUP(G594,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>8956032234712409889</v>
       </c>
       <c r="J594" s="11"/>
@@ -21787,37 +21788,37 @@
       <c r="P594" s="14"/>
     </row>
     <row r="595" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A595" s="16" t="s">
+      <c r="A595" s="17" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B595" s="16" t="s">
         <v>1283</v>
-      </c>
-      <c r="B595" s="17" t="s">
-        <v>1329</v>
       </c>
       <c r="C595" s="17"/>
       <c r="D595" s="3" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="F595" s="10"/>
       <c r="G595" s="11" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="H595" s="15" t="s">
         <v>185</v>
       </c>
       <c r="I595" t="e">
-        <f>VLOOKUP(G595,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>#N/A</v>
       </c>
       <c r="J595" s="11"/>
       <c r="N595" s="13"/>
       <c r="P595" s="14"/>
     </row>
-    <row r="596" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A596" s="16" t="s">
+    <row r="596" spans="1:16" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A596" s="17" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B596" s="16" t="s">
         <v>1283</v>
-      </c>
-      <c r="B596" s="17" t="s">
-        <v>1332</v>
       </c>
       <c r="C596" s="17"/>
       <c r="D596" s="3" t="s">
@@ -21825,13 +21826,13 @@
       </c>
       <c r="F596" s="10"/>
       <c r="G596" s="11" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="H596" s="15" t="s">
         <v>185</v>
       </c>
       <c r="I596" t="e">
-        <f>VLOOKUP(G596,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>#N/A</v>
       </c>
       <c r="J596" s="11"/>
@@ -21839,51 +21840,51 @@
       <c r="P596" s="14"/>
     </row>
     <row r="597" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A597" s="9" t="s">
+      <c r="A597" s="3" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B597" s="9" t="s">
         <v>1283</v>
-      </c>
-      <c r="B597" s="3" t="s">
-        <v>1334</v>
       </c>
       <c r="C597" s="3"/>
       <c r="D597" s="3" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="F597" s="10"/>
       <c r="G597" s="11" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="H597" s="15" t="s">
         <v>185</v>
       </c>
       <c r="I597" t="e">
-        <f>VLOOKUP(G597,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>#N/A</v>
       </c>
       <c r="J597" s="11"/>
       <c r="N597" s="13"/>
       <c r="P597" s="14"/>
     </row>
-    <row r="598" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A598" s="16" t="s">
+    <row r="598" spans="1:16" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A598" s="17" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B598" s="16" t="s">
         <v>1283</v>
-      </c>
-      <c r="B598" s="17" t="s">
-        <v>1337</v>
       </c>
       <c r="C598" s="17"/>
       <c r="D598" s="3" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="F598" s="10"/>
       <c r="G598" s="11" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="H598" s="15" t="s">
         <v>185</v>
       </c>
       <c r="I598" t="e">
-        <f>VLOOKUP(G598,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>#N/A</v>
       </c>
       <c r="J598" s="11"/>
@@ -21891,15 +21892,15 @@
       <c r="P598" s="14"/>
     </row>
     <row r="599" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A599" s="9" t="s">
+      <c r="A599" s="3" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B599" s="9" t="s">
         <v>1283</v>
-      </c>
-      <c r="B599" s="3" t="s">
-        <v>1340</v>
       </c>
       <c r="C599" s="3"/>
       <c r="D599" s="3" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="F599" s="10"/>
       <c r="G599" s="11" t="s">
@@ -21909,23 +21910,23 @@
         <v>185</v>
       </c>
       <c r="I599" t="str">
-        <f>VLOOKUP(G599,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>8956030216926380388</v>
       </c>
       <c r="J599" s="11"/>
       <c r="N599" s="13"/>
       <c r="P599" s="14"/>
     </row>
-    <row r="600" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A600" s="9" t="s">
+    <row r="600" spans="1:16" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A600" s="3" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B600" s="9" t="s">
         <v>1283</v>
-      </c>
-      <c r="B600" s="3" t="s">
-        <v>1341</v>
       </c>
       <c r="C600" s="3"/>
       <c r="D600" s="3" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="F600" s="10"/>
       <c r="G600" s="11" t="s">
@@ -21935,7 +21936,7 @@
         <v>185</v>
       </c>
       <c r="I600" t="str">
-        <f>VLOOKUP(G600,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>8956032254752139949</v>
       </c>
       <c r="J600" s="11"/>
@@ -21943,11 +21944,11 @@
       <c r="P600" s="14"/>
     </row>
     <row r="601" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A601" s="16" t="s">
+      <c r="A601" s="17" t="s">
+        <v>1342</v>
+      </c>
+      <c r="B601" s="16" t="s">
         <v>1283</v>
-      </c>
-      <c r="B601" s="17" t="s">
-        <v>1343</v>
       </c>
       <c r="C601" s="17"/>
       <c r="D601" s="3" t="s">
@@ -21961,7 +21962,7 @@
         <v>185</v>
       </c>
       <c r="I601" t="str">
-        <f>VLOOKUP(G601,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>8956032254752139972</v>
       </c>
       <c r="J601" s="23" t="s">
@@ -21971,11 +21972,11 @@
       <c r="P601" s="14"/>
     </row>
     <row r="602" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A602" s="9" t="s">
+      <c r="A602" s="3" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B602" s="9" t="s">
         <v>1283</v>
-      </c>
-      <c r="B602" s="3" t="s">
-        <v>1344</v>
       </c>
       <c r="C602" s="3"/>
       <c r="D602" s="3" t="s">
@@ -21989,23 +21990,23 @@
         <v>185</v>
       </c>
       <c r="I602" t="str">
-        <f>VLOOKUP(G602,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>8956030205811195209</v>
       </c>
       <c r="J602" s="11"/>
       <c r="N602" s="13"/>
       <c r="P602" s="14"/>
     </row>
-    <row r="603" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A603" s="18" t="s">
+    <row r="603" spans="1:16" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A603" s="19" t="s">
+        <v>1344</v>
+      </c>
+      <c r="B603" s="18" t="s">
         <v>1283</v>
-      </c>
-      <c r="B603" s="19" t="s">
-        <v>1345</v>
       </c>
       <c r="C603" s="19"/>
       <c r="D603" s="3" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="F603" s="10"/>
       <c r="G603" s="11" t="s">
@@ -22015,7 +22016,7 @@
         <v>185</v>
       </c>
       <c r="I603" t="str">
-        <f>VLOOKUP(G603,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>8956032211667101778</v>
       </c>
       <c r="J603" s="11"/>
@@ -22023,11 +22024,11 @@
       <c r="P603" s="14"/>
     </row>
     <row r="604" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A604" s="16" t="s">
+      <c r="A604" s="17" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B604" s="16" t="s">
         <v>1283</v>
-      </c>
-      <c r="B604" s="17" t="s">
-        <v>1347</v>
       </c>
       <c r="C604" s="17"/>
       <c r="D604" s="3" t="s">
@@ -22041,7 +22042,7 @@
         <v>185</v>
       </c>
       <c r="I604" t="str">
-        <f>VLOOKUP(G604,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>8956032254752140012</v>
       </c>
       <c r="J604" s="11"/>
@@ -22049,11 +22050,11 @@
       <c r="P604" s="14"/>
     </row>
     <row r="605" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A605" s="9" t="s">
+      <c r="A605" s="3" t="s">
+        <v>1347</v>
+      </c>
+      <c r="B605" s="9" t="s">
         <v>1283</v>
-      </c>
-      <c r="B605" s="3" t="s">
-        <v>1348</v>
       </c>
       <c r="C605" s="3"/>
       <c r="D605" s="3" t="s">
@@ -22061,25 +22062,25 @@
       </c>
       <c r="F605" s="10"/>
       <c r="G605" s="11" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="H605" s="15" t="s">
         <v>185</v>
       </c>
       <c r="I605" t="str">
-        <f>VLOOKUP(G605,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>8956032254752140061</v>
       </c>
       <c r="J605" s="11"/>
       <c r="N605" s="13"/>
       <c r="P605" s="14"/>
     </row>
-    <row r="606" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A606" s="9" t="s">
+    <row r="606" spans="1:16" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A606" s="3" t="s">
+        <v>1348</v>
+      </c>
+      <c r="B606" s="9" t="s">
         <v>1283</v>
-      </c>
-      <c r="B606" s="3" t="s">
-        <v>1349</v>
       </c>
       <c r="C606" s="3"/>
       <c r="D606" s="3" t="s">
@@ -22087,39 +22088,39 @@
       </c>
       <c r="F606" s="10"/>
       <c r="G606" s="11" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="H606" s="15" t="s">
         <v>185</v>
       </c>
       <c r="I606" t="str">
-        <f>VLOOKUP(G606,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>8956032254752140079</v>
       </c>
       <c r="J606" s="11"/>
       <c r="N606" s="13"/>
       <c r="P606" s="14"/>
     </row>
-    <row r="607" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A607" s="9" t="s">
+    <row r="607" spans="1:16" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A607" s="3" t="s">
+        <v>1349</v>
+      </c>
+      <c r="B607" s="9" t="s">
         <v>1283</v>
-      </c>
-      <c r="B607" s="3" t="s">
-        <v>1350</v>
       </c>
       <c r="C607" s="3"/>
       <c r="D607" s="3" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="F607" s="10"/>
       <c r="G607" s="11" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="H607" s="15" t="s">
         <v>185</v>
       </c>
       <c r="I607" t="str">
-        <f>VLOOKUP(G607,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>8956032254752140087</v>
       </c>
       <c r="J607" s="11"/>
@@ -22127,11 +22128,11 @@
       <c r="P607" s="14"/>
     </row>
     <row r="608" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A608" s="9" t="s">
+      <c r="A608" s="3" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B608" s="9" t="s">
         <v>1283</v>
-      </c>
-      <c r="B608" s="3" t="s">
-        <v>1352</v>
       </c>
       <c r="C608" s="3"/>
       <c r="D608" s="3" t="s">
@@ -22145,7 +22146,7 @@
         <v>185</v>
       </c>
       <c r="I608" t="str">
-        <f>VLOOKUP(G608,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>8956032234712409640</v>
       </c>
       <c r="J608" s="11"/>
@@ -22153,11 +22154,11 @@
       <c r="P608" s="14"/>
     </row>
     <row r="609" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A609" s="16" t="s">
+      <c r="A609" s="17" t="s">
+        <v>1352</v>
+      </c>
+      <c r="B609" s="16" t="s">
         <v>1283</v>
-      </c>
-      <c r="B609" s="17" t="s">
-        <v>1353</v>
       </c>
       <c r="C609" s="29"/>
       <c r="D609" s="3" t="s">
@@ -22171,23 +22172,23 @@
         <v>185</v>
       </c>
       <c r="I609" t="str">
-        <f>VLOOKUP(G609,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>8956030216926242786</v>
       </c>
       <c r="J609" s="11"/>
       <c r="N609" s="13"/>
       <c r="P609" s="14"/>
     </row>
-    <row r="610" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A610" s="9" t="s">
+    <row r="610" spans="1:16" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A610" s="3" t="s">
+        <v>1353</v>
+      </c>
+      <c r="B610" s="9" t="s">
         <v>1283</v>
-      </c>
-      <c r="B610" s="3" t="s">
-        <v>1354</v>
       </c>
       <c r="C610" s="3"/>
       <c r="D610" s="3" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="F610" s="10"/>
       <c r="G610" s="20" t="s">
@@ -22197,21 +22198,21 @@
         <v>185</v>
       </c>
       <c r="I610" t="str">
-        <f>VLOOKUP(G610,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>8956032254752140095</v>
       </c>
       <c r="J610" s="23" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="N610" s="13"/>
       <c r="P610" s="14"/>
     </row>
-    <row r="611" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A611" s="9" t="s">
+    <row r="611" spans="1:16" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A611" s="3" t="s">
+        <v>1355</v>
+      </c>
+      <c r="B611" s="9" t="s">
         <v>1283</v>
-      </c>
-      <c r="B611" s="3" t="s">
-        <v>1356</v>
       </c>
       <c r="C611" s="3"/>
       <c r="D611" s="3" t="s">
@@ -22225,35 +22226,35 @@
         <v>185</v>
       </c>
       <c r="I611" t="str">
-        <f>VLOOKUP(G611,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>8956032254752140103</v>
       </c>
       <c r="J611" s="23" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="N611" s="13"/>
       <c r="P611" s="14"/>
     </row>
     <row r="612" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A612" s="9" t="s">
+      <c r="A612" s="3" t="s">
+        <v>1357</v>
+      </c>
+      <c r="B612" s="9" t="s">
         <v>1283</v>
-      </c>
-      <c r="B612" s="3" t="s">
-        <v>1358</v>
       </c>
       <c r="C612" s="3"/>
       <c r="D612" s="3" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="F612" s="10"/>
       <c r="G612" s="11" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="H612" s="15" t="s">
         <v>185</v>
       </c>
       <c r="I612" t="e">
-        <f>VLOOKUP(G612,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>#N/A</v>
       </c>
       <c r="J612" s="11"/>
@@ -22261,11 +22262,11 @@
       <c r="P612" s="14"/>
     </row>
     <row r="613" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A613" s="9" t="s">
+      <c r="A613" s="3" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B613" s="9" t="s">
         <v>1283</v>
-      </c>
-      <c r="B613" s="3" t="s">
-        <v>1361</v>
       </c>
       <c r="C613" s="3"/>
       <c r="D613" s="3" t="s">
@@ -22279,21 +22280,21 @@
         <v>185</v>
       </c>
       <c r="I613" t="str">
-        <f>VLOOKUP(G613,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>8956032254752140111</v>
       </c>
       <c r="J613" s="23" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="N613" s="13"/>
       <c r="P613" s="14"/>
     </row>
     <row r="614" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A614" s="9" t="s">
+      <c r="A614" s="3" t="s">
+        <v>1362</v>
+      </c>
+      <c r="B614" s="9" t="s">
         <v>1283</v>
-      </c>
-      <c r="B614" s="3" t="s">
-        <v>1363</v>
       </c>
       <c r="C614" s="3"/>
       <c r="D614" s="3" t="s">
@@ -22301,13 +22302,13 @@
       </c>
       <c r="F614" s="10"/>
       <c r="G614" s="11" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="H614" s="15" t="s">
         <v>185</v>
       </c>
       <c r="I614" t="e">
-        <f>VLOOKUP(G614,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>#N/A</v>
       </c>
       <c r="J614" s="11"/>
@@ -22315,15 +22316,15 @@
       <c r="P614" s="14"/>
     </row>
     <row r="615" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A615" s="16" t="s">
+      <c r="A615" s="30" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B615" s="16" t="s">
         <v>1283</v>
-      </c>
-      <c r="B615" s="30" t="s">
-        <v>1365</v>
       </c>
       <c r="C615" s="17"/>
       <c r="D615" s="3" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="F615" s="10"/>
       <c r="G615" s="11" t="s">
@@ -22333,7 +22334,7 @@
         <v>185</v>
       </c>
       <c r="I615" t="str">
-        <f>VLOOKUP(G615,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>8956032254752140129</v>
       </c>
       <c r="J615" s="11"/>
@@ -22341,15 +22342,15 @@
       <c r="P615" s="14"/>
     </row>
     <row r="616" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A616" s="9" t="s">
+      <c r="A616" s="31" t="s">
+        <v>1365</v>
+      </c>
+      <c r="B616" s="9" t="s">
         <v>1283</v>
-      </c>
-      <c r="B616" s="31" t="s">
-        <v>1366</v>
       </c>
       <c r="C616" s="3"/>
       <c r="D616" s="3" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="F616" s="10"/>
       <c r="G616" s="11" t="s">
@@ -22359,7 +22360,7 @@
         <v>185</v>
       </c>
       <c r="I616" t="str">
-        <f>VLOOKUP(G616,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>8956032211667084453</v>
       </c>
       <c r="J616" s="11"/>
@@ -22367,11 +22368,11 @@
       <c r="P616" s="14"/>
     </row>
     <row r="617" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A617" s="9" t="s">
+      <c r="A617" s="31" t="s">
+        <v>1367</v>
+      </c>
+      <c r="B617" s="9" t="s">
         <v>1283</v>
-      </c>
-      <c r="B617" s="31" t="s">
-        <v>1368</v>
       </c>
       <c r="C617" s="3"/>
       <c r="D617" s="3" t="s">
@@ -22385,22 +22386,22 @@
         <v>185</v>
       </c>
       <c r="I617" t="str">
-        <f>VLOOKUP(G617,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>8956032211667084495</v>
       </c>
       <c r="J617" s="11"/>
       <c r="N617" s="13"/>
     </row>
     <row r="618" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A618" s="9" t="s">
+      <c r="A618" s="31" t="s">
+        <v>1368</v>
+      </c>
+      <c r="B618" s="9" t="s">
         <v>1283</v>
-      </c>
-      <c r="B618" s="31" t="s">
-        <v>1369</v>
       </c>
       <c r="C618" s="3"/>
       <c r="D618" s="3" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="F618" s="10"/>
       <c r="G618" s="11" t="s">
@@ -22410,33 +22411,33 @@
         <v>185</v>
       </c>
       <c r="I618" t="str">
-        <f>VLOOKUP(G618,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>8956032254752140145</v>
       </c>
       <c r="J618" s="11"/>
       <c r="N618" s="13"/>
       <c r="P618" s="14"/>
     </row>
-    <row r="619" spans="1:16" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A619" s="9" t="s">
+    <row r="619" spans="1:16" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A619" s="31" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B619" s="9" t="s">
         <v>1283</v>
-      </c>
-      <c r="B619" s="31" t="s">
-        <v>1371</v>
       </c>
       <c r="C619" s="3"/>
       <c r="D619" s="3" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="F619" s="10"/>
       <c r="G619" s="11" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="H619" s="15" t="s">
         <v>185</v>
       </c>
       <c r="I619" t="e">
-        <f>VLOOKUP(G619,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>#N/A</v>
       </c>
       <c r="J619" s="11"/>
@@ -22449,13 +22450,13 @@
       <c r="C620" s="3"/>
       <c r="F620" s="10"/>
       <c r="G620" s="20" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="H620" s="22" t="s">
         <v>185</v>
       </c>
       <c r="I620" t="str">
-        <f>VLOOKUP(G620,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>8956032254752140137</v>
       </c>
       <c r="J620" s="23" t="s">
@@ -22476,7 +22477,7 @@
         <v>185</v>
       </c>
       <c r="I621" t="str">
-        <f>VLOOKUP(G621,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>8956030205811195746</v>
       </c>
       <c r="J621" s="11"/>
@@ -22489,13 +22490,13 @@
       <c r="C622" s="3"/>
       <c r="F622" s="10"/>
       <c r="G622" s="11" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="H622" s="15" t="s">
         <v>185</v>
       </c>
       <c r="I622" t="e">
-        <f>VLOOKUP(G622,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>#N/A</v>
       </c>
       <c r="J622" s="11"/>
@@ -22514,7 +22515,7 @@
         <v>185</v>
       </c>
       <c r="I623" t="str">
-        <f>VLOOKUP(G623,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>8956032234713494500</v>
       </c>
       <c r="J623" s="11"/>
@@ -22527,17 +22528,17 @@
       <c r="C624" s="3"/>
       <c r="F624" s="10"/>
       <c r="G624" s="20" t="s">
+        <v>1374</v>
+      </c>
+      <c r="H624" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="I624" t="e">
+        <f t="shared" si="9"/>
+        <v>#N/A</v>
+      </c>
+      <c r="J624" s="23" t="s">
         <v>1375</v>
-      </c>
-      <c r="H624" s="22" t="s">
-        <v>185</v>
-      </c>
-      <c r="I624" t="e">
-        <f>VLOOKUP(G624,D:D,1,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J624" s="23" t="s">
-        <v>1376</v>
       </c>
       <c r="N624" s="13"/>
       <c r="P624" s="14"/>
@@ -22548,13 +22549,13 @@
       <c r="C625" s="3"/>
       <c r="F625" s="10"/>
       <c r="G625" s="11" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="H625" s="15" t="s">
         <v>185</v>
       </c>
       <c r="I625" t="e">
-        <f>VLOOKUP(G625,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>#N/A</v>
       </c>
       <c r="J625" s="11"/>
@@ -22567,13 +22568,13 @@
       <c r="C626" s="3"/>
       <c r="F626" s="10"/>
       <c r="G626" s="11" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="H626" s="15" t="s">
         <v>185</v>
       </c>
       <c r="I626" t="e">
-        <f>VLOOKUP(G626,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>#N/A</v>
       </c>
       <c r="J626" s="11"/>
@@ -22591,7 +22592,7 @@
         <v>185</v>
       </c>
       <c r="I627" t="str">
-        <f>VLOOKUP(G627,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>8956032254752140160</v>
       </c>
       <c r="J627" s="11"/>
@@ -22603,13 +22604,13 @@
       <c r="C628" s="3"/>
       <c r="F628" s="10"/>
       <c r="G628" s="11" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="H628" s="15" t="s">
         <v>185</v>
       </c>
       <c r="I628" t="e">
-        <f>VLOOKUP(G628,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>#N/A</v>
       </c>
       <c r="J628" s="11"/>
@@ -22627,7 +22628,7 @@
         <v>185</v>
       </c>
       <c r="I629" t="str">
-        <f>VLOOKUP(G629,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>8956030242988532344</v>
       </c>
       <c r="J629" s="11"/>
@@ -22645,7 +22646,7 @@
         <v>185</v>
       </c>
       <c r="I630" t="str">
-        <f>VLOOKUP(G630,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>8956032244730755908</v>
       </c>
       <c r="J630" s="11"/>
@@ -22657,13 +22658,13 @@
       <c r="C631" s="3"/>
       <c r="F631" s="10"/>
       <c r="G631" s="11" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="H631" s="15" t="s">
         <v>185</v>
       </c>
       <c r="I631" t="e">
-        <f>VLOOKUP(G631,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>#N/A</v>
       </c>
       <c r="J631" s="11"/>
@@ -22681,7 +22682,7 @@
         <v>185</v>
       </c>
       <c r="I632" t="str">
-        <f>VLOOKUP(G632,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>8956030205811195845</v>
       </c>
       <c r="J632" s="11"/>
@@ -22699,7 +22700,7 @@
         <v>185</v>
       </c>
       <c r="I633" t="str">
-        <f>VLOOKUP(G633,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>8956030221943028051</v>
       </c>
       <c r="J633" s="11"/>
@@ -22711,13 +22712,13 @@
       <c r="C634" s="3"/>
       <c r="F634" s="10"/>
       <c r="G634" s="11" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="H634" s="15" t="s">
         <v>185</v>
       </c>
       <c r="I634" t="e">
-        <f>VLOOKUP(G634,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>#N/A</v>
       </c>
       <c r="J634" s="11"/>
@@ -22729,13 +22730,13 @@
       <c r="C635" s="3"/>
       <c r="F635" s="10"/>
       <c r="G635" s="11" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="H635" s="15" t="s">
         <v>185</v>
       </c>
       <c r="I635" t="e">
-        <f>VLOOKUP(G635,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>#N/A</v>
       </c>
       <c r="J635" s="11"/>
@@ -22753,7 +22754,7 @@
         <v>185</v>
       </c>
       <c r="I636" t="str">
-        <f>VLOOKUP(G636,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>8956032201581696854</v>
       </c>
       <c r="J636" s="11"/>
@@ -22765,13 +22766,13 @@
       <c r="C637" s="3"/>
       <c r="F637" s="10"/>
       <c r="G637" s="11" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="H637" s="15" t="s">
         <v>185</v>
       </c>
       <c r="I637" t="e">
-        <f>VLOOKUP(G637,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>#N/A</v>
       </c>
       <c r="J637" s="11"/>
@@ -22783,13 +22784,13 @@
       <c r="C638" s="3"/>
       <c r="F638" s="10"/>
       <c r="G638" s="11" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="H638" s="15" t="s">
         <v>185</v>
       </c>
       <c r="I638" t="e">
-        <f>VLOOKUP(G638,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>#N/A</v>
       </c>
       <c r="J638" s="11"/>
@@ -22807,7 +22808,7 @@
         <v>185</v>
       </c>
       <c r="I639" t="str">
-        <f>VLOOKUP(G639,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>8956032186552548277</v>
       </c>
       <c r="J639" s="11"/>
@@ -22825,7 +22826,7 @@
         <v>185</v>
       </c>
       <c r="I640" t="str">
-        <f>VLOOKUP(G640,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>8956030205811195126</v>
       </c>
       <c r="J640" s="11"/>
@@ -22843,7 +22844,7 @@
         <v>185</v>
       </c>
       <c r="I641" t="str">
-        <f>VLOOKUP(G641,D:D,1,0)</f>
+        <f t="shared" si="9"/>
         <v>8956032254752140186</v>
       </c>
       <c r="J641" s="11"/>
@@ -22861,7 +22862,7 @@
         <v>185</v>
       </c>
       <c r="I642" t="str">
-        <f>VLOOKUP(G642,D:D,1,0)</f>
+        <f t="shared" ref="I642:I705" si="10">VLOOKUP(G642,D:D,1,0)</f>
         <v>8956030216926247397</v>
       </c>
       <c r="J642" s="11"/>
@@ -22879,7 +22880,7 @@
         <v>185</v>
       </c>
       <c r="I643" t="str">
-        <f>VLOOKUP(G643,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>8956032254752140194</v>
       </c>
       <c r="J643" s="11"/>
@@ -22891,17 +22892,17 @@
       <c r="C644" s="3"/>
       <c r="F644" s="10"/>
       <c r="G644" s="20" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="H644" s="22" t="s">
         <v>185</v>
       </c>
       <c r="I644" t="str">
-        <f>VLOOKUP(G644,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>8956032254752140202</v>
       </c>
       <c r="J644" s="23" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="N644" s="13"/>
     </row>
@@ -22917,7 +22918,7 @@
         <v>185</v>
       </c>
       <c r="I645" t="str">
-        <f>VLOOKUP(G645,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>8956034203014361229</v>
       </c>
       <c r="J645" s="11"/>
@@ -22929,13 +22930,13 @@
       <c r="C646" s="3"/>
       <c r="F646" s="10"/>
       <c r="G646" s="11" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="H646" s="15" t="s">
         <v>185</v>
       </c>
       <c r="I646" t="e">
-        <f>VLOOKUP(G646,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>#N/A</v>
       </c>
       <c r="J646" s="11"/>
@@ -22947,13 +22948,13 @@
       <c r="C647" s="3"/>
       <c r="F647" s="10"/>
       <c r="G647" s="11" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="H647" s="15" t="s">
         <v>185</v>
       </c>
       <c r="I647" t="e">
-        <f>VLOOKUP(G647,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>#N/A</v>
       </c>
       <c r="J647" s="11"/>
@@ -22971,7 +22972,7 @@
         <v>185</v>
       </c>
       <c r="I648" t="str">
-        <f>VLOOKUP(G648,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>8956034203014348267</v>
       </c>
       <c r="J648" s="11"/>
@@ -22989,7 +22990,7 @@
         <v>185</v>
       </c>
       <c r="I649" t="str">
-        <f>VLOOKUP(G649,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>8956032185521956736</v>
       </c>
       <c r="J649" s="11"/>
@@ -23000,7 +23001,7 @@
       <c r="B650" s="31"/>
       <c r="C650" s="3"/>
       <c r="D650" s="3" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="F650" s="10"/>
       <c r="G650" s="11" t="s">
@@ -23010,7 +23011,7 @@
         <v>185</v>
       </c>
       <c r="I650" t="str">
-        <f>VLOOKUP(G650,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>8956032244730755916</v>
       </c>
       <c r="J650" s="11"/>
@@ -23027,7 +23028,7 @@
         <v>185</v>
       </c>
       <c r="I651" t="str">
-        <f>VLOOKUP(G651,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>8956034203014361369</v>
       </c>
       <c r="J651" s="11"/>
@@ -23044,7 +23045,7 @@
         <v>185</v>
       </c>
       <c r="I652" t="str">
-        <f>VLOOKUP(G652,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>8956034203014361310</v>
       </c>
       <c r="J652" s="11"/>
@@ -23055,13 +23056,13 @@
       <c r="C653" s="3"/>
       <c r="F653" s="10"/>
       <c r="G653" s="11" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="H653" s="15" t="s">
         <v>185</v>
       </c>
       <c r="I653" t="e">
-        <f>VLOOKUP(G653,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>#N/A</v>
       </c>
       <c r="J653" s="11"/>
@@ -23078,7 +23079,7 @@
         <v>185</v>
       </c>
       <c r="I654" t="str">
-        <f>VLOOKUP(G654,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>8956030205811222052</v>
       </c>
       <c r="J654" s="11"/>
@@ -23095,7 +23096,7 @@
         <v>185</v>
       </c>
       <c r="I655" t="str">
-        <f>VLOOKUP(G655,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>8956032244730755973</v>
       </c>
       <c r="J655" s="11"/>
@@ -23106,13 +23107,13 @@
       <c r="C656" s="3"/>
       <c r="F656" s="10"/>
       <c r="G656" s="11" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="H656" s="15" t="s">
         <v>185</v>
       </c>
       <c r="I656" t="e">
-        <f>VLOOKUP(G656,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>#N/A</v>
       </c>
       <c r="J656" s="11"/>
@@ -23129,7 +23130,7 @@
         <v>185</v>
       </c>
       <c r="I657" t="str">
-        <f>VLOOKUP(G657,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>8956030205811195100</v>
       </c>
       <c r="J657" s="11"/>
@@ -23146,7 +23147,7 @@
         <v>185</v>
       </c>
       <c r="I658" t="str">
-        <f>VLOOKUP(G658,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>8956032254752134213</v>
       </c>
       <c r="J658" s="11"/>
@@ -23163,7 +23164,7 @@
         <v>185</v>
       </c>
       <c r="I659" t="str">
-        <f>VLOOKUP(G659,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>8956030216921418357</v>
       </c>
       <c r="J659" s="11"/>
@@ -23174,13 +23175,13 @@
       <c r="C660" s="3"/>
       <c r="F660" s="10"/>
       <c r="G660" s="11" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="H660" s="15" t="s">
         <v>185</v>
       </c>
       <c r="I660" t="str">
-        <f>VLOOKUP(G660,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>8956032254752140236</v>
       </c>
       <c r="J660" s="11"/>
@@ -23191,13 +23192,13 @@
       <c r="C661" s="3"/>
       <c r="F661" s="10"/>
       <c r="G661" s="11" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="H661" s="15" t="s">
         <v>185</v>
       </c>
       <c r="I661" t="e">
-        <f>VLOOKUP(G661,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>#N/A</v>
       </c>
       <c r="J661" s="11"/>
@@ -23214,7 +23215,7 @@
         <v>185</v>
       </c>
       <c r="I662" t="str">
-        <f>VLOOKUP(G662,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>8956030205811195787</v>
       </c>
       <c r="J662" s="11"/>
@@ -23231,7 +23232,7 @@
         <v>185</v>
       </c>
       <c r="I663" t="str">
-        <f>VLOOKUP(G663,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>8956032211667101554</v>
       </c>
       <c r="J663" s="11"/>
@@ -23248,7 +23249,7 @@
         <v>185</v>
       </c>
       <c r="I664" t="str">
-        <f>VLOOKUP(G664,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>8956034203014350594</v>
       </c>
       <c r="J664" s="11"/>
@@ -23259,13 +23260,13 @@
       <c r="C665" s="3"/>
       <c r="F665" s="10"/>
       <c r="G665" s="11" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="H665" s="15" t="s">
         <v>185</v>
       </c>
       <c r="I665" t="str">
-        <f>VLOOKUP(G665,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>8956032204612106968</v>
       </c>
       <c r="J665" s="11"/>
@@ -23282,7 +23283,7 @@
         <v>185</v>
       </c>
       <c r="I666" t="str">
-        <f>VLOOKUP(G666,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>8956030221943028069</v>
       </c>
       <c r="J666" s="11"/>
@@ -23299,7 +23300,7 @@
         <v>185</v>
       </c>
       <c r="I667" t="str">
-        <f>VLOOKUP(G667,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>8956034203014361260</v>
       </c>
       <c r="J667" s="11"/>
@@ -23316,7 +23317,7 @@
         <v>185</v>
       </c>
       <c r="I668" t="str">
-        <f>VLOOKUP(G668,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>8956034203014348366</v>
       </c>
       <c r="J668" s="11"/>
@@ -23333,7 +23334,7 @@
         <v>185</v>
       </c>
       <c r="I669" t="str">
-        <f>VLOOKUP(G669,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>8956030205811195563</v>
       </c>
       <c r="J669" s="11"/>
@@ -23350,7 +23351,7 @@
         <v>185</v>
       </c>
       <c r="I670" t="str">
-        <f>VLOOKUP(G670,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>8956030205811195175</v>
       </c>
       <c r="J670" s="11"/>
@@ -23361,13 +23362,13 @@
       <c r="C671" s="3"/>
       <c r="F671" s="10"/>
       <c r="G671" s="11" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="H671" s="15" t="s">
         <v>185</v>
       </c>
       <c r="I671" t="e">
-        <f>VLOOKUP(G671,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>#N/A</v>
       </c>
       <c r="J671" s="11"/>
@@ -23378,13 +23379,13 @@
       <c r="C672" s="3"/>
       <c r="F672" s="10"/>
       <c r="G672" s="11" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="H672" s="15" t="s">
         <v>185</v>
       </c>
       <c r="I672" t="e">
-        <f>VLOOKUP(G672,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>#N/A</v>
       </c>
       <c r="J672" s="11"/>
@@ -23395,13 +23396,13 @@
       <c r="C673" s="3"/>
       <c r="F673" s="10"/>
       <c r="G673" s="11" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="H673" s="15" t="s">
         <v>185</v>
       </c>
       <c r="I673" t="e">
-        <f>VLOOKUP(G673,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>#N/A</v>
       </c>
       <c r="J673" s="11"/>
@@ -23418,7 +23419,7 @@
         <v>185</v>
       </c>
       <c r="I674" t="str">
-        <f>VLOOKUP(G674,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>8956032185521956769</v>
       </c>
       <c r="J674" s="11"/>
@@ -23435,7 +23436,7 @@
         <v>185</v>
       </c>
       <c r="I675" t="str">
-        <f>VLOOKUP(G675,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>8956030216921386117</v>
       </c>
       <c r="J675" s="11"/>
@@ -23452,7 +23453,7 @@
         <v>185</v>
       </c>
       <c r="I676" t="str">
-        <f>VLOOKUP(G676,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>8956034203014348341</v>
       </c>
       <c r="J676" s="11"/>
@@ -23469,7 +23470,7 @@
         <v>185</v>
       </c>
       <c r="I677" t="str">
-        <f>VLOOKUP(G677,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>8956032234713494591</v>
       </c>
       <c r="J677" s="11"/>
@@ -23480,13 +23481,13 @@
       <c r="C678" s="3"/>
       <c r="F678" s="10"/>
       <c r="G678" s="11" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="H678" s="15" t="s">
         <v>185</v>
       </c>
       <c r="I678" t="e">
-        <f>VLOOKUP(G678,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>#N/A</v>
       </c>
       <c r="J678" s="11"/>
@@ -23503,7 +23504,7 @@
         <v>185</v>
       </c>
       <c r="I679" t="str">
-        <f>VLOOKUP(G679,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>8956030205811195720</v>
       </c>
       <c r="J679" s="11"/>
@@ -23520,7 +23521,7 @@
         <v>185</v>
       </c>
       <c r="I680" t="str">
-        <f>VLOOKUP(G680,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>8956032201581696870</v>
       </c>
       <c r="J680" s="11"/>
@@ -23537,7 +23538,7 @@
         <v>185</v>
       </c>
       <c r="I681" t="str">
-        <f>VLOOKUP(G681,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>8956032204612105697</v>
       </c>
       <c r="J681" s="11"/>
@@ -23554,7 +23555,7 @@
         <v>185</v>
       </c>
       <c r="I682" t="str">
-        <f>VLOOKUP(G682,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>8956030242988505506</v>
       </c>
       <c r="J682" s="11"/>
@@ -23571,7 +23572,7 @@
         <v>185</v>
       </c>
       <c r="I683" t="str">
-        <f>VLOOKUP(G683,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>8956034203014348374</v>
       </c>
       <c r="J683" s="11"/>
@@ -23588,7 +23589,7 @@
         <v>185</v>
       </c>
       <c r="I684" t="str">
-        <f>VLOOKUP(G684,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>8956032201581696847</v>
       </c>
       <c r="J684" s="11"/>
@@ -23599,13 +23600,13 @@
       <c r="C685" s="3"/>
       <c r="F685" s="10"/>
       <c r="G685" s="11" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="H685" s="15" t="s">
         <v>185</v>
       </c>
       <c r="I685" t="e">
-        <f>VLOOKUP(G685,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>#N/A</v>
       </c>
       <c r="J685" s="11"/>
@@ -23616,13 +23617,13 @@
       <c r="C686" s="3"/>
       <c r="F686" s="10"/>
       <c r="G686" s="11" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="H686" s="15" t="s">
         <v>185</v>
       </c>
       <c r="I686" t="e">
-        <f>VLOOKUP(G686,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>#N/A</v>
       </c>
       <c r="J686" s="11"/>
@@ -23639,7 +23640,7 @@
         <v>185</v>
       </c>
       <c r="I687" t="str">
-        <f>VLOOKUP(G687,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>8956030216921386125</v>
       </c>
       <c r="J687" s="11"/>
@@ -23656,7 +23657,7 @@
         <v>185</v>
       </c>
       <c r="I688" t="str">
-        <f>VLOOKUP(G688,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>8956032234713494658</v>
       </c>
       <c r="J688" s="11"/>
@@ -23673,7 +23674,7 @@
         <v>185</v>
       </c>
       <c r="I689" t="str">
-        <f>VLOOKUP(G689,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>8956032254752134197</v>
       </c>
       <c r="J689" s="11"/>
@@ -23690,7 +23691,7 @@
         <v>185</v>
       </c>
       <c r="I690" t="str">
-        <f>VLOOKUP(G690,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>8956030216926241549</v>
       </c>
       <c r="J690" s="11"/>
@@ -23707,7 +23708,7 @@
         <v>185</v>
       </c>
       <c r="I691" t="str">
-        <f>VLOOKUP(G691,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>8956030216921386091</v>
       </c>
       <c r="J691" s="11"/>
@@ -23718,13 +23719,13 @@
       <c r="C692" s="3"/>
       <c r="F692" s="10"/>
       <c r="G692" s="11" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="H692" s="15" t="s">
         <v>185</v>
       </c>
       <c r="I692" t="e">
-        <f>VLOOKUP(G692,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>#N/A</v>
       </c>
       <c r="J692" s="11"/>
@@ -23741,7 +23742,7 @@
         <v>185</v>
       </c>
       <c r="I693" t="str">
-        <f>VLOOKUP(G693,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>8956030216926247405</v>
       </c>
       <c r="J693" s="11"/>
@@ -23758,7 +23759,7 @@
         <v>185</v>
       </c>
       <c r="I694" t="str">
-        <f>VLOOKUP(G694,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>8956030205811195456</v>
       </c>
       <c r="J694" s="11"/>
@@ -23769,13 +23770,13 @@
       <c r="C695" s="3"/>
       <c r="F695" s="10"/>
       <c r="G695" s="11" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="H695" s="15" t="s">
         <v>185</v>
       </c>
       <c r="I695" t="e">
-        <f>VLOOKUP(G695,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>#N/A</v>
       </c>
       <c r="J695" s="11"/>
@@ -23786,13 +23787,13 @@
       <c r="C696" s="3"/>
       <c r="F696" s="10"/>
       <c r="G696" t="s">
+        <v>1398</v>
+      </c>
+      <c r="H696" s="33" t="s">
         <v>1399</v>
       </c>
-      <c r="H696" s="33" t="s">
-        <v>1400</v>
-      </c>
       <c r="I696" t="e">
-        <f>VLOOKUP(G696,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>#N/A</v>
       </c>
     </row>
@@ -23802,13 +23803,13 @@
       <c r="C697" s="3"/>
       <c r="F697" s="10"/>
       <c r="G697" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="H697" s="33" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="I697" t="e">
-        <f>VLOOKUP(G697,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>#N/A</v>
       </c>
     </row>
@@ -23818,13 +23819,13 @@
       <c r="C698" s="3"/>
       <c r="F698" s="10"/>
       <c r="G698" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="H698" s="33" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="I698" t="e">
-        <f>VLOOKUP(G698,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>#N/A</v>
       </c>
     </row>
@@ -23834,13 +23835,13 @@
       <c r="C699" s="3"/>
       <c r="F699" s="10"/>
       <c r="G699" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="H699" s="33" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="I699" t="e">
-        <f>VLOOKUP(G699,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>#N/A</v>
       </c>
     </row>
@@ -23850,13 +23851,13 @@
       <c r="C700" s="3"/>
       <c r="F700" s="10"/>
       <c r="G700" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="H700" s="33" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="I700" t="e">
-        <f>VLOOKUP(G700,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>#N/A</v>
       </c>
     </row>
@@ -23869,10 +23870,10 @@
         <v>730</v>
       </c>
       <c r="H701" s="33" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="I701" t="str">
-        <f>VLOOKUP(G701,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>89560900000863586762</v>
       </c>
     </row>
@@ -23882,13 +23883,13 @@
       <c r="C702" s="3"/>
       <c r="F702" s="10"/>
       <c r="G702" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="H702" s="33" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="I702" t="e">
-        <f>VLOOKUP(G702,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>#N/A</v>
       </c>
     </row>
@@ -23898,13 +23899,13 @@
       <c r="C703" s="3"/>
       <c r="F703" s="10"/>
       <c r="G703" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="H703" s="33" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="I703" t="e">
-        <f>VLOOKUP(G703,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>#N/A</v>
       </c>
     </row>
@@ -23914,13 +23915,13 @@
       <c r="C704" s="3"/>
       <c r="F704" s="10"/>
       <c r="G704" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="H704" s="33" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="I704" t="e">
-        <f>VLOOKUP(G704,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>#N/A</v>
       </c>
     </row>
@@ -23933,10 +23934,10 @@
         <v>925</v>
       </c>
       <c r="H705" s="33" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="I705" t="str">
-        <f>VLOOKUP(G705,D:D,1,0)</f>
+        <f t="shared" si="10"/>
         <v>89560900000863585764</v>
       </c>
     </row>
@@ -23946,13 +23947,13 @@
       <c r="C706" s="3"/>
       <c r="F706" s="10"/>
       <c r="G706" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="H706" s="33" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="I706" t="e">
-        <f>VLOOKUP(G706,D:D,1,0)</f>
+        <f t="shared" ref="I706:I744" si="11">VLOOKUP(G706,D:D,1,0)</f>
         <v>#N/A</v>
       </c>
     </row>
@@ -23962,13 +23963,13 @@
       <c r="C707" s="3"/>
       <c r="F707" s="10"/>
       <c r="G707" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="H707" s="33" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="I707" t="e">
-        <f>VLOOKUP(G707,D:D,1,0)</f>
+        <f t="shared" si="11"/>
         <v>#N/A</v>
       </c>
     </row>
@@ -23981,10 +23982,10 @@
         <v>1072</v>
       </c>
       <c r="H708" s="33" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="I708" t="str">
-        <f>VLOOKUP(G708,D:D,1,0)</f>
+        <f t="shared" si="11"/>
         <v>89560900000863585756</v>
       </c>
     </row>
@@ -23997,10 +23998,10 @@
         <v>1018</v>
       </c>
       <c r="H709" s="33" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="I709" t="str">
-        <f>VLOOKUP(G709,D:D,1,0)</f>
+        <f t="shared" si="11"/>
         <v>89560900000863585699</v>
       </c>
     </row>
@@ -24013,10 +24014,10 @@
         <v>406</v>
       </c>
       <c r="H710" s="33" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="I710" t="str">
-        <f>VLOOKUP(G710,D:D,1,0)</f>
+        <f t="shared" si="11"/>
         <v>89560900000863585681</v>
       </c>
     </row>
@@ -24029,10 +24030,10 @@
         <v>1166</v>
       </c>
       <c r="H711" s="33" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="I711" t="str">
-        <f>VLOOKUP(G711,D:D,1,0)</f>
+        <f t="shared" si="11"/>
         <v>89560900000863574164</v>
       </c>
     </row>
@@ -24042,13 +24043,13 @@
       <c r="C712" s="3"/>
       <c r="F712" s="10"/>
       <c r="G712" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="H712" s="33" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="I712" t="str">
-        <f>VLOOKUP(G712,D:D,1,0)</f>
+        <f t="shared" si="11"/>
         <v>89560900000863574065</v>
       </c>
     </row>
@@ -24058,13 +24059,13 @@
       <c r="C713" s="3"/>
       <c r="F713" s="10"/>
       <c r="G713" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="H713" s="33" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="I713" t="e">
-        <f>VLOOKUP(G713,D:D,1,0)</f>
+        <f t="shared" si="11"/>
         <v>#N/A</v>
       </c>
     </row>
@@ -24074,13 +24075,13 @@
       <c r="C714" s="3"/>
       <c r="F714" s="10"/>
       <c r="G714" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="H714" s="33" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="I714" t="e">
-        <f>VLOOKUP(G714,D:D,1,0)</f>
+        <f t="shared" si="11"/>
         <v>#N/A</v>
       </c>
     </row>
@@ -24090,13 +24091,13 @@
       <c r="C715" s="3"/>
       <c r="F715" s="10"/>
       <c r="G715" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="H715" s="33" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="I715" t="e">
-        <f>VLOOKUP(G715,D:D,1,0)</f>
+        <f t="shared" si="11"/>
         <v>#N/A</v>
       </c>
     </row>
@@ -24109,10 +24110,10 @@
         <v>461</v>
       </c>
       <c r="H716" s="33" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="I716" t="str">
-        <f>VLOOKUP(G716,D:D,1,0)</f>
+        <f t="shared" si="11"/>
         <v>89560900000863585749</v>
       </c>
     </row>
@@ -24122,13 +24123,13 @@
       <c r="C717" s="3"/>
       <c r="F717" s="10"/>
       <c r="G717" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="H717" s="33" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="I717" t="e">
-        <f>VLOOKUP(G717,D:D,1,0)</f>
+        <f t="shared" si="11"/>
         <v>#N/A</v>
       </c>
     </row>
@@ -24138,13 +24139,13 @@
       <c r="C718" s="3"/>
       <c r="F718" s="10"/>
       <c r="G718" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="H718" s="33" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="I718" t="e">
-        <f>VLOOKUP(G718,D:D,1,0)</f>
+        <f t="shared" si="11"/>
         <v>#N/A</v>
       </c>
     </row>
@@ -24154,13 +24155,13 @@
       <c r="C719" s="3"/>
       <c r="F719" s="10"/>
       <c r="G719" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="H719" s="33" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="I719" t="e">
-        <f>VLOOKUP(G719,D:D,1,0)</f>
+        <f t="shared" si="11"/>
         <v>#N/A</v>
       </c>
     </row>
@@ -24173,10 +24174,10 @@
         <v>484</v>
       </c>
       <c r="H720" s="33" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="I720" t="str">
-        <f>VLOOKUP(G720,D:D,1,0)</f>
+        <f t="shared" si="11"/>
         <v>89560900000863585632</v>
       </c>
     </row>
@@ -24185,13 +24186,13 @@
       <c r="B721" s="36"/>
       <c r="F721" s="10"/>
       <c r="G721" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="H721" s="33" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="I721" t="e">
-        <f>VLOOKUP(G721,D:D,1,0)</f>
+        <f t="shared" si="11"/>
         <v>#N/A</v>
       </c>
     </row>
@@ -24200,13 +24201,13 @@
       <c r="B722" s="36"/>
       <c r="F722" s="10"/>
       <c r="G722" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="H722" s="33" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="I722" t="e">
-        <f>VLOOKUP(G722,D:D,1,0)</f>
+        <f t="shared" si="11"/>
         <v>#N/A</v>
       </c>
     </row>
@@ -24215,13 +24216,13 @@
       <c r="B723" s="36"/>
       <c r="F723" s="10"/>
       <c r="G723" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="H723" s="33" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="I723" t="e">
-        <f>VLOOKUP(G723,D:D,1,0)</f>
+        <f t="shared" si="11"/>
         <v>#N/A</v>
       </c>
     </row>
@@ -24230,13 +24231,13 @@
       <c r="B724" s="36"/>
       <c r="F724" s="10"/>
       <c r="G724" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="H724" s="33" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="I724" t="e">
-        <f>VLOOKUP(G724,D:D,1,0)</f>
+        <f t="shared" si="11"/>
         <v>#N/A</v>
       </c>
     </row>
@@ -24245,13 +24246,13 @@
       <c r="B725" s="36"/>
       <c r="F725" s="10"/>
       <c r="G725" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="H725" s="33" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="I725" t="e">
-        <f>VLOOKUP(G725,D:D,1,0)</f>
+        <f t="shared" si="11"/>
         <v>#N/A</v>
       </c>
     </row>
@@ -24260,13 +24261,13 @@
       <c r="B726" s="36"/>
       <c r="F726" s="10"/>
       <c r="G726" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="H726" s="33" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="I726" t="e">
-        <f>VLOOKUP(G726,D:D,1,0)</f>
+        <f t="shared" si="11"/>
         <v>#N/A</v>
       </c>
     </row>
@@ -24275,13 +24276,13 @@
       <c r="B727" s="36"/>
       <c r="F727" s="10"/>
       <c r="G727" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="H727" s="33" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="I727" t="e">
-        <f>VLOOKUP(G727,D:D,1,0)</f>
+        <f t="shared" si="11"/>
         <v>#N/A</v>
       </c>
     </row>
@@ -24290,13 +24291,13 @@
       <c r="B728" s="36"/>
       <c r="F728" s="10"/>
       <c r="G728" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="H728" s="33" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="I728" t="str">
-        <f>VLOOKUP(G728,D:D,1,0)</f>
+        <f t="shared" si="11"/>
         <v>89560900000863585582</v>
       </c>
     </row>
@@ -24305,13 +24306,13 @@
       <c r="B729" s="36"/>
       <c r="F729" s="10"/>
       <c r="G729" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="H729" s="33" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="I729" t="e">
-        <f>VLOOKUP(G729,D:D,1,0)</f>
+        <f t="shared" si="11"/>
         <v>#N/A</v>
       </c>
     </row>
@@ -24323,10 +24324,10 @@
         <v>972</v>
       </c>
       <c r="H730" s="33" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="I730" t="str">
-        <f>VLOOKUP(G730,D:D,1,0)</f>
+        <f t="shared" si="11"/>
         <v>89560900000863586739</v>
       </c>
     </row>
@@ -24335,13 +24336,13 @@
       <c r="B731" s="36"/>
       <c r="F731" s="10"/>
       <c r="G731" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="H731" s="33" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="I731" t="e">
-        <f>VLOOKUP(G731,D:D,1,0)</f>
+        <f t="shared" si="11"/>
         <v>#N/A</v>
       </c>
     </row>
@@ -24353,10 +24354,10 @@
         <v>1031</v>
       </c>
       <c r="H732" s="33" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="I732" t="str">
-        <f>VLOOKUP(G732,D:D,1,0)</f>
+        <f t="shared" si="11"/>
         <v>89560900000863586754</v>
       </c>
     </row>
@@ -24365,13 +24366,13 @@
       <c r="B733" s="36"/>
       <c r="F733" s="10"/>
       <c r="G733" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="H733" s="33" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="I733" t="e">
-        <f>VLOOKUP(G733,D:D,1,0)</f>
+        <f t="shared" si="11"/>
         <v>#N/A</v>
       </c>
     </row>
@@ -24383,10 +24384,10 @@
         <v>1286</v>
       </c>
       <c r="H734" s="33" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="I734" t="str">
-        <f>VLOOKUP(G734,D:D,1,0)</f>
+        <f t="shared" si="11"/>
         <v>89560900000863585566</v>
       </c>
     </row>
@@ -24395,13 +24396,13 @@
       <c r="B735" s="36"/>
       <c r="F735" s="10"/>
       <c r="G735" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="H735" s="33" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="I735" t="str">
-        <f>VLOOKUP(G735,D:D,1,0)</f>
+        <f t="shared" si="11"/>
         <v>89560900000863585558</v>
       </c>
     </row>
@@ -24410,13 +24411,13 @@
       <c r="B736" s="36"/>
       <c r="F736" s="10"/>
       <c r="G736" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="H736" s="33" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="I736" t="e">
-        <f>VLOOKUP(G736,D:D,1,0)</f>
+        <f t="shared" si="11"/>
         <v>#N/A</v>
       </c>
     </row>
@@ -24425,13 +24426,13 @@
       <c r="B737" s="36"/>
       <c r="F737" s="10"/>
       <c r="G737" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="H737" s="33" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="I737" t="str">
-        <f>VLOOKUP(G737,D:D,1,0)</f>
+        <f t="shared" si="11"/>
         <v>89560900000863574248</v>
       </c>
     </row>
@@ -24440,13 +24441,13 @@
       <c r="B738" s="36"/>
       <c r="F738" s="10"/>
       <c r="G738" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="H738" s="33" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="I738" t="e">
-        <f>VLOOKUP(G738,D:D,1,0)</f>
+        <f t="shared" si="11"/>
         <v>#N/A</v>
       </c>
     </row>
@@ -24458,10 +24459,10 @@
         <v>274</v>
       </c>
       <c r="H739" s="33" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="I739" t="str">
-        <f>VLOOKUP(G739,D:D,1,0)</f>
+        <f t="shared" si="11"/>
         <v>89560900000863574057</v>
       </c>
     </row>
@@ -24470,13 +24471,13 @@
       <c r="B740" s="36"/>
       <c r="F740" s="10"/>
       <c r="G740" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="H740" s="33" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="I740" t="e">
-        <f>VLOOKUP(G740,D:D,1,0)</f>
+        <f t="shared" si="11"/>
         <v>#N/A</v>
       </c>
     </row>
@@ -24485,13 +24486,13 @@
       <c r="B741" s="36"/>
       <c r="F741" s="10"/>
       <c r="G741" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="H741" s="33" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="I741" t="e">
-        <f>VLOOKUP(G741,D:D,1,0)</f>
+        <f t="shared" si="11"/>
         <v>#N/A</v>
       </c>
     </row>
@@ -24503,10 +24504,10 @@
         <v>1073</v>
       </c>
       <c r="H742" s="33" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="I742" t="str">
-        <f>VLOOKUP(G742,D:D,1,0)</f>
+        <f t="shared" si="11"/>
         <v>89560900000863574206</v>
       </c>
     </row>
@@ -24515,13 +24516,13 @@
       <c r="B743" s="36"/>
       <c r="F743" s="10"/>
       <c r="G743" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="H743" s="33" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="I743" t="e">
-        <f>VLOOKUP(G743,D:D,1,0)</f>
+        <f t="shared" si="11"/>
         <v>#N/A</v>
       </c>
     </row>
@@ -24530,13 +24531,13 @@
       <c r="B744" s="36"/>
       <c r="F744" s="10"/>
       <c r="G744" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="H744" s="33" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="I744" t="e">
-        <f>VLOOKUP(G744,D:D,1,0)</f>
+        <f t="shared" si="11"/>
         <v>#N/A</v>
       </c>
     </row>
@@ -24544,30 +24545,30 @@
       <c r="A745" s="35"/>
       <c r="B745" s="36"/>
       <c r="G745" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="H745" s="33" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="746" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A746" s="35"/>
       <c r="B746" s="36"/>
       <c r="G746" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="H746" s="33" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="747" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A747" s="35"/>
       <c r="B747" s="36"/>
       <c r="G747" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="H747" s="33" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="748" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
@@ -24577,7 +24578,7 @@
         <v>166</v>
       </c>
       <c r="H748" s="33" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="749" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
@@ -25001,7 +25002,7 @@
       <c r="B853" s="36"/>
     </row>
   </sheetData>
-  <autoFilter ref="G1:K744" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
+  <autoFilter ref="A1:D619" xr:uid="{B0B3DB5E-92A7-4CC4-9B7D-0BC3DF3498E9}"/>
   <conditionalFormatting sqref="C609:D609">
     <cfRule type="expression" dxfId="5" priority="5">
       <formula>NOT(ISERROR(VLOOKUP(C609,#REF!,1,0)))</formula>

--- a/Libro1.xlsx
+++ b/Libro1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hug.leon\Desktop\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C337B92-00E4-463B-89C9-C9F9F0F2A971}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{942BB4D4-5500-4977-B97E-92BD10D20A35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{04497E22-FEAF-4EAE-A69F-4E82C41B14CF}"/>
   </bookViews>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3374" uniqueCount="1363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3474" uniqueCount="1413">
   <si>
     <t>Bus</t>
   </si>
@@ -4166,13 +4166,163 @@
   </si>
   <si>
     <t>8956032256758023225</t>
+  </si>
+  <si>
+    <t>89560900000863707921</t>
+  </si>
+  <si>
+    <t>89560900000863707954</t>
+  </si>
+  <si>
+    <t>89560900000863707962</t>
+  </si>
+  <si>
+    <t>89560900000863707970</t>
+  </si>
+  <si>
+    <t>89560900000863707988</t>
+  </si>
+  <si>
+    <t>89560900000863707996</t>
+  </si>
+  <si>
+    <t>89560900000863708069</t>
+  </si>
+  <si>
+    <t>89560900000863708077</t>
+  </si>
+  <si>
+    <t>89560900000863708143</t>
+  </si>
+  <si>
+    <t>89560900000863708275</t>
+  </si>
+  <si>
+    <t>89560900000863708283</t>
+  </si>
+  <si>
+    <t>89560900000863708291</t>
+  </si>
+  <si>
+    <t>89560900000863708309</t>
+  </si>
+  <si>
+    <t>89560900000863708317</t>
+  </si>
+  <si>
+    <t>89560900000863708325</t>
+  </si>
+  <si>
+    <t>89560900000863708333</t>
+  </si>
+  <si>
+    <t>89560900000863708341</t>
+  </si>
+  <si>
+    <t>89560900000863708556</t>
+  </si>
+  <si>
+    <t>89560900000863708598</t>
+  </si>
+  <si>
+    <t>89560900000863708630</t>
+  </si>
+  <si>
+    <t>89560900000863708648</t>
+  </si>
+  <si>
+    <t>89560900000863708655</t>
+  </si>
+  <si>
+    <t>89560900000863708663</t>
+  </si>
+  <si>
+    <t>89560900000863708671</t>
+  </si>
+  <si>
+    <t>89560900000863708689</t>
+  </si>
+  <si>
+    <t>89560900000863708697</t>
+  </si>
+  <si>
+    <t>89560900000863708705</t>
+  </si>
+  <si>
+    <t>89560900000863708747</t>
+  </si>
+  <si>
+    <t>89560900000863708754</t>
+  </si>
+  <si>
+    <t>89560900000863708762</t>
+  </si>
+  <si>
+    <t>89560900000863708804</t>
+  </si>
+  <si>
+    <t>89560900000863708812</t>
+  </si>
+  <si>
+    <t>89560900000863708820</t>
+  </si>
+  <si>
+    <t>89560900000863708846</t>
+  </si>
+  <si>
+    <t>89560900000863708853</t>
+  </si>
+  <si>
+    <t>89560900000863708861</t>
+  </si>
+  <si>
+    <t>89560900000863708887</t>
+  </si>
+  <si>
+    <t>89560900000876934165</t>
+  </si>
+  <si>
+    <t>89560900000886139003</t>
+  </si>
+  <si>
+    <t>89560900000928036274</t>
+  </si>
+  <si>
+    <t>89560900000928036282</t>
+  </si>
+  <si>
+    <t>89560900000928036290</t>
+  </si>
+  <si>
+    <t>89560900000928036308</t>
+  </si>
+  <si>
+    <t>89560900000928036316</t>
+  </si>
+  <si>
+    <t>89560900000928036340</t>
+  </si>
+  <si>
+    <t>89560900000928036431</t>
+  </si>
+  <si>
+    <t>89560900000928036449</t>
+  </si>
+  <si>
+    <t>89560900000928036456</t>
+  </si>
+  <si>
+    <t>89560900000928036480</t>
+  </si>
+  <si>
+    <t>89560900000928036498</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4237,8 +4387,13 @@
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4315,6 +4470,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFB34DBB"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9F6FC"/>
+        <bgColor rgb="FFF9F6FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFF9F6FC"/>
       </patternFill>
     </fill>
   </fills>
@@ -4438,7 +4605,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4525,6 +4692,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="9" fillId="14" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="15" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -22862,8 +23035,8 @@
       <c r="B655" s="29"/>
       <c r="C655" s="3"/>
       <c r="F655" s="10"/>
-      <c r="G655" t="s">
-        <v>1307</v>
+      <c r="G655" s="38" t="s">
+        <v>1339</v>
       </c>
       <c r="H655" s="31" t="s">
         <v>1308</v>
@@ -22879,8 +23052,8 @@
       <c r="B656" s="29"/>
       <c r="C656" s="3"/>
       <c r="F656" s="10"/>
-      <c r="G656" t="s">
-        <v>1309</v>
+      <c r="G656" s="38" t="s">
+        <v>1340</v>
       </c>
       <c r="H656" s="31" t="s">
         <v>1308</v>
@@ -22896,8 +23069,8 @@
       <c r="B657" s="29"/>
       <c r="C657" s="3"/>
       <c r="F657" s="10"/>
-      <c r="G657" t="s">
-        <v>1310</v>
+      <c r="G657" s="38" t="s">
+        <v>1338</v>
       </c>
       <c r="H657" s="31" t="s">
         <v>1308</v>
@@ -22913,15 +23086,15 @@
       <c r="B658" s="29"/>
       <c r="C658" s="3"/>
       <c r="F658" s="10"/>
-      <c r="G658" t="s">
-        <v>1311</v>
+      <c r="G658" s="38" t="s">
+        <v>166</v>
       </c>
       <c r="H658" s="31" t="s">
         <v>1308</v>
       </c>
-      <c r="I658" t="e">
+      <c r="I658" t="str">
         <f t="shared" si="10"/>
-        <v>#N/A</v>
+        <v>89560900000863574032</v>
       </c>
       <c r="J658" s="11"/>
     </row>
@@ -22930,8 +23103,8 @@
       <c r="B659" s="29"/>
       <c r="C659" s="3"/>
       <c r="F659" s="10"/>
-      <c r="G659" t="s">
-        <v>1312</v>
+      <c r="G659" s="38" t="s">
+        <v>1342</v>
       </c>
       <c r="H659" s="31" t="s">
         <v>1308</v>
@@ -22947,15 +23120,15 @@
       <c r="B660" s="29"/>
       <c r="C660" s="3"/>
       <c r="F660" s="10"/>
-      <c r="G660" t="s">
-        <v>698</v>
+      <c r="G660" s="38" t="s">
+        <v>269</v>
       </c>
       <c r="H660" s="31" t="s">
         <v>1308</v>
       </c>
       <c r="I660" t="str">
         <f t="shared" si="10"/>
-        <v>89560900000863586762</v>
+        <v>89560900000863574057</v>
       </c>
       <c r="J660" s="11"/>
     </row>
@@ -22964,15 +23137,15 @@
       <c r="B661" s="29"/>
       <c r="C661" s="3"/>
       <c r="F661" s="10"/>
-      <c r="G661" t="s">
-        <v>1313</v>
+      <c r="G661" s="38" t="s">
+        <v>1287</v>
       </c>
       <c r="H661" s="31" t="s">
         <v>1308</v>
       </c>
-      <c r="I661" t="e">
+      <c r="I661" t="str">
         <f t="shared" si="10"/>
-        <v>#N/A</v>
+        <v>89560900000863574065</v>
       </c>
       <c r="J661" s="11"/>
     </row>
@@ -22981,7 +23154,7 @@
       <c r="B662" s="29"/>
       <c r="C662" s="3"/>
       <c r="F662" s="10"/>
-      <c r="G662" t="s">
+      <c r="G662" s="38" t="s">
         <v>1314</v>
       </c>
       <c r="H662" s="31" t="s">
@@ -22998,8 +23171,8 @@
       <c r="B663" s="29"/>
       <c r="C663" s="3"/>
       <c r="F663" s="10"/>
-      <c r="G663" t="s">
-        <v>1315</v>
+      <c r="G663" s="38" t="s">
+        <v>1328</v>
       </c>
       <c r="H663" s="31" t="s">
         <v>1308</v>
@@ -23015,15 +23188,15 @@
       <c r="B664" s="29"/>
       <c r="C664" s="3"/>
       <c r="F664" s="10"/>
-      <c r="G664" t="s">
-        <v>885</v>
+      <c r="G664" s="38" t="s">
+        <v>1312</v>
       </c>
       <c r="H664" s="31" t="s">
         <v>1308</v>
       </c>
-      <c r="I664" t="str">
+      <c r="I664" t="e">
         <f t="shared" si="10"/>
-        <v>89560900000863585764</v>
+        <v>#N/A</v>
       </c>
       <c r="J664" s="11"/>
     </row>
@@ -23032,8 +23205,8 @@
       <c r="B665" s="29"/>
       <c r="C665" s="3"/>
       <c r="F665" s="10"/>
-      <c r="G665" t="s">
-        <v>1316</v>
+      <c r="G665" s="38" t="s">
+        <v>1311</v>
       </c>
       <c r="H665" s="31" t="s">
         <v>1308</v>
@@ -23049,8 +23222,8 @@
       <c r="B666" s="29"/>
       <c r="C666" s="3"/>
       <c r="F666" s="10"/>
-      <c r="G666" t="s">
-        <v>1317</v>
+      <c r="G666" s="38" t="s">
+        <v>1331</v>
       </c>
       <c r="H666" s="31" t="s">
         <v>1308</v>
@@ -23066,15 +23239,15 @@
       <c r="B667" s="29"/>
       <c r="C667" s="3"/>
       <c r="F667" s="10"/>
-      <c r="G667" t="s">
-        <v>1018</v>
+      <c r="G667" s="38" t="s">
+        <v>1326</v>
       </c>
       <c r="H667" s="31" t="s">
         <v>1308</v>
       </c>
-      <c r="I667" t="str">
+      <c r="I667" t="e">
         <f t="shared" si="10"/>
-        <v>89560900000863585756</v>
+        <v>#N/A</v>
       </c>
       <c r="J667" s="11"/>
     </row>
@@ -23083,15 +23256,15 @@
       <c r="B668" s="29"/>
       <c r="C668" s="3"/>
       <c r="F668" s="10"/>
-      <c r="G668" t="s">
-        <v>971</v>
+      <c r="G668" s="38" t="s">
+        <v>1105</v>
       </c>
       <c r="H668" s="31" t="s">
         <v>1308</v>
       </c>
       <c r="I668" t="str">
         <f t="shared" si="10"/>
-        <v>89560900000863585699</v>
+        <v>89560900000863574164</v>
       </c>
       <c r="J668" s="11"/>
     </row>
@@ -23100,15 +23273,15 @@
       <c r="B669" s="29"/>
       <c r="C669" s="3"/>
       <c r="F669" s="10"/>
-      <c r="G669" t="s">
-        <v>396</v>
+      <c r="G669" s="38" t="s">
+        <v>1316</v>
       </c>
       <c r="H669" s="31" t="s">
         <v>1308</v>
       </c>
-      <c r="I669" t="str">
+      <c r="I669" t="e">
         <f t="shared" si="10"/>
-        <v>89560900000863585681</v>
+        <v>#N/A</v>
       </c>
       <c r="J669" s="11"/>
     </row>
@@ -23117,15 +23290,15 @@
       <c r="B670" s="29"/>
       <c r="C670" s="3"/>
       <c r="F670" s="10"/>
-      <c r="G670" t="s">
-        <v>1105</v>
+      <c r="G670" s="38" t="s">
+        <v>1317</v>
       </c>
       <c r="H670" s="31" t="s">
         <v>1308</v>
       </c>
-      <c r="I670" t="str">
+      <c r="I670" t="e">
         <f t="shared" si="10"/>
-        <v>89560900000863574164</v>
+        <v>#N/A</v>
       </c>
       <c r="J670" s="11"/>
     </row>
@@ -23134,15 +23307,15 @@
       <c r="B671" s="29"/>
       <c r="C671" s="3"/>
       <c r="F671" s="10"/>
-      <c r="G671" t="s">
-        <v>1287</v>
+      <c r="G671" s="38" t="s">
+        <v>1315</v>
       </c>
       <c r="H671" s="31" t="s">
         <v>1308</v>
       </c>
-      <c r="I671" t="str">
+      <c r="I671" t="e">
         <f t="shared" si="10"/>
-        <v>89560900000863574065</v>
+        <v>#N/A</v>
       </c>
       <c r="J671" s="11"/>
     </row>
@@ -23151,15 +23324,15 @@
       <c r="B672" s="29"/>
       <c r="C672" s="3"/>
       <c r="F672" s="10"/>
-      <c r="G672" t="s">
-        <v>1318</v>
+      <c r="G672" s="38" t="s">
+        <v>1019</v>
       </c>
       <c r="H672" s="31" t="s">
         <v>1308</v>
       </c>
-      <c r="I672" t="e">
+      <c r="I672" t="str">
         <f t="shared" si="10"/>
-        <v>#N/A</v>
+        <v>89560900000863574206</v>
       </c>
       <c r="J672" s="11"/>
     </row>
@@ -23168,8 +23341,8 @@
       <c r="B673" s="29"/>
       <c r="C673" s="3"/>
       <c r="F673" s="10"/>
-      <c r="G673" t="s">
-        <v>1319</v>
+      <c r="G673" s="38" t="s">
+        <v>1337</v>
       </c>
       <c r="H673" s="31" t="s">
         <v>1308</v>
@@ -23185,8 +23358,8 @@
       <c r="B674" s="29"/>
       <c r="C674" s="3"/>
       <c r="F674" s="10"/>
-      <c r="G674" t="s">
-        <v>1320</v>
+      <c r="G674" s="38" t="s">
+        <v>1336</v>
       </c>
       <c r="H674" s="31" t="s">
         <v>1308</v>
@@ -23202,15 +23375,15 @@
       <c r="B675" s="29"/>
       <c r="C675" s="3"/>
       <c r="F675" s="10"/>
-      <c r="G675" t="s">
-        <v>445</v>
+      <c r="G675" s="38" t="s">
+        <v>1335</v>
       </c>
       <c r="H675" s="31" t="s">
         <v>1308</v>
       </c>
-      <c r="I675" t="str">
+      <c r="I675" t="e">
         <f t="shared" si="10"/>
-        <v>89560900000863585749</v>
+        <v>#N/A</v>
       </c>
       <c r="J675" s="11"/>
     </row>
@@ -23219,15 +23392,15 @@
       <c r="B676" s="29"/>
       <c r="C676" s="3"/>
       <c r="F676" s="10"/>
-      <c r="G676" t="s">
-        <v>1321</v>
+      <c r="G676" s="38" t="s">
+        <v>1297</v>
       </c>
       <c r="H676" s="31" t="s">
         <v>1308</v>
       </c>
-      <c r="I676" t="e">
+      <c r="I676" t="str">
         <f t="shared" si="10"/>
-        <v>#N/A</v>
+        <v>89560900000863574248</v>
       </c>
       <c r="J676" s="11"/>
     </row>
@@ -23236,8 +23409,8 @@
       <c r="B677" s="29"/>
       <c r="C677" s="3"/>
       <c r="F677" s="10"/>
-      <c r="G677" t="s">
-        <v>1322</v>
+      <c r="G677" s="38" t="s">
+        <v>1310</v>
       </c>
       <c r="H677" s="31" t="s">
         <v>1308</v>
@@ -23253,8 +23426,8 @@
       <c r="B678" s="29"/>
       <c r="C678" s="3"/>
       <c r="F678" s="10"/>
-      <c r="G678" t="s">
-        <v>1323</v>
+      <c r="G678" s="38" t="s">
+        <v>1313</v>
       </c>
       <c r="H678" s="31" t="s">
         <v>1308</v>
@@ -23270,15 +23443,15 @@
       <c r="B679" s="29"/>
       <c r="C679" s="3"/>
       <c r="F679" s="10"/>
-      <c r="G679" t="s">
-        <v>467</v>
+      <c r="G679" s="38" t="s">
+        <v>1307</v>
       </c>
       <c r="H679" s="31" t="s">
         <v>1308</v>
       </c>
-      <c r="I679" t="str">
+      <c r="I679" t="e">
         <f t="shared" si="10"/>
-        <v>89560900000863585632</v>
+        <v>#N/A</v>
       </c>
       <c r="J679" s="11"/>
     </row>
@@ -23287,8 +23460,8 @@
       <c r="B680" s="29"/>
       <c r="C680" s="3"/>
       <c r="F680" s="10"/>
-      <c r="G680" t="s">
-        <v>1324</v>
+      <c r="G680" s="38" t="s">
+        <v>1341</v>
       </c>
       <c r="H680" s="31" t="s">
         <v>1308</v>
@@ -23304,8 +23477,8 @@
       <c r="B681" s="29"/>
       <c r="C681" s="3"/>
       <c r="F681" s="10"/>
-      <c r="G681" t="s">
-        <v>1325</v>
+      <c r="G681" s="38" t="s">
+        <v>1309</v>
       </c>
       <c r="H681" s="31" t="s">
         <v>1308</v>
@@ -23321,15 +23494,15 @@
       <c r="B682" s="29"/>
       <c r="C682" s="3"/>
       <c r="F682" s="10"/>
-      <c r="G682" t="s">
-        <v>1326</v>
+      <c r="G682" s="38" t="s">
+        <v>1299</v>
       </c>
       <c r="H682" s="31" t="s">
         <v>1308</v>
       </c>
-      <c r="I682" t="e">
+      <c r="I682" t="str">
         <f t="shared" si="10"/>
-        <v>#N/A</v>
+        <v>89560900000863585558</v>
       </c>
       <c r="J682" s="11"/>
     </row>
@@ -23338,15 +23511,15 @@
       <c r="B683" s="29"/>
       <c r="C683" s="3"/>
       <c r="F683" s="10"/>
-      <c r="G683" t="s">
-        <v>1327</v>
+      <c r="G683" s="38" t="s">
+        <v>1220</v>
       </c>
       <c r="H683" s="31" t="s">
         <v>1308</v>
       </c>
-      <c r="I683" t="e">
+      <c r="I683" t="str">
         <f t="shared" si="10"/>
-        <v>#N/A</v>
+        <v>89560900000863585566</v>
       </c>
       <c r="J683" s="11"/>
     </row>
@@ -23355,8 +23528,8 @@
       <c r="B684" s="29"/>
       <c r="C684" s="3"/>
       <c r="F684" s="10"/>
-      <c r="G684" t="s">
-        <v>1328</v>
+      <c r="G684" s="38" t="s">
+        <v>1332</v>
       </c>
       <c r="H684" s="31" t="s">
         <v>1308</v>
@@ -23372,15 +23545,15 @@
       <c r="B685" s="29"/>
       <c r="C685" s="3"/>
       <c r="F685" s="10"/>
-      <c r="G685" t="s">
-        <v>1329</v>
+      <c r="G685" s="38" t="s">
+        <v>1241</v>
       </c>
       <c r="H685" s="31" t="s">
         <v>1308</v>
       </c>
-      <c r="I685" t="e">
+      <c r="I685" t="str">
         <f t="shared" si="10"/>
-        <v>#N/A</v>
+        <v>89560900000863585582</v>
       </c>
       <c r="J685" s="11"/>
     </row>
@@ -23389,7 +23562,7 @@
       <c r="B686" s="29"/>
       <c r="C686" s="3"/>
       <c r="F686" s="10"/>
-      <c r="G686" t="s">
+      <c r="G686" s="38" t="s">
         <v>1330</v>
       </c>
       <c r="H686" s="31" t="s">
@@ -23406,15 +23579,15 @@
       <c r="B687" s="29"/>
       <c r="C687" s="3"/>
       <c r="F687" s="10"/>
-      <c r="G687" t="s">
-        <v>1241</v>
+      <c r="G687" s="38" t="s">
+        <v>1327</v>
       </c>
       <c r="H687" s="31" t="s">
         <v>1308</v>
       </c>
-      <c r="I687" t="str">
+      <c r="I687" t="e">
         <f t="shared" si="10"/>
-        <v>89560900000863585582</v>
+        <v>#N/A</v>
       </c>
       <c r="J687" s="11"/>
     </row>
@@ -23423,8 +23596,8 @@
       <c r="B688" s="29"/>
       <c r="C688" s="3"/>
       <c r="F688" s="10"/>
-      <c r="G688" t="s">
-        <v>1331</v>
+      <c r="G688" s="38" t="s">
+        <v>1325</v>
       </c>
       <c r="H688" s="31" t="s">
         <v>1308</v>
@@ -23440,15 +23613,15 @@
       <c r="B689" s="29"/>
       <c r="C689" s="3"/>
       <c r="F689" s="10"/>
-      <c r="G689" t="s">
-        <v>928</v>
+      <c r="G689" s="38" t="s">
+        <v>467</v>
       </c>
       <c r="H689" s="31" t="s">
         <v>1308</v>
       </c>
       <c r="I689" t="str">
         <f t="shared" si="10"/>
-        <v>89560900000863586739</v>
+        <v>89560900000863585632</v>
       </c>
       <c r="J689" s="11"/>
     </row>
@@ -23457,8 +23630,8 @@
       <c r="B690" s="29"/>
       <c r="C690" s="3"/>
       <c r="F690" s="10"/>
-      <c r="G690" t="s">
-        <v>1332</v>
+      <c r="G690" s="38" t="s">
+        <v>1323</v>
       </c>
       <c r="H690" s="31" t="s">
         <v>1308</v>
@@ -23474,15 +23647,15 @@
       <c r="B691" s="29"/>
       <c r="C691" s="3"/>
       <c r="F691" s="10"/>
-      <c r="G691" t="s">
-        <v>984</v>
+      <c r="G691" s="38" t="s">
+        <v>1321</v>
       </c>
       <c r="H691" s="31" t="s">
         <v>1308</v>
       </c>
-      <c r="I691" t="str">
+      <c r="I691" t="e">
         <f t="shared" si="10"/>
-        <v>89560900000863586754</v>
+        <v>#N/A</v>
       </c>
       <c r="J691" s="11"/>
     </row>
@@ -23491,8 +23664,8 @@
       <c r="B692" s="29"/>
       <c r="C692" s="3"/>
       <c r="F692" s="10"/>
-      <c r="G692" t="s">
-        <v>1333</v>
+      <c r="G692" s="38" t="s">
+        <v>1320</v>
       </c>
       <c r="H692" s="31" t="s">
         <v>1308</v>
@@ -23508,15 +23681,15 @@
       <c r="B693" s="29"/>
       <c r="C693" s="3"/>
       <c r="F693" s="10"/>
-      <c r="G693" t="s">
-        <v>1220</v>
+      <c r="G693" s="38" t="s">
+        <v>1318</v>
       </c>
       <c r="H693" s="31" t="s">
         <v>1308</v>
       </c>
-      <c r="I693" t="str">
+      <c r="I693" t="e">
         <f t="shared" si="10"/>
-        <v>89560900000863585566</v>
+        <v>#N/A</v>
       </c>
       <c r="J693" s="11"/>
     </row>
@@ -23525,15 +23698,15 @@
       <c r="B694" s="29"/>
       <c r="C694" s="3"/>
       <c r="F694" s="10"/>
-      <c r="G694" t="s">
-        <v>1299</v>
+      <c r="G694" s="38" t="s">
+        <v>396</v>
       </c>
       <c r="H694" s="31" t="s">
         <v>1308</v>
       </c>
       <c r="I694" t="str">
         <f t="shared" si="10"/>
-        <v>89560900000863585558</v>
+        <v>89560900000863585681</v>
       </c>
       <c r="J694" s="11"/>
     </row>
@@ -23542,15 +23715,15 @@
       <c r="B695" s="29"/>
       <c r="C695" s="3"/>
       <c r="F695" s="10"/>
-      <c r="G695" t="s">
-        <v>1334</v>
+      <c r="G695" s="38" t="s">
+        <v>971</v>
       </c>
       <c r="H695" s="31" t="s">
         <v>1308</v>
       </c>
-      <c r="I695" t="e">
+      <c r="I695" t="str">
         <f t="shared" si="10"/>
-        <v>#N/A</v>
+        <v>89560900000863585699</v>
       </c>
       <c r="J695" s="11"/>
     </row>
@@ -23559,15 +23732,15 @@
       <c r="B696" s="29"/>
       <c r="C696" s="3"/>
       <c r="F696" s="10"/>
-      <c r="G696" t="s">
-        <v>1297</v>
+      <c r="G696" s="38" t="s">
+        <v>1319</v>
       </c>
       <c r="H696" s="31" t="s">
         <v>1308</v>
       </c>
-      <c r="I696" t="str">
+      <c r="I696" t="e">
         <f t="shared" si="10"/>
-        <v>89560900000863574248</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="697" spans="1:10" thickBot="1" x14ac:dyDescent="0.3">
@@ -23575,8 +23748,8 @@
       <c r="B697" s="29"/>
       <c r="C697" s="3"/>
       <c r="F697" s="10"/>
-      <c r="G697" t="s">
-        <v>1335</v>
+      <c r="G697" s="38" t="s">
+        <v>1324</v>
       </c>
       <c r="H697" s="31" t="s">
         <v>1308</v>
@@ -23591,15 +23764,15 @@
       <c r="B698" s="29"/>
       <c r="C698" s="3"/>
       <c r="F698" s="10"/>
-      <c r="G698" t="s">
-        <v>269</v>
+      <c r="G698" s="38" t="s">
+        <v>1329</v>
       </c>
       <c r="H698" s="31" t="s">
         <v>1308</v>
       </c>
-      <c r="I698" t="str">
+      <c r="I698" t="e">
         <f t="shared" si="10"/>
-        <v>89560900000863574057</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="699" spans="1:10" thickBot="1" x14ac:dyDescent="0.3">
@@ -23607,8 +23780,8 @@
       <c r="B699" s="29"/>
       <c r="C699" s="3"/>
       <c r="F699" s="10"/>
-      <c r="G699" t="s">
-        <v>1336</v>
+      <c r="G699" s="38" t="s">
+        <v>1322</v>
       </c>
       <c r="H699" s="31" t="s">
         <v>1308</v>
@@ -23623,15 +23796,15 @@
       <c r="B700" s="29"/>
       <c r="C700" s="3"/>
       <c r="F700" s="10"/>
-      <c r="G700" t="s">
-        <v>1337</v>
+      <c r="G700" s="38" t="s">
+        <v>445</v>
       </c>
       <c r="H700" s="31" t="s">
         <v>1308</v>
       </c>
-      <c r="I700" t="e">
+      <c r="I700" t="str">
         <f t="shared" si="10"/>
-        <v>#N/A</v>
+        <v>89560900000863585749</v>
       </c>
     </row>
     <row r="701" spans="1:10" thickBot="1" x14ac:dyDescent="0.3">
@@ -23639,15 +23812,15 @@
       <c r="B701" s="29"/>
       <c r="C701" s="3"/>
       <c r="F701" s="10"/>
-      <c r="G701" t="s">
-        <v>1019</v>
+      <c r="G701" s="38" t="s">
+        <v>1018</v>
       </c>
       <c r="H701" s="31" t="s">
         <v>1308</v>
       </c>
       <c r="I701" t="str">
         <f t="shared" si="10"/>
-        <v>89560900000863574206</v>
+        <v>89560900000863585756</v>
       </c>
     </row>
     <row r="702" spans="1:10" thickBot="1" x14ac:dyDescent="0.3">
@@ -23655,15 +23828,15 @@
       <c r="B702" s="29"/>
       <c r="C702" s="3"/>
       <c r="F702" s="10"/>
-      <c r="G702" t="s">
-        <v>1338</v>
+      <c r="G702" s="38" t="s">
+        <v>885</v>
       </c>
       <c r="H702" s="31" t="s">
         <v>1308</v>
       </c>
-      <c r="I702" t="e">
+      <c r="I702" t="str">
         <f t="shared" si="10"/>
-        <v>#N/A</v>
+        <v>89560900000863585764</v>
       </c>
     </row>
     <row r="703" spans="1:10" thickBot="1" x14ac:dyDescent="0.3">
@@ -23671,8 +23844,8 @@
       <c r="B703" s="29"/>
       <c r="C703" s="3"/>
       <c r="F703" s="10"/>
-      <c r="G703" t="s">
-        <v>1339</v>
+      <c r="G703" s="38" t="s">
+        <v>1334</v>
       </c>
       <c r="H703" s="31" t="s">
         <v>1308</v>
@@ -23687,8 +23860,8 @@
       <c r="B704" s="29"/>
       <c r="C704" s="3"/>
       <c r="F704" s="10"/>
-      <c r="G704" t="s">
-        <v>1340</v>
+      <c r="G704" s="38" t="s">
+        <v>1333</v>
       </c>
       <c r="H704" s="31" t="s">
         <v>1308</v>
@@ -23703,15 +23876,15 @@
       <c r="B705" s="29"/>
       <c r="C705" s="3"/>
       <c r="F705" s="10"/>
-      <c r="G705" t="s">
-        <v>1341</v>
+      <c r="G705" s="38" t="s">
+        <v>928</v>
       </c>
       <c r="H705" s="31" t="s">
         <v>1308</v>
       </c>
-      <c r="I705" t="e">
+      <c r="I705" t="str">
         <f t="shared" si="10"/>
-        <v>#N/A</v>
+        <v>89560900000863586739</v>
       </c>
     </row>
     <row r="706" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
@@ -23719,15 +23892,15 @@
       <c r="B706" s="29"/>
       <c r="C706" s="3"/>
       <c r="F706" s="10"/>
-      <c r="G706" t="s">
-        <v>1342</v>
+      <c r="G706" s="38" t="s">
+        <v>984</v>
       </c>
       <c r="H706" s="31" t="s">
         <v>1308</v>
       </c>
-      <c r="I706" t="e">
-        <f t="shared" ref="I706:I744" si="11">VLOOKUP(G706,D:D,1,0)</f>
-        <v>#N/A</v>
+      <c r="I706" t="str">
+        <f t="shared" ref="I706:I707" si="11">VLOOKUP(G706,D:D,1,0)</f>
+        <v>89560900000863586754</v>
       </c>
     </row>
     <row r="707" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
@@ -23735,15 +23908,15 @@
       <c r="B707" s="29"/>
       <c r="C707" s="3"/>
       <c r="F707" s="10"/>
-      <c r="G707" t="s">
-        <v>166</v>
+      <c r="G707" s="38" t="s">
+        <v>698</v>
       </c>
       <c r="H707" s="31" t="s">
         <v>1308</v>
       </c>
       <c r="I707" t="str">
         <f t="shared" si="11"/>
-        <v>89560900000863574032</v>
+        <v>89560900000863586762</v>
       </c>
     </row>
     <row r="708" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
@@ -23751,292 +23924,792 @@
       <c r="B708" s="29"/>
       <c r="C708" s="3"/>
       <c r="F708" s="10"/>
+      <c r="G708" s="39" t="s">
+        <v>1363</v>
+      </c>
+      <c r="H708" s="31" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I708" t="e">
+        <f t="shared" ref="I708:I757" si="12">VLOOKUP(G708,D:D,1,0)</f>
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="709" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A709" s="30"/>
       <c r="B709" s="29"/>
       <c r="C709" s="3"/>
       <c r="F709" s="10"/>
+      <c r="G709" s="39" t="s">
+        <v>1364</v>
+      </c>
+      <c r="H709" s="31" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I709" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="710" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A710" s="30"/>
       <c r="B710" s="29"/>
       <c r="C710" s="3"/>
       <c r="F710" s="10"/>
+      <c r="G710" s="39" t="s">
+        <v>1365</v>
+      </c>
+      <c r="H710" s="31" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I710" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="711" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A711" s="30"/>
       <c r="B711" s="29"/>
       <c r="C711" s="3"/>
       <c r="F711" s="10"/>
+      <c r="G711" s="39" t="s">
+        <v>1366</v>
+      </c>
+      <c r="H711" s="31" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I711" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="712" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A712" s="30"/>
       <c r="B712" s="29"/>
       <c r="C712" s="3"/>
       <c r="F712" s="10"/>
+      <c r="G712" s="39" t="s">
+        <v>1367</v>
+      </c>
+      <c r="H712" s="31" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I712" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="713" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A713" s="30"/>
       <c r="B713" s="29"/>
       <c r="C713" s="3"/>
       <c r="F713" s="10"/>
+      <c r="G713" s="39" t="s">
+        <v>1368</v>
+      </c>
+      <c r="H713" s="31" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I713" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="714" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A714" s="30"/>
       <c r="B714" s="29"/>
       <c r="C714" s="3"/>
       <c r="F714" s="10"/>
+      <c r="G714" s="39" t="s">
+        <v>1369</v>
+      </c>
+      <c r="H714" s="31" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I714" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="715" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A715" s="30"/>
       <c r="B715" s="29"/>
       <c r="C715" s="3"/>
       <c r="F715" s="10"/>
+      <c r="G715" s="39" t="s">
+        <v>1370</v>
+      </c>
+      <c r="H715" s="31" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I715" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="716" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A716" s="30"/>
       <c r="B716" s="29"/>
       <c r="C716" s="3"/>
       <c r="F716" s="10"/>
+      <c r="G716" s="39" t="s">
+        <v>1371</v>
+      </c>
+      <c r="H716" s="31" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I716" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="717" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A717" s="30"/>
       <c r="B717" s="29"/>
       <c r="C717" s="3"/>
       <c r="F717" s="10"/>
+      <c r="G717" s="39" t="s">
+        <v>1372</v>
+      </c>
+      <c r="H717" s="31" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I717" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="718" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A718" s="30"/>
       <c r="B718" s="29"/>
       <c r="C718" s="3"/>
       <c r="F718" s="10"/>
+      <c r="G718" s="39" t="s">
+        <v>1373</v>
+      </c>
+      <c r="H718" s="31" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I718" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="719" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A719" s="30"/>
       <c r="B719" s="29"/>
       <c r="C719" s="3"/>
       <c r="F719" s="10"/>
+      <c r="G719" s="39" t="s">
+        <v>1374</v>
+      </c>
+      <c r="H719" s="31" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I719" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="720" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A720" s="30"/>
       <c r="B720" s="29"/>
       <c r="C720" s="3"/>
       <c r="F720" s="10"/>
-    </row>
-    <row r="721" spans="1:6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G720" s="39" t="s">
+        <v>1375</v>
+      </c>
+      <c r="H720" s="31" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I720" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="721" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A721" s="33"/>
       <c r="B721" s="34"/>
       <c r="F721" s="10"/>
-    </row>
-    <row r="722" spans="1:6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G721" s="39" t="s">
+        <v>1376</v>
+      </c>
+      <c r="H721" s="31" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I721" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="722" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A722" s="33"/>
       <c r="B722" s="34"/>
       <c r="F722" s="10"/>
-    </row>
-    <row r="723" spans="1:6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G722" s="39" t="s">
+        <v>1377</v>
+      </c>
+      <c r="H722" s="31" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I722" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="723" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A723" s="33"/>
       <c r="B723" s="34"/>
       <c r="F723" s="10"/>
-    </row>
-    <row r="724" spans="1:6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G723" s="39" t="s">
+        <v>1378</v>
+      </c>
+      <c r="H723" s="31" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I723" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="724" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A724" s="33"/>
       <c r="B724" s="34"/>
       <c r="F724" s="10"/>
-    </row>
-    <row r="725" spans="1:6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G724" s="39" t="s">
+        <v>1379</v>
+      </c>
+      <c r="H724" s="31" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I724" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="725" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A725" s="33"/>
       <c r="B725" s="34"/>
       <c r="F725" s="10"/>
-    </row>
-    <row r="726" spans="1:6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G725" s="39" t="s">
+        <v>1380</v>
+      </c>
+      <c r="H725" s="31" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I725" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="726" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A726" s="33"/>
       <c r="B726" s="34"/>
       <c r="F726" s="10"/>
-    </row>
-    <row r="727" spans="1:6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G726" s="39" t="s">
+        <v>1381</v>
+      </c>
+      <c r="H726" s="31" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I726" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="727" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A727" s="33"/>
       <c r="B727" s="34"/>
       <c r="F727" s="10"/>
-    </row>
-    <row r="728" spans="1:6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G727" s="39" t="s">
+        <v>1382</v>
+      </c>
+      <c r="H727" s="31" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I727" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="728" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A728" s="33"/>
       <c r="B728" s="34"/>
       <c r="F728" s="10"/>
-    </row>
-    <row r="729" spans="1:6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G728" s="39" t="s">
+        <v>1383</v>
+      </c>
+      <c r="H728" s="31" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I728" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="729" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A729" s="33"/>
       <c r="B729" s="34"/>
       <c r="F729" s="10"/>
-    </row>
-    <row r="730" spans="1:6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G729" s="39" t="s">
+        <v>1384</v>
+      </c>
+      <c r="H729" s="31" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I729" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="730" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A730" s="33"/>
       <c r="B730" s="34"/>
       <c r="F730" s="10"/>
-    </row>
-    <row r="731" spans="1:6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G730" s="39" t="s">
+        <v>1385</v>
+      </c>
+      <c r="H730" s="31" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I730" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="731" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A731" s="33"/>
       <c r="B731" s="34"/>
       <c r="F731" s="10"/>
-    </row>
-    <row r="732" spans="1:6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G731" s="39" t="s">
+        <v>1386</v>
+      </c>
+      <c r="H731" s="31" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I731" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="732" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A732" s="33"/>
       <c r="B732" s="34"/>
       <c r="F732" s="10"/>
-    </row>
-    <row r="733" spans="1:6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G732" s="39" t="s">
+        <v>1387</v>
+      </c>
+      <c r="H732" s="31" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I732" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="733" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A733" s="33"/>
       <c r="B733" s="34"/>
       <c r="F733" s="10"/>
-    </row>
-    <row r="734" spans="1:6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G733" s="39" t="s">
+        <v>1388</v>
+      </c>
+      <c r="H733" s="31" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I733" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="734" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A734" s="33"/>
       <c r="B734" s="34"/>
       <c r="F734" s="10"/>
-    </row>
-    <row r="735" spans="1:6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G734" s="39" t="s">
+        <v>1389</v>
+      </c>
+      <c r="H734" s="31" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I734" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="735" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A735" s="33"/>
       <c r="B735" s="34"/>
       <c r="F735" s="10"/>
-    </row>
-    <row r="736" spans="1:6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G735" s="39" t="s">
+        <v>1390</v>
+      </c>
+      <c r="H735" s="31" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I735" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="736" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A736" s="33"/>
       <c r="B736" s="34"/>
       <c r="F736" s="10"/>
-    </row>
-    <row r="737" spans="1:6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G736" s="39" t="s">
+        <v>1391</v>
+      </c>
+      <c r="H736" s="31" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I736" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="737" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A737" s="33"/>
       <c r="B737" s="34"/>
       <c r="F737" s="10"/>
-    </row>
-    <row r="738" spans="1:6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G737" s="39" t="s">
+        <v>1392</v>
+      </c>
+      <c r="H737" s="31" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I737" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="738" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A738" s="33"/>
       <c r="B738" s="34"/>
       <c r="F738" s="10"/>
-    </row>
-    <row r="739" spans="1:6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G738" s="39" t="s">
+        <v>1393</v>
+      </c>
+      <c r="H738" s="31" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I738" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="739" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A739" s="33"/>
       <c r="B739" s="34"/>
       <c r="F739" s="10"/>
-    </row>
-    <row r="740" spans="1:6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G739" s="39" t="s">
+        <v>1394</v>
+      </c>
+      <c r="H739" s="31" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I739" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="740" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A740" s="33"/>
       <c r="B740" s="34"/>
       <c r="F740" s="10"/>
-    </row>
-    <row r="741" spans="1:6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G740" s="39" t="s">
+        <v>1395</v>
+      </c>
+      <c r="H740" s="31" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I740" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="741" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A741" s="33"/>
       <c r="B741" s="34"/>
       <c r="F741" s="10"/>
-    </row>
-    <row r="742" spans="1:6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G741" s="39" t="s">
+        <v>1396</v>
+      </c>
+      <c r="H741" s="31" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I741" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="742" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A742" s="33"/>
       <c r="B742" s="34"/>
       <c r="F742" s="10"/>
-    </row>
-    <row r="743" spans="1:6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G742" s="39" t="s">
+        <v>1397</v>
+      </c>
+      <c r="H742" s="31" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I742" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="743" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A743" s="33"/>
       <c r="B743" s="34"/>
       <c r="F743" s="10"/>
-    </row>
-    <row r="744" spans="1:6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G743" s="39" t="s">
+        <v>1398</v>
+      </c>
+      <c r="H743" s="31" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I743" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="744" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A744" s="33"/>
       <c r="B744" s="34"/>
       <c r="F744" s="10"/>
-    </row>
-    <row r="745" spans="1:6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G744" s="39" t="s">
+        <v>1399</v>
+      </c>
+      <c r="H744" s="31" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I744" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="745" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A745" s="33"/>
       <c r="B745" s="34"/>
-    </row>
-    <row r="746" spans="1:6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G745" s="39" t="s">
+        <v>1400</v>
+      </c>
+      <c r="H745" s="31" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I745" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="746" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A746" s="33"/>
       <c r="B746" s="34"/>
-    </row>
-    <row r="747" spans="1:6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G746" s="39" t="s">
+        <v>1401</v>
+      </c>
+      <c r="H746" s="31" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I746" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="747" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A747" s="33"/>
       <c r="B747" s="34"/>
-    </row>
-    <row r="748" spans="1:6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G747" s="39" t="s">
+        <v>1402</v>
+      </c>
+      <c r="H747" s="31" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I747" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="748" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A748" s="33"/>
       <c r="B748" s="34"/>
-    </row>
-    <row r="749" spans="1:6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G748" s="39" t="s">
+        <v>1403</v>
+      </c>
+      <c r="H748" s="31" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I748" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="749" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A749" s="33"/>
       <c r="B749" s="34"/>
-    </row>
-    <row r="750" spans="1:6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G749" s="39" t="s">
+        <v>1404</v>
+      </c>
+      <c r="H749" s="31" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I749" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="750" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A750" s="33"/>
       <c r="B750" s="34"/>
-    </row>
-    <row r="751" spans="1:6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G750" s="39" t="s">
+        <v>1405</v>
+      </c>
+      <c r="H750" s="31" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I750" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="751" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A751" s="33"/>
       <c r="B751" s="34"/>
-    </row>
-    <row r="752" spans="1:6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G751" s="39" t="s">
+        <v>1406</v>
+      </c>
+      <c r="H751" s="31" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I751" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="752" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A752" s="33"/>
       <c r="B752" s="34"/>
-    </row>
-    <row r="753" spans="1:2" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G752" s="39" t="s">
+        <v>1407</v>
+      </c>
+      <c r="H752" s="31" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I752" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="753" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A753" s="33"/>
       <c r="B753" s="34"/>
-    </row>
-    <row r="754" spans="1:2" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G753" s="39" t="s">
+        <v>1408</v>
+      </c>
+      <c r="H753" s="31" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I753" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="754" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A754" s="33"/>
       <c r="B754" s="34"/>
-    </row>
-    <row r="755" spans="1:2" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G754" s="39" t="s">
+        <v>1409</v>
+      </c>
+      <c r="H754" s="31" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I754" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="755" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A755" s="33"/>
       <c r="B755" s="34"/>
-    </row>
-    <row r="756" spans="1:2" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G755" s="39" t="s">
+        <v>1410</v>
+      </c>
+      <c r="H755" s="31" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I755" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="756" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A756" s="33"/>
       <c r="B756" s="34"/>
-    </row>
-    <row r="757" spans="1:2" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G756" s="39" t="s">
+        <v>1411</v>
+      </c>
+      <c r="H756" s="31" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I756" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="757" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A757" s="33"/>
       <c r="B757" s="34"/>
-    </row>
-    <row r="758" spans="1:2" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G757" s="39" t="s">
+        <v>1412</v>
+      </c>
+      <c r="H757" s="31" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I757" t="e">
+        <f t="shared" si="12"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="758" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A758" s="33"/>
       <c r="B758" s="34"/>
     </row>
-    <row r="759" spans="1:2" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="759" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A759" s="33"/>
       <c r="B759" s="34"/>
     </row>
-    <row r="760" spans="1:2" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="760" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A760" s="33"/>
       <c r="B760" s="34"/>
     </row>
-    <row r="761" spans="1:2" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="761" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A761" s="33"/>
       <c r="B761" s="34"/>
     </row>
-    <row r="762" spans="1:2" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="762" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A762" s="33"/>
       <c r="B762" s="34"/>
     </row>
-    <row r="763" spans="1:2" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="763" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A763" s="33"/>
       <c r="B763" s="34"/>
     </row>
-    <row r="764" spans="1:2" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="764" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A764" s="33"/>
       <c r="B764" s="34"/>
     </row>
-    <row r="765" spans="1:2" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="765" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A765" s="33"/>
       <c r="B765" s="34"/>
     </row>
-    <row r="766" spans="1:2" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="766" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A766" s="33"/>
       <c r="B766" s="34"/>
     </row>
-    <row r="767" spans="1:2" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="767" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A767" s="33"/>
       <c r="B767" s="34"/>
     </row>
-    <row r="768" spans="1:2" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="768" spans="1:9" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A768" s="33"/>
       <c r="B768" s="34"/>
     </row>
